--- a/internal/app/templates/admin-loan-request-template.xlsx
+++ b/internal/app/templates/admin-loan-request-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pengajuan Pinjaman" sheetId="1" r:id="R81d99bcc603a4504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R3c2f304dbbca4b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pengajuan Pinjaman" sheetId="1" r:id="R188b1756b04e4ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R0b5e9368cddf4476"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -75,8 +75,13 @@
         <x:fgColor rgb="FF115E59"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF145B59"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="4">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -106,11 +111,25 @@
         <x:color rgb="FFD1D5DB"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD5DAE2"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD5DAE2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD5DAE2"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD5DAE2"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -158,6 +177,16 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -365,6 +394,7 @@
     <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -408,6 +438,9 @@
       <x:c r="E4" s="15" t="str">
         <x:v>Tujuan</x:v>
       </x:c>
+      <x:c r="F4" s="26" t="str">
+        <x:v>Biaya Admin (Nominal)</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="18"/>
@@ -415,6 +448,7 @@
       <x:c r="C5" s="19"/>
       <x:c r="D5" s="19"/>
       <x:c r="E5" s="17"/>
+      <x:c r="F5" s="28"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="18"/>
@@ -422,6 +456,7 @@
       <x:c r="C6" s="19"/>
       <x:c r="D6" s="19"/>
       <x:c r="E6" s="17"/>
+      <x:c r="F6" s="28"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="18"/>
@@ -429,6 +464,7 @@
       <x:c r="C7" s="19"/>
       <x:c r="D7" s="19"/>
       <x:c r="E7" s="17"/>
+      <x:c r="F7" s="28"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="18"/>
@@ -436,6 +472,7 @@
       <x:c r="C8" s="19"/>
       <x:c r="D8" s="19"/>
       <x:c r="E8" s="17"/>
+      <x:c r="F8" s="28"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="18"/>
@@ -443,6 +480,7 @@
       <x:c r="C9" s="19"/>
       <x:c r="D9" s="19"/>
       <x:c r="E9" s="17"/>
+      <x:c r="F9" s="28"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="18"/>
@@ -450,6 +488,7 @@
       <x:c r="C10" s="19"/>
       <x:c r="D10" s="19"/>
       <x:c r="E10" s="17"/>
+      <x:c r="F10" s="28"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="18"/>
@@ -457,6 +496,7 @@
       <x:c r="C11" s="19"/>
       <x:c r="D11" s="19"/>
       <x:c r="E11" s="17"/>
+      <x:c r="F11" s="28"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="18"/>
@@ -464,6 +504,7 @@
       <x:c r="C12" s="19"/>
       <x:c r="D12" s="19"/>
       <x:c r="E12" s="17"/>
+      <x:c r="F12" s="28"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="18"/>
@@ -471,6 +512,7 @@
       <x:c r="C13" s="19"/>
       <x:c r="D13" s="19"/>
       <x:c r="E13" s="17"/>
+      <x:c r="F13" s="28"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="18"/>
@@ -478,6 +520,7 @@
       <x:c r="C14" s="19"/>
       <x:c r="D14" s="19"/>
       <x:c r="E14" s="17"/>
+      <x:c r="F14" s="28"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="18"/>
@@ -485,6 +528,7 @@
       <x:c r="C15" s="19"/>
       <x:c r="D15" s="19"/>
       <x:c r="E15" s="17"/>
+      <x:c r="F15" s="28"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="18"/>
@@ -492,6 +536,7 @@
       <x:c r="C16" s="19"/>
       <x:c r="D16" s="19"/>
       <x:c r="E16" s="17"/>
+      <x:c r="F16" s="28"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="18"/>
@@ -499,6 +544,7 @@
       <x:c r="C17" s="19"/>
       <x:c r="D17" s="19"/>
       <x:c r="E17" s="17"/>
+      <x:c r="F17" s="28"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="18"/>
@@ -506,6 +552,7 @@
       <x:c r="C18" s="19"/>
       <x:c r="D18" s="19"/>
       <x:c r="E18" s="17"/>
+      <x:c r="F18" s="28"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="18"/>
@@ -513,6 +560,7 @@
       <x:c r="C19" s="19"/>
       <x:c r="D19" s="19"/>
       <x:c r="E19" s="17"/>
+      <x:c r="F19" s="28"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="18"/>
@@ -520,6 +568,7 @@
       <x:c r="C20" s="19"/>
       <x:c r="D20" s="19"/>
       <x:c r="E20" s="17"/>
+      <x:c r="F20" s="28"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="18"/>
@@ -527,6 +576,7 @@
       <x:c r="C21" s="19"/>
       <x:c r="D21" s="19"/>
       <x:c r="E21" s="17"/>
+      <x:c r="F21" s="28"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="18"/>
@@ -534,6 +584,7 @@
       <x:c r="C22" s="19"/>
       <x:c r="D22" s="19"/>
       <x:c r="E22" s="17"/>
+      <x:c r="F22" s="28"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="18"/>
@@ -541,6 +592,7 @@
       <x:c r="C23" s="19"/>
       <x:c r="D23" s="19"/>
       <x:c r="E23" s="17"/>
+      <x:c r="F23" s="28"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="18"/>
@@ -548,6 +600,7 @@
       <x:c r="C24" s="19"/>
       <x:c r="D24" s="19"/>
       <x:c r="E24" s="17"/>
+      <x:c r="F24" s="28"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="18"/>
@@ -555,6 +608,7 @@
       <x:c r="C25" s="19"/>
       <x:c r="D25" s="19"/>
       <x:c r="E25" s="17"/>
+      <x:c r="F25" s="28"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="18"/>
@@ -562,6 +616,7 @@
       <x:c r="C26" s="19"/>
       <x:c r="D26" s="19"/>
       <x:c r="E26" s="17"/>
+      <x:c r="F26" s="28"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="18"/>
@@ -569,6 +624,7 @@
       <x:c r="C27" s="19"/>
       <x:c r="D27" s="19"/>
       <x:c r="E27" s="17"/>
+      <x:c r="F27" s="28"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="18"/>
@@ -576,6 +632,7 @@
       <x:c r="C28" s="19"/>
       <x:c r="D28" s="19"/>
       <x:c r="E28" s="17"/>
+      <x:c r="F28" s="28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="18"/>
@@ -583,6 +640,7 @@
       <x:c r="C29" s="19"/>
       <x:c r="D29" s="19"/>
       <x:c r="E29" s="17"/>
+      <x:c r="F29" s="28"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="18"/>
@@ -590,6 +648,7 @@
       <x:c r="C30" s="19"/>
       <x:c r="D30" s="19"/>
       <x:c r="E30" s="17"/>
+      <x:c r="F30" s="28"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="18"/>
@@ -597,6 +656,7 @@
       <x:c r="C31" s="19"/>
       <x:c r="D31" s="19"/>
       <x:c r="E31" s="17"/>
+      <x:c r="F31" s="28"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="18"/>
@@ -604,6 +664,7 @@
       <x:c r="C32" s="19"/>
       <x:c r="D32" s="19"/>
       <x:c r="E32" s="17"/>
+      <x:c r="F32" s="28"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="18"/>
@@ -611,6 +672,7 @@
       <x:c r="C33" s="19"/>
       <x:c r="D33" s="19"/>
       <x:c r="E33" s="17"/>
+      <x:c r="F33" s="28"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="18"/>
@@ -618,6 +680,7 @@
       <x:c r="C34" s="19"/>
       <x:c r="D34" s="19"/>
       <x:c r="E34" s="17"/>
+      <x:c r="F34" s="28"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="18"/>
@@ -625,6 +688,7 @@
       <x:c r="C35" s="19"/>
       <x:c r="D35" s="19"/>
       <x:c r="E35" s="17"/>
+      <x:c r="F35" s="28"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="18"/>
@@ -632,6 +696,7 @@
       <x:c r="C36" s="19"/>
       <x:c r="D36" s="19"/>
       <x:c r="E36" s="17"/>
+      <x:c r="F36" s="28"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="18"/>
@@ -639,6 +704,7 @@
       <x:c r="C37" s="19"/>
       <x:c r="D37" s="19"/>
       <x:c r="E37" s="17"/>
+      <x:c r="F37" s="28"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="18"/>
@@ -646,6 +712,7 @@
       <x:c r="C38" s="19"/>
       <x:c r="D38" s="19"/>
       <x:c r="E38" s="17"/>
+      <x:c r="F38" s="28"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="18"/>
@@ -653,6 +720,7 @@
       <x:c r="C39" s="19"/>
       <x:c r="D39" s="19"/>
       <x:c r="E39" s="17"/>
+      <x:c r="F39" s="28"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="18"/>
@@ -660,6 +728,7 @@
       <x:c r="C40" s="19"/>
       <x:c r="D40" s="19"/>
       <x:c r="E40" s="17"/>
+      <x:c r="F40" s="28"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="18"/>
@@ -667,6 +736,7 @@
       <x:c r="C41" s="19"/>
       <x:c r="D41" s="19"/>
       <x:c r="E41" s="17"/>
+      <x:c r="F41" s="28"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="18"/>
@@ -674,6 +744,7 @@
       <x:c r="C42" s="19"/>
       <x:c r="D42" s="19"/>
       <x:c r="E42" s="17"/>
+      <x:c r="F42" s="28"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="18"/>
@@ -681,6 +752,7 @@
       <x:c r="C43" s="19"/>
       <x:c r="D43" s="19"/>
       <x:c r="E43" s="17"/>
+      <x:c r="F43" s="28"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="18"/>
@@ -688,6 +760,7 @@
       <x:c r="C44" s="19"/>
       <x:c r="D44" s="19"/>
       <x:c r="E44" s="17"/>
+      <x:c r="F44" s="28"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="18"/>
@@ -695,6 +768,7 @@
       <x:c r="C45" s="19"/>
       <x:c r="D45" s="19"/>
       <x:c r="E45" s="17"/>
+      <x:c r="F45" s="28"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="18"/>
@@ -702,6 +776,7 @@
       <x:c r="C46" s="19"/>
       <x:c r="D46" s="19"/>
       <x:c r="E46" s="17"/>
+      <x:c r="F46" s="28"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="18"/>
@@ -709,6 +784,7 @@
       <x:c r="C47" s="19"/>
       <x:c r="D47" s="19"/>
       <x:c r="E47" s="17"/>
+      <x:c r="F47" s="28"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="18"/>
@@ -716,6 +792,7 @@
       <x:c r="C48" s="19"/>
       <x:c r="D48" s="19"/>
       <x:c r="E48" s="17"/>
+      <x:c r="F48" s="28"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="18"/>
@@ -723,6 +800,7 @@
       <x:c r="C49" s="19"/>
       <x:c r="D49" s="19"/>
       <x:c r="E49" s="17"/>
+      <x:c r="F49" s="28"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="18"/>
@@ -730,6 +808,7 @@
       <x:c r="C50" s="19"/>
       <x:c r="D50" s="19"/>
       <x:c r="E50" s="17"/>
+      <x:c r="F50" s="28"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="18"/>
@@ -737,6 +816,7 @@
       <x:c r="C51" s="19"/>
       <x:c r="D51" s="19"/>
       <x:c r="E51" s="17"/>
+      <x:c r="F51" s="28"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="18"/>
@@ -744,6 +824,7 @@
       <x:c r="C52" s="19"/>
       <x:c r="D52" s="19"/>
       <x:c r="E52" s="17"/>
+      <x:c r="F52" s="28"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="18"/>
@@ -751,6 +832,7 @@
       <x:c r="C53" s="19"/>
       <x:c r="D53" s="19"/>
       <x:c r="E53" s="17"/>
+      <x:c r="F53" s="28"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="18"/>
@@ -758,6 +840,7 @@
       <x:c r="C54" s="19"/>
       <x:c r="D54" s="19"/>
       <x:c r="E54" s="17"/>
+      <x:c r="F54" s="28"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="18"/>
@@ -765,6 +848,7 @@
       <x:c r="C55" s="19"/>
       <x:c r="D55" s="19"/>
       <x:c r="E55" s="17"/>
+      <x:c r="F55" s="28"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="18"/>
@@ -772,6 +856,7 @@
       <x:c r="C56" s="19"/>
       <x:c r="D56" s="19"/>
       <x:c r="E56" s="17"/>
+      <x:c r="F56" s="28"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="18"/>
@@ -779,6 +864,7 @@
       <x:c r="C57" s="19"/>
       <x:c r="D57" s="19"/>
       <x:c r="E57" s="17"/>
+      <x:c r="F57" s="28"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="18"/>
@@ -786,6 +872,7 @@
       <x:c r="C58" s="19"/>
       <x:c r="D58" s="19"/>
       <x:c r="E58" s="17"/>
+      <x:c r="F58" s="28"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="18"/>
@@ -793,6 +880,7 @@
       <x:c r="C59" s="19"/>
       <x:c r="D59" s="19"/>
       <x:c r="E59" s="17"/>
+      <x:c r="F59" s="28"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="18"/>
@@ -800,6 +888,7 @@
       <x:c r="C60" s="19"/>
       <x:c r="D60" s="19"/>
       <x:c r="E60" s="17"/>
+      <x:c r="F60" s="28"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="18"/>
@@ -807,6 +896,7 @@
       <x:c r="C61" s="19"/>
       <x:c r="D61" s="19"/>
       <x:c r="E61" s="17"/>
+      <x:c r="F61" s="28"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="18"/>
@@ -814,6 +904,7 @@
       <x:c r="C62" s="19"/>
       <x:c r="D62" s="19"/>
       <x:c r="E62" s="17"/>
+      <x:c r="F62" s="28"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="18"/>
@@ -821,6 +912,7 @@
       <x:c r="C63" s="19"/>
       <x:c r="D63" s="19"/>
       <x:c r="E63" s="17"/>
+      <x:c r="F63" s="28"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="18"/>
@@ -828,6 +920,7 @@
       <x:c r="C64" s="19"/>
       <x:c r="D64" s="19"/>
       <x:c r="E64" s="17"/>
+      <x:c r="F64" s="28"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="18"/>
@@ -835,6 +928,7 @@
       <x:c r="C65" s="19"/>
       <x:c r="D65" s="19"/>
       <x:c r="E65" s="17"/>
+      <x:c r="F65" s="28"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="18"/>
@@ -842,6 +936,7 @@
       <x:c r="C66" s="19"/>
       <x:c r="D66" s="19"/>
       <x:c r="E66" s="17"/>
+      <x:c r="F66" s="28"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="18"/>
@@ -849,6 +944,7 @@
       <x:c r="C67" s="19"/>
       <x:c r="D67" s="19"/>
       <x:c r="E67" s="17"/>
+      <x:c r="F67" s="28"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="18"/>
@@ -856,6 +952,7 @@
       <x:c r="C68" s="19"/>
       <x:c r="D68" s="19"/>
       <x:c r="E68" s="17"/>
+      <x:c r="F68" s="28"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="18"/>
@@ -863,6 +960,7 @@
       <x:c r="C69" s="19"/>
       <x:c r="D69" s="19"/>
       <x:c r="E69" s="17"/>
+      <x:c r="F69" s="28"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="18"/>
@@ -870,6 +968,7 @@
       <x:c r="C70" s="19"/>
       <x:c r="D70" s="19"/>
       <x:c r="E70" s="17"/>
+      <x:c r="F70" s="28"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="18"/>
@@ -877,6 +976,7 @@
       <x:c r="C71" s="19"/>
       <x:c r="D71" s="19"/>
       <x:c r="E71" s="17"/>
+      <x:c r="F71" s="28"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="18"/>
@@ -884,6 +984,7 @@
       <x:c r="C72" s="19"/>
       <x:c r="D72" s="19"/>
       <x:c r="E72" s="17"/>
+      <x:c r="F72" s="28"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="18"/>
@@ -891,6 +992,7 @@
       <x:c r="C73" s="19"/>
       <x:c r="D73" s="19"/>
       <x:c r="E73" s="17"/>
+      <x:c r="F73" s="28"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="18"/>
@@ -898,6 +1000,7 @@
       <x:c r="C74" s="19"/>
       <x:c r="D74" s="19"/>
       <x:c r="E74" s="17"/>
+      <x:c r="F74" s="28"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="18"/>
@@ -905,6 +1008,7 @@
       <x:c r="C75" s="19"/>
       <x:c r="D75" s="19"/>
       <x:c r="E75" s="17"/>
+      <x:c r="F75" s="28"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="18"/>
@@ -912,6 +1016,7 @@
       <x:c r="C76" s="19"/>
       <x:c r="D76" s="19"/>
       <x:c r="E76" s="17"/>
+      <x:c r="F76" s="28"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="18"/>
@@ -919,6 +1024,7 @@
       <x:c r="C77" s="19"/>
       <x:c r="D77" s="19"/>
       <x:c r="E77" s="17"/>
+      <x:c r="F77" s="28"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="18"/>
@@ -926,6 +1032,7 @@
       <x:c r="C78" s="19"/>
       <x:c r="D78" s="19"/>
       <x:c r="E78" s="17"/>
+      <x:c r="F78" s="28"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="18"/>
@@ -933,6 +1040,7 @@
       <x:c r="C79" s="19"/>
       <x:c r="D79" s="19"/>
       <x:c r="E79" s="17"/>
+      <x:c r="F79" s="28"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="18"/>
@@ -940,6 +1048,7 @@
       <x:c r="C80" s="19"/>
       <x:c r="D80" s="19"/>
       <x:c r="E80" s="17"/>
+      <x:c r="F80" s="28"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="18"/>
@@ -947,6 +1056,7 @@
       <x:c r="C81" s="19"/>
       <x:c r="D81" s="19"/>
       <x:c r="E81" s="17"/>
+      <x:c r="F81" s="28"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="18"/>
@@ -954,6 +1064,7 @@
       <x:c r="C82" s="19"/>
       <x:c r="D82" s="19"/>
       <x:c r="E82" s="17"/>
+      <x:c r="F82" s="28"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="18"/>
@@ -961,6 +1072,7 @@
       <x:c r="C83" s="19"/>
       <x:c r="D83" s="19"/>
       <x:c r="E83" s="17"/>
+      <x:c r="F83" s="28"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="18"/>
@@ -968,6 +1080,7 @@
       <x:c r="C84" s="19"/>
       <x:c r="D84" s="19"/>
       <x:c r="E84" s="17"/>
+      <x:c r="F84" s="28"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="18"/>
@@ -975,6 +1088,7 @@
       <x:c r="C85" s="19"/>
       <x:c r="D85" s="19"/>
       <x:c r="E85" s="17"/>
+      <x:c r="F85" s="28"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="18"/>
@@ -982,6 +1096,7 @@
       <x:c r="C86" s="19"/>
       <x:c r="D86" s="19"/>
       <x:c r="E86" s="17"/>
+      <x:c r="F86" s="28"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="18"/>
@@ -989,6 +1104,7 @@
       <x:c r="C87" s="19"/>
       <x:c r="D87" s="19"/>
       <x:c r="E87" s="17"/>
+      <x:c r="F87" s="28"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="18"/>
@@ -996,6 +1112,7 @@
       <x:c r="C88" s="19"/>
       <x:c r="D88" s="19"/>
       <x:c r="E88" s="17"/>
+      <x:c r="F88" s="28"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="18"/>
@@ -1003,6 +1120,7 @@
       <x:c r="C89" s="19"/>
       <x:c r="D89" s="19"/>
       <x:c r="E89" s="17"/>
+      <x:c r="F89" s="28"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="18"/>
@@ -1010,6 +1128,7 @@
       <x:c r="C90" s="19"/>
       <x:c r="D90" s="19"/>
       <x:c r="E90" s="17"/>
+      <x:c r="F90" s="28"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="18"/>
@@ -1017,6 +1136,7 @@
       <x:c r="C91" s="19"/>
       <x:c r="D91" s="19"/>
       <x:c r="E91" s="17"/>
+      <x:c r="F91" s="28"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="18"/>
@@ -1024,6 +1144,7 @@
       <x:c r="C92" s="19"/>
       <x:c r="D92" s="19"/>
       <x:c r="E92" s="17"/>
+      <x:c r="F92" s="28"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="18"/>
@@ -1031,6 +1152,7 @@
       <x:c r="C93" s="19"/>
       <x:c r="D93" s="19"/>
       <x:c r="E93" s="17"/>
+      <x:c r="F93" s="28"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="18"/>
@@ -1038,6 +1160,7 @@
       <x:c r="C94" s="19"/>
       <x:c r="D94" s="19"/>
       <x:c r="E94" s="17"/>
+      <x:c r="F94" s="28"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="18"/>
@@ -1045,6 +1168,7 @@
       <x:c r="C95" s="19"/>
       <x:c r="D95" s="19"/>
       <x:c r="E95" s="17"/>
+      <x:c r="F95" s="28"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="18"/>
@@ -1052,6 +1176,7 @@
       <x:c r="C96" s="19"/>
       <x:c r="D96" s="19"/>
       <x:c r="E96" s="17"/>
+      <x:c r="F96" s="28"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="18"/>
@@ -1059,6 +1184,7 @@
       <x:c r="C97" s="19"/>
       <x:c r="D97" s="19"/>
       <x:c r="E97" s="17"/>
+      <x:c r="F97" s="28"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="18"/>
@@ -1066,6 +1192,7 @@
       <x:c r="C98" s="19"/>
       <x:c r="D98" s="19"/>
       <x:c r="E98" s="17"/>
+      <x:c r="F98" s="28"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="18"/>
@@ -1073,6 +1200,7 @@
       <x:c r="C99" s="19"/>
       <x:c r="D99" s="19"/>
       <x:c r="E99" s="17"/>
+      <x:c r="F99" s="28"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="18"/>
@@ -1080,6 +1208,7 @@
       <x:c r="C100" s="19"/>
       <x:c r="D100" s="19"/>
       <x:c r="E100" s="17"/>
+      <x:c r="F100" s="28"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="18"/>
@@ -1087,6 +1216,7 @@
       <x:c r="C101" s="19"/>
       <x:c r="D101" s="19"/>
       <x:c r="E101" s="17"/>
+      <x:c r="F101" s="28"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="18"/>
@@ -1094,6 +1224,7 @@
       <x:c r="C102" s="19"/>
       <x:c r="D102" s="19"/>
       <x:c r="E102" s="17"/>
+      <x:c r="F102" s="28"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="18"/>
@@ -1101,6 +1232,7 @@
       <x:c r="C103" s="19"/>
       <x:c r="D103" s="19"/>
       <x:c r="E103" s="17"/>
+      <x:c r="F103" s="28"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="18"/>
@@ -1108,6 +1240,7 @@
       <x:c r="C104" s="19"/>
       <x:c r="D104" s="19"/>
       <x:c r="E104" s="17"/>
+      <x:c r="F104" s="28"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="18"/>
@@ -1115,6 +1248,7 @@
       <x:c r="C105" s="19"/>
       <x:c r="D105" s="19"/>
       <x:c r="E105" s="17"/>
+      <x:c r="F105" s="28"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="18"/>
@@ -1122,6 +1256,7 @@
       <x:c r="C106" s="19"/>
       <x:c r="D106" s="19"/>
       <x:c r="E106" s="17"/>
+      <x:c r="F106" s="28"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="18"/>
@@ -1129,6 +1264,7 @@
       <x:c r="C107" s="19"/>
       <x:c r="D107" s="19"/>
       <x:c r="E107" s="17"/>
+      <x:c r="F107" s="28"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="18"/>
@@ -1136,6 +1272,7 @@
       <x:c r="C108" s="19"/>
       <x:c r="D108" s="19"/>
       <x:c r="E108" s="17"/>
+      <x:c r="F108" s="28"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="18"/>
@@ -1143,6 +1280,7 @@
       <x:c r="C109" s="19"/>
       <x:c r="D109" s="19"/>
       <x:c r="E109" s="17"/>
+      <x:c r="F109" s="28"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="18"/>
@@ -1150,6 +1288,7 @@
       <x:c r="C110" s="19"/>
       <x:c r="D110" s="19"/>
       <x:c r="E110" s="17"/>
+      <x:c r="F110" s="28"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="18"/>
@@ -1157,6 +1296,7 @@
       <x:c r="C111" s="19"/>
       <x:c r="D111" s="19"/>
       <x:c r="E111" s="17"/>
+      <x:c r="F111" s="28"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="18"/>
@@ -1164,6 +1304,7 @@
       <x:c r="C112" s="19"/>
       <x:c r="D112" s="19"/>
       <x:c r="E112" s="17"/>
+      <x:c r="F112" s="28"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="18"/>
@@ -1171,6 +1312,7 @@
       <x:c r="C113" s="19"/>
       <x:c r="D113" s="19"/>
       <x:c r="E113" s="17"/>
+      <x:c r="F113" s="28"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="18"/>
@@ -1178,6 +1320,7 @@
       <x:c r="C114" s="19"/>
       <x:c r="D114" s="19"/>
       <x:c r="E114" s="17"/>
+      <x:c r="F114" s="28"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="18"/>
@@ -1185,6 +1328,7 @@
       <x:c r="C115" s="19"/>
       <x:c r="D115" s="19"/>
       <x:c r="E115" s="17"/>
+      <x:c r="F115" s="28"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="18"/>
@@ -1192,6 +1336,7 @@
       <x:c r="C116" s="19"/>
       <x:c r="D116" s="19"/>
       <x:c r="E116" s="17"/>
+      <x:c r="F116" s="28"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="18"/>
@@ -1199,6 +1344,7 @@
       <x:c r="C117" s="19"/>
       <x:c r="D117" s="19"/>
       <x:c r="E117" s="17"/>
+      <x:c r="F117" s="28"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="18"/>
@@ -1206,6 +1352,7 @@
       <x:c r="C118" s="19"/>
       <x:c r="D118" s="19"/>
       <x:c r="E118" s="17"/>
+      <x:c r="F118" s="28"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="18"/>
@@ -1213,6 +1360,7 @@
       <x:c r="C119" s="19"/>
       <x:c r="D119" s="19"/>
       <x:c r="E119" s="17"/>
+      <x:c r="F119" s="28"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="18"/>
@@ -1220,6 +1368,7 @@
       <x:c r="C120" s="19"/>
       <x:c r="D120" s="19"/>
       <x:c r="E120" s="17"/>
+      <x:c r="F120" s="28"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="18"/>
@@ -1227,6 +1376,7 @@
       <x:c r="C121" s="19"/>
       <x:c r="D121" s="19"/>
       <x:c r="E121" s="17"/>
+      <x:c r="F121" s="28"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="18"/>
@@ -1234,6 +1384,7 @@
       <x:c r="C122" s="19"/>
       <x:c r="D122" s="19"/>
       <x:c r="E122" s="17"/>
+      <x:c r="F122" s="28"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="18"/>
@@ -1241,6 +1392,7 @@
       <x:c r="C123" s="19"/>
       <x:c r="D123" s="19"/>
       <x:c r="E123" s="17"/>
+      <x:c r="F123" s="28"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="18"/>
@@ -1248,6 +1400,7 @@
       <x:c r="C124" s="19"/>
       <x:c r="D124" s="19"/>
       <x:c r="E124" s="17"/>
+      <x:c r="F124" s="28"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="18"/>
@@ -1255,6 +1408,7 @@
       <x:c r="C125" s="19"/>
       <x:c r="D125" s="19"/>
       <x:c r="E125" s="17"/>
+      <x:c r="F125" s="28"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="18"/>
@@ -1262,6 +1416,7 @@
       <x:c r="C126" s="19"/>
       <x:c r="D126" s="19"/>
       <x:c r="E126" s="17"/>
+      <x:c r="F126" s="28"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="18"/>
@@ -1269,6 +1424,7 @@
       <x:c r="C127" s="19"/>
       <x:c r="D127" s="19"/>
       <x:c r="E127" s="17"/>
+      <x:c r="F127" s="28"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="18"/>
@@ -1276,6 +1432,7 @@
       <x:c r="C128" s="19"/>
       <x:c r="D128" s="19"/>
       <x:c r="E128" s="17"/>
+      <x:c r="F128" s="28"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="18"/>
@@ -1283,6 +1440,7 @@
       <x:c r="C129" s="19"/>
       <x:c r="D129" s="19"/>
       <x:c r="E129" s="17"/>
+      <x:c r="F129" s="28"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="18"/>
@@ -1290,6 +1448,7 @@
       <x:c r="C130" s="19"/>
       <x:c r="D130" s="19"/>
       <x:c r="E130" s="17"/>
+      <x:c r="F130" s="28"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="18"/>
@@ -1297,6 +1456,7 @@
       <x:c r="C131" s="19"/>
       <x:c r="D131" s="19"/>
       <x:c r="E131" s="17"/>
+      <x:c r="F131" s="28"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="18"/>
@@ -1304,6 +1464,7 @@
       <x:c r="C132" s="19"/>
       <x:c r="D132" s="19"/>
       <x:c r="E132" s="17"/>
+      <x:c r="F132" s="28"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="18"/>
@@ -1311,6 +1472,7 @@
       <x:c r="C133" s="19"/>
       <x:c r="D133" s="19"/>
       <x:c r="E133" s="17"/>
+      <x:c r="F133" s="28"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="18"/>
@@ -1318,6 +1480,7 @@
       <x:c r="C134" s="19"/>
       <x:c r="D134" s="19"/>
       <x:c r="E134" s="17"/>
+      <x:c r="F134" s="28"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="18"/>
@@ -1325,6 +1488,7 @@
       <x:c r="C135" s="19"/>
       <x:c r="D135" s="19"/>
       <x:c r="E135" s="17"/>
+      <x:c r="F135" s="28"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="18"/>
@@ -1332,6 +1496,7 @@
       <x:c r="C136" s="19"/>
       <x:c r="D136" s="19"/>
       <x:c r="E136" s="17"/>
+      <x:c r="F136" s="28"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="18"/>
@@ -1339,6 +1504,7 @@
       <x:c r="C137" s="19"/>
       <x:c r="D137" s="19"/>
       <x:c r="E137" s="17"/>
+      <x:c r="F137" s="28"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="18"/>
@@ -1346,6 +1512,7 @@
       <x:c r="C138" s="19"/>
       <x:c r="D138" s="19"/>
       <x:c r="E138" s="17"/>
+      <x:c r="F138" s="28"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="18"/>
@@ -1353,6 +1520,7 @@
       <x:c r="C139" s="19"/>
       <x:c r="D139" s="19"/>
       <x:c r="E139" s="17"/>
+      <x:c r="F139" s="28"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="18"/>
@@ -1360,6 +1528,7 @@
       <x:c r="C140" s="19"/>
       <x:c r="D140" s="19"/>
       <x:c r="E140" s="17"/>
+      <x:c r="F140" s="28"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="18"/>
@@ -1367,6 +1536,7 @@
       <x:c r="C141" s="19"/>
       <x:c r="D141" s="19"/>
       <x:c r="E141" s="17"/>
+      <x:c r="F141" s="28"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="18"/>
@@ -1374,6 +1544,7 @@
       <x:c r="C142" s="19"/>
       <x:c r="D142" s="19"/>
       <x:c r="E142" s="17"/>
+      <x:c r="F142" s="28"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="18"/>
@@ -1381,6 +1552,7 @@
       <x:c r="C143" s="19"/>
       <x:c r="D143" s="19"/>
       <x:c r="E143" s="17"/>
+      <x:c r="F143" s="28"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="18"/>
@@ -1388,6 +1560,7 @@
       <x:c r="C144" s="19"/>
       <x:c r="D144" s="19"/>
       <x:c r="E144" s="17"/>
+      <x:c r="F144" s="28"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="18"/>
@@ -1395,6 +1568,7 @@
       <x:c r="C145" s="19"/>
       <x:c r="D145" s="19"/>
       <x:c r="E145" s="17"/>
+      <x:c r="F145" s="28"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="18"/>
@@ -1402,6 +1576,7 @@
       <x:c r="C146" s="19"/>
       <x:c r="D146" s="19"/>
       <x:c r="E146" s="17"/>
+      <x:c r="F146" s="28"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="18"/>
@@ -1409,6 +1584,7 @@
       <x:c r="C147" s="19"/>
       <x:c r="D147" s="19"/>
       <x:c r="E147" s="17"/>
+      <x:c r="F147" s="28"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="18"/>
@@ -1416,6 +1592,7 @@
       <x:c r="C148" s="19"/>
       <x:c r="D148" s="19"/>
       <x:c r="E148" s="17"/>
+      <x:c r="F148" s="28"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="18"/>
@@ -1423,6 +1600,7 @@
       <x:c r="C149" s="19"/>
       <x:c r="D149" s="19"/>
       <x:c r="E149" s="17"/>
+      <x:c r="F149" s="28"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="18"/>
@@ -1430,6 +1608,7 @@
       <x:c r="C150" s="19"/>
       <x:c r="D150" s="19"/>
       <x:c r="E150" s="17"/>
+      <x:c r="F150" s="28"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="18"/>
@@ -1437,6 +1616,7 @@
       <x:c r="C151" s="19"/>
       <x:c r="D151" s="19"/>
       <x:c r="E151" s="17"/>
+      <x:c r="F151" s="28"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="18"/>
@@ -1444,6 +1624,7 @@
       <x:c r="C152" s="19"/>
       <x:c r="D152" s="19"/>
       <x:c r="E152" s="17"/>
+      <x:c r="F152" s="28"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="18"/>
@@ -1451,6 +1632,7 @@
       <x:c r="C153" s="19"/>
       <x:c r="D153" s="19"/>
       <x:c r="E153" s="17"/>
+      <x:c r="F153" s="28"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="18"/>
@@ -1458,6 +1640,7 @@
       <x:c r="C154" s="19"/>
       <x:c r="D154" s="19"/>
       <x:c r="E154" s="17"/>
+      <x:c r="F154" s="28"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="18"/>
@@ -1465,6 +1648,7 @@
       <x:c r="C155" s="19"/>
       <x:c r="D155" s="19"/>
       <x:c r="E155" s="17"/>
+      <x:c r="F155" s="28"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="18"/>
@@ -1472,6 +1656,7 @@
       <x:c r="C156" s="19"/>
       <x:c r="D156" s="19"/>
       <x:c r="E156" s="17"/>
+      <x:c r="F156" s="28"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="18"/>
@@ -1479,6 +1664,7 @@
       <x:c r="C157" s="19"/>
       <x:c r="D157" s="19"/>
       <x:c r="E157" s="17"/>
+      <x:c r="F157" s="28"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="18"/>
@@ -1486,6 +1672,7 @@
       <x:c r="C158" s="19"/>
       <x:c r="D158" s="19"/>
       <x:c r="E158" s="17"/>
+      <x:c r="F158" s="28"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="18"/>
@@ -1493,6 +1680,7 @@
       <x:c r="C159" s="19"/>
       <x:c r="D159" s="19"/>
       <x:c r="E159" s="17"/>
+      <x:c r="F159" s="28"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="18"/>
@@ -1500,6 +1688,7 @@
       <x:c r="C160" s="19"/>
       <x:c r="D160" s="19"/>
       <x:c r="E160" s="17"/>
+      <x:c r="F160" s="28"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="18"/>
@@ -1507,6 +1696,7 @@
       <x:c r="C161" s="19"/>
       <x:c r="D161" s="19"/>
       <x:c r="E161" s="17"/>
+      <x:c r="F161" s="28"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="18"/>
@@ -1514,6 +1704,7 @@
       <x:c r="C162" s="19"/>
       <x:c r="D162" s="19"/>
       <x:c r="E162" s="17"/>
+      <x:c r="F162" s="28"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="18"/>
@@ -1521,6 +1712,7 @@
       <x:c r="C163" s="19"/>
       <x:c r="D163" s="19"/>
       <x:c r="E163" s="17"/>
+      <x:c r="F163" s="28"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="18"/>
@@ -1528,6 +1720,7 @@
       <x:c r="C164" s="19"/>
       <x:c r="D164" s="19"/>
       <x:c r="E164" s="17"/>
+      <x:c r="F164" s="28"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="18"/>
@@ -1535,6 +1728,7 @@
       <x:c r="C165" s="19"/>
       <x:c r="D165" s="19"/>
       <x:c r="E165" s="17"/>
+      <x:c r="F165" s="28"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="18"/>
@@ -1542,6 +1736,7 @@
       <x:c r="C166" s="19"/>
       <x:c r="D166" s="19"/>
       <x:c r="E166" s="17"/>
+      <x:c r="F166" s="28"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="18"/>
@@ -1549,6 +1744,7 @@
       <x:c r="C167" s="19"/>
       <x:c r="D167" s="19"/>
       <x:c r="E167" s="17"/>
+      <x:c r="F167" s="28"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="18"/>
@@ -1556,6 +1752,7 @@
       <x:c r="C168" s="19"/>
       <x:c r="D168" s="19"/>
       <x:c r="E168" s="17"/>
+      <x:c r="F168" s="28"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="18"/>
@@ -1563,6 +1760,7 @@
       <x:c r="C169" s="19"/>
       <x:c r="D169" s="19"/>
       <x:c r="E169" s="17"/>
+      <x:c r="F169" s="28"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="18"/>
@@ -1570,6 +1768,7 @@
       <x:c r="C170" s="19"/>
       <x:c r="D170" s="19"/>
       <x:c r="E170" s="17"/>
+      <x:c r="F170" s="28"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="18"/>
@@ -1577,6 +1776,7 @@
       <x:c r="C171" s="19"/>
       <x:c r="D171" s="19"/>
       <x:c r="E171" s="17"/>
+      <x:c r="F171" s="28"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="18"/>
@@ -1584,6 +1784,7 @@
       <x:c r="C172" s="19"/>
       <x:c r="D172" s="19"/>
       <x:c r="E172" s="17"/>
+      <x:c r="F172" s="28"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="18"/>
@@ -1591,6 +1792,7 @@
       <x:c r="C173" s="19"/>
       <x:c r="D173" s="19"/>
       <x:c r="E173" s="17"/>
+      <x:c r="F173" s="28"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="18"/>
@@ -1598,6 +1800,7 @@
       <x:c r="C174" s="19"/>
       <x:c r="D174" s="19"/>
       <x:c r="E174" s="17"/>
+      <x:c r="F174" s="28"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="18"/>
@@ -1605,6 +1808,7 @@
       <x:c r="C175" s="19"/>
       <x:c r="D175" s="19"/>
       <x:c r="E175" s="17"/>
+      <x:c r="F175" s="28"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="18"/>
@@ -1612,6 +1816,7 @@
       <x:c r="C176" s="19"/>
       <x:c r="D176" s="19"/>
       <x:c r="E176" s="17"/>
+      <x:c r="F176" s="28"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="18"/>
@@ -1619,6 +1824,7 @@
       <x:c r="C177" s="19"/>
       <x:c r="D177" s="19"/>
       <x:c r="E177" s="17"/>
+      <x:c r="F177" s="28"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="18"/>
@@ -1626,6 +1832,7 @@
       <x:c r="C178" s="19"/>
       <x:c r="D178" s="19"/>
       <x:c r="E178" s="17"/>
+      <x:c r="F178" s="28"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="18"/>
@@ -1633,6 +1840,7 @@
       <x:c r="C179" s="19"/>
       <x:c r="D179" s="19"/>
       <x:c r="E179" s="17"/>
+      <x:c r="F179" s="28"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="18"/>
@@ -1640,6 +1848,7 @@
       <x:c r="C180" s="19"/>
       <x:c r="D180" s="19"/>
       <x:c r="E180" s="17"/>
+      <x:c r="F180" s="28"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="18"/>
@@ -1647,6 +1856,7 @@
       <x:c r="C181" s="19"/>
       <x:c r="D181" s="19"/>
       <x:c r="E181" s="17"/>
+      <x:c r="F181" s="28"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="18"/>
@@ -1654,6 +1864,7 @@
       <x:c r="C182" s="19"/>
       <x:c r="D182" s="19"/>
       <x:c r="E182" s="17"/>
+      <x:c r="F182" s="28"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="18"/>
@@ -1661,6 +1872,7 @@
       <x:c r="C183" s="19"/>
       <x:c r="D183" s="19"/>
       <x:c r="E183" s="17"/>
+      <x:c r="F183" s="28"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="18"/>
@@ -1668,6 +1880,7 @@
       <x:c r="C184" s="19"/>
       <x:c r="D184" s="19"/>
       <x:c r="E184" s="17"/>
+      <x:c r="F184" s="28"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="18"/>
@@ -1675,6 +1888,7 @@
       <x:c r="C185" s="19"/>
       <x:c r="D185" s="19"/>
       <x:c r="E185" s="17"/>
+      <x:c r="F185" s="28"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="18"/>
@@ -1682,6 +1896,7 @@
       <x:c r="C186" s="19"/>
       <x:c r="D186" s="19"/>
       <x:c r="E186" s="17"/>
+      <x:c r="F186" s="28"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="18"/>
@@ -1689,6 +1904,7 @@
       <x:c r="C187" s="19"/>
       <x:c r="D187" s="19"/>
       <x:c r="E187" s="17"/>
+      <x:c r="F187" s="28"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="18"/>
@@ -1696,6 +1912,7 @@
       <x:c r="C188" s="19"/>
       <x:c r="D188" s="19"/>
       <x:c r="E188" s="17"/>
+      <x:c r="F188" s="28"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="18"/>
@@ -1703,6 +1920,7 @@
       <x:c r="C189" s="19"/>
       <x:c r="D189" s="19"/>
       <x:c r="E189" s="17"/>
+      <x:c r="F189" s="28"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="18"/>
@@ -1710,6 +1928,7 @@
       <x:c r="C190" s="19"/>
       <x:c r="D190" s="19"/>
       <x:c r="E190" s="17"/>
+      <x:c r="F190" s="28"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="18"/>
@@ -1717,6 +1936,7 @@
       <x:c r="C191" s="19"/>
       <x:c r="D191" s="19"/>
       <x:c r="E191" s="17"/>
+      <x:c r="F191" s="28"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="18"/>
@@ -1724,6 +1944,7 @@
       <x:c r="C192" s="19"/>
       <x:c r="D192" s="19"/>
       <x:c r="E192" s="17"/>
+      <x:c r="F192" s="28"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="18"/>
@@ -1731,6 +1952,7 @@
       <x:c r="C193" s="19"/>
       <x:c r="D193" s="19"/>
       <x:c r="E193" s="17"/>
+      <x:c r="F193" s="28"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="18"/>
@@ -1738,6 +1960,7 @@
       <x:c r="C194" s="19"/>
       <x:c r="D194" s="19"/>
       <x:c r="E194" s="17"/>
+      <x:c r="F194" s="28"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="18"/>
@@ -1745,6 +1968,7 @@
       <x:c r="C195" s="19"/>
       <x:c r="D195" s="19"/>
       <x:c r="E195" s="17"/>
+      <x:c r="F195" s="28"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="18"/>
@@ -1752,6 +1976,7 @@
       <x:c r="C196" s="19"/>
       <x:c r="D196" s="19"/>
       <x:c r="E196" s="17"/>
+      <x:c r="F196" s="28"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="18"/>
@@ -1759,6 +1984,7 @@
       <x:c r="C197" s="19"/>
       <x:c r="D197" s="19"/>
       <x:c r="E197" s="17"/>
+      <x:c r="F197" s="28"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="18"/>
@@ -1766,6 +1992,7 @@
       <x:c r="C198" s="19"/>
       <x:c r="D198" s="19"/>
       <x:c r="E198" s="17"/>
+      <x:c r="F198" s="28"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="18"/>
@@ -1773,6 +2000,7 @@
       <x:c r="C199" s="19"/>
       <x:c r="D199" s="19"/>
       <x:c r="E199" s="17"/>
+      <x:c r="F199" s="28"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="18"/>
@@ -1780,6 +2008,7 @@
       <x:c r="C200" s="19"/>
       <x:c r="D200" s="19"/>
       <x:c r="E200" s="17"/>
+      <x:c r="F200" s="28"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="18"/>
@@ -1787,6 +2016,7 @@
       <x:c r="C201" s="19"/>
       <x:c r="D201" s="19"/>
       <x:c r="E201" s="17"/>
+      <x:c r="F201" s="28"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="18"/>
@@ -1794,6 +2024,7 @@
       <x:c r="C202" s="19"/>
       <x:c r="D202" s="19"/>
       <x:c r="E202" s="17"/>
+      <x:c r="F202" s="28"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="18"/>
@@ -1801,6 +2032,7 @@
       <x:c r="C203" s="19"/>
       <x:c r="D203" s="19"/>
       <x:c r="E203" s="17"/>
+      <x:c r="F203" s="28"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="18"/>
@@ -1808,6 +2040,7 @@
       <x:c r="C204" s="19"/>
       <x:c r="D204" s="19"/>
       <x:c r="E204" s="17"/>
+      <x:c r="F204" s="28"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="18"/>
@@ -1815,6 +2048,7 @@
       <x:c r="C205" s="19"/>
       <x:c r="D205" s="19"/>
       <x:c r="E205" s="17"/>
+      <x:c r="F205" s="28"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="18"/>
@@ -1822,6 +2056,7 @@
       <x:c r="C206" s="19"/>
       <x:c r="D206" s="19"/>
       <x:c r="E206" s="17"/>
+      <x:c r="F206" s="28"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="18"/>
@@ -1829,6 +2064,7 @@
       <x:c r="C207" s="19"/>
       <x:c r="D207" s="19"/>
       <x:c r="E207" s="17"/>
+      <x:c r="F207" s="28"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="18"/>
@@ -1836,6 +2072,7 @@
       <x:c r="C208" s="19"/>
       <x:c r="D208" s="19"/>
       <x:c r="E208" s="17"/>
+      <x:c r="F208" s="28"/>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="18"/>
@@ -1843,6 +2080,7 @@
       <x:c r="C209" s="19"/>
       <x:c r="D209" s="19"/>
       <x:c r="E209" s="17"/>
+      <x:c r="F209" s="28"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="18"/>
@@ -1850,6 +2088,7 @@
       <x:c r="C210" s="19"/>
       <x:c r="D210" s="19"/>
       <x:c r="E210" s="17"/>
+      <x:c r="F210" s="28"/>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="18"/>
@@ -1857,6 +2096,7 @@
       <x:c r="C211" s="19"/>
       <x:c r="D211" s="19"/>
       <x:c r="E211" s="17"/>
+      <x:c r="F211" s="28"/>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="18"/>
@@ -1864,6 +2104,7 @@
       <x:c r="C212" s="19"/>
       <x:c r="D212" s="19"/>
       <x:c r="E212" s="17"/>
+      <x:c r="F212" s="28"/>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="18"/>
@@ -1871,6 +2112,7 @@
       <x:c r="C213" s="19"/>
       <x:c r="D213" s="19"/>
       <x:c r="E213" s="17"/>
+      <x:c r="F213" s="28"/>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="18"/>
@@ -1878,6 +2120,7 @@
       <x:c r="C214" s="19"/>
       <x:c r="D214" s="19"/>
       <x:c r="E214" s="17"/>
+      <x:c r="F214" s="28"/>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="18"/>
@@ -1885,6 +2128,7 @@
       <x:c r="C215" s="19"/>
       <x:c r="D215" s="19"/>
       <x:c r="E215" s="17"/>
+      <x:c r="F215" s="28"/>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="18"/>
@@ -1892,6 +2136,7 @@
       <x:c r="C216" s="19"/>
       <x:c r="D216" s="19"/>
       <x:c r="E216" s="17"/>
+      <x:c r="F216" s="28"/>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="18"/>
@@ -1899,6 +2144,7 @@
       <x:c r="C217" s="19"/>
       <x:c r="D217" s="19"/>
       <x:c r="E217" s="17"/>
+      <x:c r="F217" s="28"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="18"/>
@@ -1906,6 +2152,7 @@
       <x:c r="C218" s="19"/>
       <x:c r="D218" s="19"/>
       <x:c r="E218" s="17"/>
+      <x:c r="F218" s="28"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="18"/>
@@ -1913,6 +2160,7 @@
       <x:c r="C219" s="19"/>
       <x:c r="D219" s="19"/>
       <x:c r="E219" s="17"/>
+      <x:c r="F219" s="28"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="18"/>
@@ -1920,6 +2168,7 @@
       <x:c r="C220" s="19"/>
       <x:c r="D220" s="19"/>
       <x:c r="E220" s="17"/>
+      <x:c r="F220" s="28"/>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="18"/>
@@ -1927,6 +2176,7 @@
       <x:c r="C221" s="19"/>
       <x:c r="D221" s="19"/>
       <x:c r="E221" s="17"/>
+      <x:c r="F221" s="28"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="18"/>
@@ -1934,6 +2184,7 @@
       <x:c r="C222" s="19"/>
       <x:c r="D222" s="19"/>
       <x:c r="E222" s="17"/>
+      <x:c r="F222" s="28"/>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="18"/>
@@ -1941,6 +2192,7 @@
       <x:c r="C223" s="19"/>
       <x:c r="D223" s="19"/>
       <x:c r="E223" s="17"/>
+      <x:c r="F223" s="28"/>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="18"/>
@@ -1948,6 +2200,7 @@
       <x:c r="C224" s="19"/>
       <x:c r="D224" s="19"/>
       <x:c r="E224" s="17"/>
+      <x:c r="F224" s="28"/>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="18"/>
@@ -1955,6 +2208,7 @@
       <x:c r="C225" s="19"/>
       <x:c r="D225" s="19"/>
       <x:c r="E225" s="17"/>
+      <x:c r="F225" s="28"/>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="18"/>
@@ -1962,6 +2216,7 @@
       <x:c r="C226" s="19"/>
       <x:c r="D226" s="19"/>
       <x:c r="E226" s="17"/>
+      <x:c r="F226" s="28"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="18"/>
@@ -1969,6 +2224,7 @@
       <x:c r="C227" s="19"/>
       <x:c r="D227" s="19"/>
       <x:c r="E227" s="17"/>
+      <x:c r="F227" s="28"/>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="18"/>
@@ -1976,6 +2232,7 @@
       <x:c r="C228" s="19"/>
       <x:c r="D228" s="19"/>
       <x:c r="E228" s="17"/>
+      <x:c r="F228" s="28"/>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="18"/>
@@ -1983,6 +2240,7 @@
       <x:c r="C229" s="19"/>
       <x:c r="D229" s="19"/>
       <x:c r="E229" s="17"/>
+      <x:c r="F229" s="28"/>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="18"/>
@@ -1990,6 +2248,7 @@
       <x:c r="C230" s="19"/>
       <x:c r="D230" s="19"/>
       <x:c r="E230" s="17"/>
+      <x:c r="F230" s="28"/>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="18"/>
@@ -1997,6 +2256,7 @@
       <x:c r="C231" s="19"/>
       <x:c r="D231" s="19"/>
       <x:c r="E231" s="17"/>
+      <x:c r="F231" s="28"/>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="18"/>
@@ -2004,6 +2264,7 @@
       <x:c r="C232" s="19"/>
       <x:c r="D232" s="19"/>
       <x:c r="E232" s="17"/>
+      <x:c r="F232" s="28"/>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="18"/>
@@ -2011,6 +2272,7 @@
       <x:c r="C233" s="19"/>
       <x:c r="D233" s="19"/>
       <x:c r="E233" s="17"/>
+      <x:c r="F233" s="28"/>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="18"/>
@@ -2018,6 +2280,7 @@
       <x:c r="C234" s="19"/>
       <x:c r="D234" s="19"/>
       <x:c r="E234" s="17"/>
+      <x:c r="F234" s="28"/>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="18"/>
@@ -2025,6 +2288,7 @@
       <x:c r="C235" s="19"/>
       <x:c r="D235" s="19"/>
       <x:c r="E235" s="17"/>
+      <x:c r="F235" s="28"/>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="18"/>
@@ -2032,6 +2296,7 @@
       <x:c r="C236" s="19"/>
       <x:c r="D236" s="19"/>
       <x:c r="E236" s="17"/>
+      <x:c r="F236" s="28"/>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="18"/>
@@ -2039,6 +2304,7 @@
       <x:c r="C237" s="19"/>
       <x:c r="D237" s="19"/>
       <x:c r="E237" s="17"/>
+      <x:c r="F237" s="28"/>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="18"/>
@@ -2046,6 +2312,7 @@
       <x:c r="C238" s="19"/>
       <x:c r="D238" s="19"/>
       <x:c r="E238" s="17"/>
+      <x:c r="F238" s="28"/>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="18"/>
@@ -2053,6 +2320,7 @@
       <x:c r="C239" s="19"/>
       <x:c r="D239" s="19"/>
       <x:c r="E239" s="17"/>
+      <x:c r="F239" s="28"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="18"/>
@@ -2060,6 +2328,7 @@
       <x:c r="C240" s="19"/>
       <x:c r="D240" s="19"/>
       <x:c r="E240" s="17"/>
+      <x:c r="F240" s="28"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="18"/>
@@ -2067,6 +2336,7 @@
       <x:c r="C241" s="19"/>
       <x:c r="D241" s="19"/>
       <x:c r="E241" s="17"/>
+      <x:c r="F241" s="28"/>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="18"/>
@@ -2074,6 +2344,7 @@
       <x:c r="C242" s="19"/>
       <x:c r="D242" s="19"/>
       <x:c r="E242" s="17"/>
+      <x:c r="F242" s="28"/>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="18"/>
@@ -2081,6 +2352,7 @@
       <x:c r="C243" s="19"/>
       <x:c r="D243" s="19"/>
       <x:c r="E243" s="17"/>
+      <x:c r="F243" s="28"/>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="18"/>
@@ -2088,6 +2360,7 @@
       <x:c r="C244" s="19"/>
       <x:c r="D244" s="19"/>
       <x:c r="E244" s="17"/>
+      <x:c r="F244" s="28"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="18"/>
@@ -2095,6 +2368,7 @@
       <x:c r="C245" s="19"/>
       <x:c r="D245" s="19"/>
       <x:c r="E245" s="17"/>
+      <x:c r="F245" s="28"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="18"/>
@@ -2102,6 +2376,7 @@
       <x:c r="C246" s="19"/>
       <x:c r="D246" s="19"/>
       <x:c r="E246" s="17"/>
+      <x:c r="F246" s="28"/>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="18"/>
@@ -2109,6 +2384,7 @@
       <x:c r="C247" s="19"/>
       <x:c r="D247" s="19"/>
       <x:c r="E247" s="17"/>
+      <x:c r="F247" s="28"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="18"/>
@@ -2116,6 +2392,7 @@
       <x:c r="C248" s="19"/>
       <x:c r="D248" s="19"/>
       <x:c r="E248" s="17"/>
+      <x:c r="F248" s="28"/>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="18"/>
@@ -2123,6 +2400,7 @@
       <x:c r="C249" s="19"/>
       <x:c r="D249" s="19"/>
       <x:c r="E249" s="17"/>
+      <x:c r="F249" s="28"/>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="18"/>
@@ -2130,6 +2408,7 @@
       <x:c r="C250" s="19"/>
       <x:c r="D250" s="19"/>
       <x:c r="E250" s="17"/>
+      <x:c r="F250" s="28"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="18"/>
@@ -2137,6 +2416,7 @@
       <x:c r="C251" s="19"/>
       <x:c r="D251" s="19"/>
       <x:c r="E251" s="17"/>
+      <x:c r="F251" s="28"/>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="18"/>
@@ -2144,6 +2424,7 @@
       <x:c r="C252" s="19"/>
       <x:c r="D252" s="19"/>
       <x:c r="E252" s="17"/>
+      <x:c r="F252" s="28"/>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="18"/>
@@ -2151,6 +2432,7 @@
       <x:c r="C253" s="19"/>
       <x:c r="D253" s="19"/>
       <x:c r="E253" s="17"/>
+      <x:c r="F253" s="28"/>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="18"/>
@@ -2158,6 +2440,7 @@
       <x:c r="C254" s="19"/>
       <x:c r="D254" s="19"/>
       <x:c r="E254" s="17"/>
+      <x:c r="F254" s="28"/>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="18"/>
@@ -2165,6 +2448,7 @@
       <x:c r="C255" s="19"/>
       <x:c r="D255" s="19"/>
       <x:c r="E255" s="17"/>
+      <x:c r="F255" s="28"/>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="18"/>
@@ -2172,6 +2456,7 @@
       <x:c r="C256" s="19"/>
       <x:c r="D256" s="19"/>
       <x:c r="E256" s="17"/>
+      <x:c r="F256" s="28"/>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="18"/>
@@ -2179,6 +2464,7 @@
       <x:c r="C257" s="19"/>
       <x:c r="D257" s="19"/>
       <x:c r="E257" s="17"/>
+      <x:c r="F257" s="28"/>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="18"/>
@@ -2186,6 +2472,7 @@
       <x:c r="C258" s="19"/>
       <x:c r="D258" s="19"/>
       <x:c r="E258" s="17"/>
+      <x:c r="F258" s="28"/>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="18"/>
@@ -2193,6 +2480,7 @@
       <x:c r="C259" s="19"/>
       <x:c r="D259" s="19"/>
       <x:c r="E259" s="17"/>
+      <x:c r="F259" s="28"/>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="18"/>
@@ -2200,6 +2488,7 @@
       <x:c r="C260" s="19"/>
       <x:c r="D260" s="19"/>
       <x:c r="E260" s="17"/>
+      <x:c r="F260" s="28"/>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="18"/>
@@ -2207,6 +2496,7 @@
       <x:c r="C261" s="19"/>
       <x:c r="D261" s="19"/>
       <x:c r="E261" s="17"/>
+      <x:c r="F261" s="28"/>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="18"/>
@@ -2214,6 +2504,7 @@
       <x:c r="C262" s="19"/>
       <x:c r="D262" s="19"/>
       <x:c r="E262" s="17"/>
+      <x:c r="F262" s="28"/>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="18"/>
@@ -2221,6 +2512,7 @@
       <x:c r="C263" s="19"/>
       <x:c r="D263" s="19"/>
       <x:c r="E263" s="17"/>
+      <x:c r="F263" s="28"/>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="18"/>
@@ -2228,6 +2520,7 @@
       <x:c r="C264" s="19"/>
       <x:c r="D264" s="19"/>
       <x:c r="E264" s="17"/>
+      <x:c r="F264" s="28"/>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="18"/>
@@ -2235,6 +2528,7 @@
       <x:c r="C265" s="19"/>
       <x:c r="D265" s="19"/>
       <x:c r="E265" s="17"/>
+      <x:c r="F265" s="28"/>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="18"/>
@@ -2242,6 +2536,7 @@
       <x:c r="C266" s="19"/>
       <x:c r="D266" s="19"/>
       <x:c r="E266" s="17"/>
+      <x:c r="F266" s="28"/>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="18"/>
@@ -2249,6 +2544,7 @@
       <x:c r="C267" s="19"/>
       <x:c r="D267" s="19"/>
       <x:c r="E267" s="17"/>
+      <x:c r="F267" s="28"/>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="18"/>
@@ -2256,6 +2552,7 @@
       <x:c r="C268" s="19"/>
       <x:c r="D268" s="19"/>
       <x:c r="E268" s="17"/>
+      <x:c r="F268" s="28"/>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="18"/>
@@ -2263,6 +2560,7 @@
       <x:c r="C269" s="19"/>
       <x:c r="D269" s="19"/>
       <x:c r="E269" s="17"/>
+      <x:c r="F269" s="28"/>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="18"/>
@@ -2270,6 +2568,7 @@
       <x:c r="C270" s="19"/>
       <x:c r="D270" s="19"/>
       <x:c r="E270" s="17"/>
+      <x:c r="F270" s="28"/>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="18"/>
@@ -2277,6 +2576,7 @@
       <x:c r="C271" s="19"/>
       <x:c r="D271" s="19"/>
       <x:c r="E271" s="17"/>
+      <x:c r="F271" s="28"/>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="18"/>
@@ -2284,6 +2584,7 @@
       <x:c r="C272" s="19"/>
       <x:c r="D272" s="19"/>
       <x:c r="E272" s="17"/>
+      <x:c r="F272" s="28"/>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="18"/>
@@ -2291,6 +2592,7 @@
       <x:c r="C273" s="19"/>
       <x:c r="D273" s="19"/>
       <x:c r="E273" s="17"/>
+      <x:c r="F273" s="28"/>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="18"/>
@@ -2298,6 +2600,7 @@
       <x:c r="C274" s="19"/>
       <x:c r="D274" s="19"/>
       <x:c r="E274" s="17"/>
+      <x:c r="F274" s="28"/>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="18"/>
@@ -2305,6 +2608,7 @@
       <x:c r="C275" s="19"/>
       <x:c r="D275" s="19"/>
       <x:c r="E275" s="17"/>
+      <x:c r="F275" s="28"/>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="18"/>
@@ -2312,6 +2616,7 @@
       <x:c r="C276" s="19"/>
       <x:c r="D276" s="19"/>
       <x:c r="E276" s="17"/>
+      <x:c r="F276" s="28"/>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="18"/>
@@ -2319,6 +2624,7 @@
       <x:c r="C277" s="19"/>
       <x:c r="D277" s="19"/>
       <x:c r="E277" s="17"/>
+      <x:c r="F277" s="28"/>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="18"/>
@@ -2326,6 +2632,7 @@
       <x:c r="C278" s="19"/>
       <x:c r="D278" s="19"/>
       <x:c r="E278" s="17"/>
+      <x:c r="F278" s="28"/>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="18"/>
@@ -2333,6 +2640,7 @@
       <x:c r="C279" s="19"/>
       <x:c r="D279" s="19"/>
       <x:c r="E279" s="17"/>
+      <x:c r="F279" s="28"/>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="18"/>
@@ -2340,6 +2648,7 @@
       <x:c r="C280" s="19"/>
       <x:c r="D280" s="19"/>
       <x:c r="E280" s="17"/>
+      <x:c r="F280" s="28"/>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="18"/>
@@ -2347,6 +2656,7 @@
       <x:c r="C281" s="19"/>
       <x:c r="D281" s="19"/>
       <x:c r="E281" s="17"/>
+      <x:c r="F281" s="28"/>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="18"/>
@@ -2354,6 +2664,7 @@
       <x:c r="C282" s="19"/>
       <x:c r="D282" s="19"/>
       <x:c r="E282" s="17"/>
+      <x:c r="F282" s="28"/>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="18"/>
@@ -2361,6 +2672,7 @@
       <x:c r="C283" s="19"/>
       <x:c r="D283" s="19"/>
       <x:c r="E283" s="17"/>
+      <x:c r="F283" s="28"/>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="18"/>
@@ -2368,6 +2680,7 @@
       <x:c r="C284" s="19"/>
       <x:c r="D284" s="19"/>
       <x:c r="E284" s="17"/>
+      <x:c r="F284" s="28"/>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="18"/>
@@ -2375,6 +2688,7 @@
       <x:c r="C285" s="19"/>
       <x:c r="D285" s="19"/>
       <x:c r="E285" s="17"/>
+      <x:c r="F285" s="28"/>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="18"/>
@@ -2382,6 +2696,7 @@
       <x:c r="C286" s="19"/>
       <x:c r="D286" s="19"/>
       <x:c r="E286" s="17"/>
+      <x:c r="F286" s="28"/>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="18"/>
@@ -2389,6 +2704,7 @@
       <x:c r="C287" s="19"/>
       <x:c r="D287" s="19"/>
       <x:c r="E287" s="17"/>
+      <x:c r="F287" s="28"/>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="18"/>
@@ -2396,6 +2712,7 @@
       <x:c r="C288" s="19"/>
       <x:c r="D288" s="19"/>
       <x:c r="E288" s="17"/>
+      <x:c r="F288" s="28"/>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="18"/>
@@ -2403,6 +2720,7 @@
       <x:c r="C289" s="19"/>
       <x:c r="D289" s="19"/>
       <x:c r="E289" s="17"/>
+      <x:c r="F289" s="28"/>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="18"/>
@@ -2410,6 +2728,7 @@
       <x:c r="C290" s="19"/>
       <x:c r="D290" s="19"/>
       <x:c r="E290" s="17"/>
+      <x:c r="F290" s="28"/>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="18"/>
@@ -2417,6 +2736,7 @@
       <x:c r="C291" s="19"/>
       <x:c r="D291" s="19"/>
       <x:c r="E291" s="17"/>
+      <x:c r="F291" s="28"/>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="18"/>
@@ -2424,6 +2744,7 @@
       <x:c r="C292" s="19"/>
       <x:c r="D292" s="19"/>
       <x:c r="E292" s="17"/>
+      <x:c r="F292" s="28"/>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="18"/>
@@ -2431,6 +2752,7 @@
       <x:c r="C293" s="19"/>
       <x:c r="D293" s="19"/>
       <x:c r="E293" s="17"/>
+      <x:c r="F293" s="28"/>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="18"/>
@@ -2438,6 +2760,7 @@
       <x:c r="C294" s="19"/>
       <x:c r="D294" s="19"/>
       <x:c r="E294" s="17"/>
+      <x:c r="F294" s="28"/>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="18"/>
@@ -2445,6 +2768,7 @@
       <x:c r="C295" s="19"/>
       <x:c r="D295" s="19"/>
       <x:c r="E295" s="17"/>
+      <x:c r="F295" s="28"/>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="18"/>
@@ -2452,6 +2776,7 @@
       <x:c r="C296" s="19"/>
       <x:c r="D296" s="19"/>
       <x:c r="E296" s="17"/>
+      <x:c r="F296" s="28"/>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="18"/>
@@ -2459,6 +2784,7 @@
       <x:c r="C297" s="19"/>
       <x:c r="D297" s="19"/>
       <x:c r="E297" s="17"/>
+      <x:c r="F297" s="28"/>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="18"/>
@@ -2466,6 +2792,7 @@
       <x:c r="C298" s="19"/>
       <x:c r="D298" s="19"/>
       <x:c r="E298" s="17"/>
+      <x:c r="F298" s="28"/>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="18"/>
@@ -2473,6 +2800,7 @@
       <x:c r="C299" s="19"/>
       <x:c r="D299" s="19"/>
       <x:c r="E299" s="17"/>
+      <x:c r="F299" s="28"/>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="18"/>
@@ -2480,6 +2808,7 @@
       <x:c r="C300" s="19"/>
       <x:c r="D300" s="19"/>
       <x:c r="E300" s="17"/>
+      <x:c r="F300" s="28"/>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="18"/>
@@ -2487,6 +2816,7 @@
       <x:c r="C301" s="19"/>
       <x:c r="D301" s="19"/>
       <x:c r="E301" s="17"/>
+      <x:c r="F301" s="28"/>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="18"/>
@@ -2494,6 +2824,7 @@
       <x:c r="C302" s="19"/>
       <x:c r="D302" s="19"/>
       <x:c r="E302" s="17"/>
+      <x:c r="F302" s="28"/>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="18"/>
@@ -2501,6 +2832,7 @@
       <x:c r="C303" s="19"/>
       <x:c r="D303" s="19"/>
       <x:c r="E303" s="17"/>
+      <x:c r="F303" s="28"/>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="18"/>
@@ -2508,6 +2840,7 @@
       <x:c r="C304" s="19"/>
       <x:c r="D304" s="19"/>
       <x:c r="E304" s="17"/>
+      <x:c r="F304" s="28"/>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="18"/>
@@ -2515,6 +2848,7 @@
       <x:c r="C305" s="19"/>
       <x:c r="D305" s="19"/>
       <x:c r="E305" s="17"/>
+      <x:c r="F305" s="28"/>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="18"/>
@@ -2522,6 +2856,7 @@
       <x:c r="C306" s="19"/>
       <x:c r="D306" s="19"/>
       <x:c r="E306" s="17"/>
+      <x:c r="F306" s="28"/>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="18"/>
@@ -2529,6 +2864,7 @@
       <x:c r="C307" s="19"/>
       <x:c r="D307" s="19"/>
       <x:c r="E307" s="17"/>
+      <x:c r="F307" s="28"/>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="18"/>
@@ -2536,6 +2872,7 @@
       <x:c r="C308" s="19"/>
       <x:c r="D308" s="19"/>
       <x:c r="E308" s="17"/>
+      <x:c r="F308" s="28"/>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="18"/>
@@ -2543,6 +2880,7 @@
       <x:c r="C309" s="19"/>
       <x:c r="D309" s="19"/>
       <x:c r="E309" s="17"/>
+      <x:c r="F309" s="28"/>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="18"/>
@@ -2550,6 +2888,7 @@
       <x:c r="C310" s="19"/>
       <x:c r="D310" s="19"/>
       <x:c r="E310" s="17"/>
+      <x:c r="F310" s="28"/>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="18"/>
@@ -2557,6 +2896,7 @@
       <x:c r="C311" s="19"/>
       <x:c r="D311" s="19"/>
       <x:c r="E311" s="17"/>
+      <x:c r="F311" s="28"/>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="18"/>
@@ -2564,6 +2904,7 @@
       <x:c r="C312" s="19"/>
       <x:c r="D312" s="19"/>
       <x:c r="E312" s="17"/>
+      <x:c r="F312" s="28"/>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="18"/>
@@ -2571,6 +2912,7 @@
       <x:c r="C313" s="19"/>
       <x:c r="D313" s="19"/>
       <x:c r="E313" s="17"/>
+      <x:c r="F313" s="28"/>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="18"/>
@@ -2578,6 +2920,7 @@
       <x:c r="C314" s="19"/>
       <x:c r="D314" s="19"/>
       <x:c r="E314" s="17"/>
+      <x:c r="F314" s="28"/>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="18"/>
@@ -2585,6 +2928,7 @@
       <x:c r="C315" s="19"/>
       <x:c r="D315" s="19"/>
       <x:c r="E315" s="17"/>
+      <x:c r="F315" s="28"/>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="18"/>
@@ -2592,6 +2936,7 @@
       <x:c r="C316" s="19"/>
       <x:c r="D316" s="19"/>
       <x:c r="E316" s="17"/>
+      <x:c r="F316" s="28"/>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="18"/>
@@ -2599,6 +2944,7 @@
       <x:c r="C317" s="19"/>
       <x:c r="D317" s="19"/>
       <x:c r="E317" s="17"/>
+      <x:c r="F317" s="28"/>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="18"/>
@@ -2606,6 +2952,7 @@
       <x:c r="C318" s="19"/>
       <x:c r="D318" s="19"/>
       <x:c r="E318" s="17"/>
+      <x:c r="F318" s="28"/>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="18"/>
@@ -2613,6 +2960,7 @@
       <x:c r="C319" s="19"/>
       <x:c r="D319" s="19"/>
       <x:c r="E319" s="17"/>
+      <x:c r="F319" s="28"/>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="18"/>
@@ -2620,6 +2968,7 @@
       <x:c r="C320" s="19"/>
       <x:c r="D320" s="19"/>
       <x:c r="E320" s="17"/>
+      <x:c r="F320" s="28"/>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="18"/>
@@ -2627,6 +2976,7 @@
       <x:c r="C321" s="19"/>
       <x:c r="D321" s="19"/>
       <x:c r="E321" s="17"/>
+      <x:c r="F321" s="28"/>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="18"/>
@@ -2634,6 +2984,7 @@
       <x:c r="C322" s="19"/>
       <x:c r="D322" s="19"/>
       <x:c r="E322" s="17"/>
+      <x:c r="F322" s="28"/>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="18"/>
@@ -2641,6 +2992,7 @@
       <x:c r="C323" s="19"/>
       <x:c r="D323" s="19"/>
       <x:c r="E323" s="17"/>
+      <x:c r="F323" s="28"/>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="18"/>
@@ -2648,6 +3000,7 @@
       <x:c r="C324" s="19"/>
       <x:c r="D324" s="19"/>
       <x:c r="E324" s="17"/>
+      <x:c r="F324" s="28"/>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="18"/>
@@ -2655,6 +3008,7 @@
       <x:c r="C325" s="19"/>
       <x:c r="D325" s="19"/>
       <x:c r="E325" s="17"/>
+      <x:c r="F325" s="28"/>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="18"/>
@@ -2662,6 +3016,7 @@
       <x:c r="C326" s="19"/>
       <x:c r="D326" s="19"/>
       <x:c r="E326" s="17"/>
+      <x:c r="F326" s="28"/>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="18"/>
@@ -2669,6 +3024,7 @@
       <x:c r="C327" s="19"/>
       <x:c r="D327" s="19"/>
       <x:c r="E327" s="17"/>
+      <x:c r="F327" s="28"/>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="18"/>
@@ -2676,6 +3032,7 @@
       <x:c r="C328" s="19"/>
       <x:c r="D328" s="19"/>
       <x:c r="E328" s="17"/>
+      <x:c r="F328" s="28"/>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="18"/>
@@ -2683,6 +3040,7 @@
       <x:c r="C329" s="19"/>
       <x:c r="D329" s="19"/>
       <x:c r="E329" s="17"/>
+      <x:c r="F329" s="28"/>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="18"/>
@@ -2690,6 +3048,7 @@
       <x:c r="C330" s="19"/>
       <x:c r="D330" s="19"/>
       <x:c r="E330" s="17"/>
+      <x:c r="F330" s="28"/>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="18"/>
@@ -2697,6 +3056,7 @@
       <x:c r="C331" s="19"/>
       <x:c r="D331" s="19"/>
       <x:c r="E331" s="17"/>
+      <x:c r="F331" s="28"/>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="18"/>
@@ -2704,6 +3064,7 @@
       <x:c r="C332" s="19"/>
       <x:c r="D332" s="19"/>
       <x:c r="E332" s="17"/>
+      <x:c r="F332" s="28"/>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="18"/>
@@ -2711,6 +3072,7 @@
       <x:c r="C333" s="19"/>
       <x:c r="D333" s="19"/>
       <x:c r="E333" s="17"/>
+      <x:c r="F333" s="28"/>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="18"/>
@@ -2718,6 +3080,7 @@
       <x:c r="C334" s="19"/>
       <x:c r="D334" s="19"/>
       <x:c r="E334" s="17"/>
+      <x:c r="F334" s="28"/>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="18"/>
@@ -2725,6 +3088,7 @@
       <x:c r="C335" s="19"/>
       <x:c r="D335" s="19"/>
       <x:c r="E335" s="17"/>
+      <x:c r="F335" s="28"/>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="18"/>
@@ -2732,6 +3096,7 @@
       <x:c r="C336" s="19"/>
       <x:c r="D336" s="19"/>
       <x:c r="E336" s="17"/>
+      <x:c r="F336" s="28"/>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="18"/>
@@ -2739,6 +3104,7 @@
       <x:c r="C337" s="19"/>
       <x:c r="D337" s="19"/>
       <x:c r="E337" s="17"/>
+      <x:c r="F337" s="28"/>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="18"/>
@@ -2746,6 +3112,7 @@
       <x:c r="C338" s="19"/>
       <x:c r="D338" s="19"/>
       <x:c r="E338" s="17"/>
+      <x:c r="F338" s="28"/>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="18"/>
@@ -2753,6 +3120,7 @@
       <x:c r="C339" s="19"/>
       <x:c r="D339" s="19"/>
       <x:c r="E339" s="17"/>
+      <x:c r="F339" s="28"/>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="18"/>
@@ -2760,6 +3128,7 @@
       <x:c r="C340" s="19"/>
       <x:c r="D340" s="19"/>
       <x:c r="E340" s="17"/>
+      <x:c r="F340" s="28"/>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="18"/>
@@ -2767,6 +3136,7 @@
       <x:c r="C341" s="19"/>
       <x:c r="D341" s="19"/>
       <x:c r="E341" s="17"/>
+      <x:c r="F341" s="28"/>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="18"/>
@@ -2774,6 +3144,7 @@
       <x:c r="C342" s="19"/>
       <x:c r="D342" s="19"/>
       <x:c r="E342" s="17"/>
+      <x:c r="F342" s="28"/>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="18"/>
@@ -2781,6 +3152,7 @@
       <x:c r="C343" s="19"/>
       <x:c r="D343" s="19"/>
       <x:c r="E343" s="17"/>
+      <x:c r="F343" s="28"/>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="18"/>
@@ -2788,6 +3160,7 @@
       <x:c r="C344" s="19"/>
       <x:c r="D344" s="19"/>
       <x:c r="E344" s="17"/>
+      <x:c r="F344" s="28"/>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="18"/>
@@ -2795,6 +3168,7 @@
       <x:c r="C345" s="19"/>
       <x:c r="D345" s="19"/>
       <x:c r="E345" s="17"/>
+      <x:c r="F345" s="28"/>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="18"/>
@@ -2802,6 +3176,7 @@
       <x:c r="C346" s="19"/>
       <x:c r="D346" s="19"/>
       <x:c r="E346" s="17"/>
+      <x:c r="F346" s="28"/>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="18"/>
@@ -2809,6 +3184,7 @@
       <x:c r="C347" s="19"/>
       <x:c r="D347" s="19"/>
       <x:c r="E347" s="17"/>
+      <x:c r="F347" s="28"/>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="18"/>
@@ -2816,6 +3192,7 @@
       <x:c r="C348" s="19"/>
       <x:c r="D348" s="19"/>
       <x:c r="E348" s="17"/>
+      <x:c r="F348" s="28"/>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="18"/>
@@ -2823,6 +3200,7 @@
       <x:c r="C349" s="19"/>
       <x:c r="D349" s="19"/>
       <x:c r="E349" s="17"/>
+      <x:c r="F349" s="28"/>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="18"/>
@@ -2830,6 +3208,7 @@
       <x:c r="C350" s="19"/>
       <x:c r="D350" s="19"/>
       <x:c r="E350" s="17"/>
+      <x:c r="F350" s="28"/>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="18"/>
@@ -2837,6 +3216,7 @@
       <x:c r="C351" s="19"/>
       <x:c r="D351" s="19"/>
       <x:c r="E351" s="17"/>
+      <x:c r="F351" s="28"/>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="18"/>
@@ -2844,6 +3224,7 @@
       <x:c r="C352" s="19"/>
       <x:c r="D352" s="19"/>
       <x:c r="E352" s="17"/>
+      <x:c r="F352" s="28"/>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="18"/>
@@ -2851,6 +3232,7 @@
       <x:c r="C353" s="19"/>
       <x:c r="D353" s="19"/>
       <x:c r="E353" s="17"/>
+      <x:c r="F353" s="28"/>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="18"/>
@@ -2858,6 +3240,7 @@
       <x:c r="C354" s="19"/>
       <x:c r="D354" s="19"/>
       <x:c r="E354" s="17"/>
+      <x:c r="F354" s="28"/>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="18"/>
@@ -2865,6 +3248,7 @@
       <x:c r="C355" s="19"/>
       <x:c r="D355" s="19"/>
       <x:c r="E355" s="17"/>
+      <x:c r="F355" s="28"/>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="18"/>
@@ -2872,6 +3256,7 @@
       <x:c r="C356" s="19"/>
       <x:c r="D356" s="19"/>
       <x:c r="E356" s="17"/>
+      <x:c r="F356" s="28"/>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="18"/>
@@ -2879,6 +3264,7 @@
       <x:c r="C357" s="19"/>
       <x:c r="D357" s="19"/>
       <x:c r="E357" s="17"/>
+      <x:c r="F357" s="28"/>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="18"/>
@@ -2886,6 +3272,7 @@
       <x:c r="C358" s="19"/>
       <x:c r="D358" s="19"/>
       <x:c r="E358" s="17"/>
+      <x:c r="F358" s="28"/>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="18"/>
@@ -2893,6 +3280,7 @@
       <x:c r="C359" s="19"/>
       <x:c r="D359" s="19"/>
       <x:c r="E359" s="17"/>
+      <x:c r="F359" s="28"/>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="18"/>
@@ -2900,6 +3288,7 @@
       <x:c r="C360" s="19"/>
       <x:c r="D360" s="19"/>
       <x:c r="E360" s="17"/>
+      <x:c r="F360" s="28"/>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="18"/>
@@ -2907,6 +3296,7 @@
       <x:c r="C361" s="19"/>
       <x:c r="D361" s="19"/>
       <x:c r="E361" s="17"/>
+      <x:c r="F361" s="28"/>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="18"/>
@@ -2914,6 +3304,7 @@
       <x:c r="C362" s="19"/>
       <x:c r="D362" s="19"/>
       <x:c r="E362" s="17"/>
+      <x:c r="F362" s="28"/>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="18"/>
@@ -2921,6 +3312,7 @@
       <x:c r="C363" s="19"/>
       <x:c r="D363" s="19"/>
       <x:c r="E363" s="17"/>
+      <x:c r="F363" s="28"/>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="18"/>
@@ -2928,6 +3320,7 @@
       <x:c r="C364" s="19"/>
       <x:c r="D364" s="19"/>
       <x:c r="E364" s="17"/>
+      <x:c r="F364" s="28"/>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="18"/>
@@ -2935,6 +3328,7 @@
       <x:c r="C365" s="19"/>
       <x:c r="D365" s="19"/>
       <x:c r="E365" s="17"/>
+      <x:c r="F365" s="28"/>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="18"/>
@@ -2942,6 +3336,7 @@
       <x:c r="C366" s="19"/>
       <x:c r="D366" s="19"/>
       <x:c r="E366" s="17"/>
+      <x:c r="F366" s="28"/>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="18"/>
@@ -2949,6 +3344,7 @@
       <x:c r="C367" s="19"/>
       <x:c r="D367" s="19"/>
       <x:c r="E367" s="17"/>
+      <x:c r="F367" s="28"/>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="18"/>
@@ -2956,6 +3352,7 @@
       <x:c r="C368" s="19"/>
       <x:c r="D368" s="19"/>
       <x:c r="E368" s="17"/>
+      <x:c r="F368" s="28"/>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="18"/>
@@ -2963,6 +3360,7 @@
       <x:c r="C369" s="19"/>
       <x:c r="D369" s="19"/>
       <x:c r="E369" s="17"/>
+      <x:c r="F369" s="28"/>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="18"/>
@@ -2970,6 +3368,7 @@
       <x:c r="C370" s="19"/>
       <x:c r="D370" s="19"/>
       <x:c r="E370" s="17"/>
+      <x:c r="F370" s="28"/>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="18"/>
@@ -2977,6 +3376,7 @@
       <x:c r="C371" s="19"/>
       <x:c r="D371" s="19"/>
       <x:c r="E371" s="17"/>
+      <x:c r="F371" s="28"/>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="18"/>
@@ -2984,6 +3384,7 @@
       <x:c r="C372" s="19"/>
       <x:c r="D372" s="19"/>
       <x:c r="E372" s="17"/>
+      <x:c r="F372" s="28"/>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="18"/>
@@ -2991,6 +3392,7 @@
       <x:c r="C373" s="19"/>
       <x:c r="D373" s="19"/>
       <x:c r="E373" s="17"/>
+      <x:c r="F373" s="28"/>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="18"/>
@@ -2998,6 +3400,7 @@
       <x:c r="C374" s="19"/>
       <x:c r="D374" s="19"/>
       <x:c r="E374" s="17"/>
+      <x:c r="F374" s="28"/>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="18"/>
@@ -3005,6 +3408,7 @@
       <x:c r="C375" s="19"/>
       <x:c r="D375" s="19"/>
       <x:c r="E375" s="17"/>
+      <x:c r="F375" s="28"/>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="18"/>
@@ -3012,6 +3416,7 @@
       <x:c r="C376" s="19"/>
       <x:c r="D376" s="19"/>
       <x:c r="E376" s="17"/>
+      <x:c r="F376" s="28"/>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="18"/>
@@ -3019,6 +3424,7 @@
       <x:c r="C377" s="19"/>
       <x:c r="D377" s="19"/>
       <x:c r="E377" s="17"/>
+      <x:c r="F377" s="28"/>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="18"/>
@@ -3026,6 +3432,7 @@
       <x:c r="C378" s="19"/>
       <x:c r="D378" s="19"/>
       <x:c r="E378" s="17"/>
+      <x:c r="F378" s="28"/>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="18"/>
@@ -3033,6 +3440,7 @@
       <x:c r="C379" s="19"/>
       <x:c r="D379" s="19"/>
       <x:c r="E379" s="17"/>
+      <x:c r="F379" s="28"/>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="18"/>
@@ -3040,6 +3448,7 @@
       <x:c r="C380" s="19"/>
       <x:c r="D380" s="19"/>
       <x:c r="E380" s="17"/>
+      <x:c r="F380" s="28"/>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="18"/>
@@ -3047,6 +3456,7 @@
       <x:c r="C381" s="19"/>
       <x:c r="D381" s="19"/>
       <x:c r="E381" s="17"/>
+      <x:c r="F381" s="28"/>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="18"/>
@@ -3054,6 +3464,7 @@
       <x:c r="C382" s="19"/>
       <x:c r="D382" s="19"/>
       <x:c r="E382" s="17"/>
+      <x:c r="F382" s="28"/>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="18"/>
@@ -3061,6 +3472,7 @@
       <x:c r="C383" s="19"/>
       <x:c r="D383" s="19"/>
       <x:c r="E383" s="17"/>
+      <x:c r="F383" s="28"/>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="18"/>
@@ -3068,6 +3480,7 @@
       <x:c r="C384" s="19"/>
       <x:c r="D384" s="19"/>
       <x:c r="E384" s="17"/>
+      <x:c r="F384" s="28"/>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="18"/>
@@ -3075,6 +3488,7 @@
       <x:c r="C385" s="19"/>
       <x:c r="D385" s="19"/>
       <x:c r="E385" s="17"/>
+      <x:c r="F385" s="28"/>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="18"/>
@@ -3082,6 +3496,7 @@
       <x:c r="C386" s="19"/>
       <x:c r="D386" s="19"/>
       <x:c r="E386" s="17"/>
+      <x:c r="F386" s="28"/>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="18"/>
@@ -3089,6 +3504,7 @@
       <x:c r="C387" s="19"/>
       <x:c r="D387" s="19"/>
       <x:c r="E387" s="17"/>
+      <x:c r="F387" s="28"/>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="18"/>
@@ -3096,6 +3512,7 @@
       <x:c r="C388" s="19"/>
       <x:c r="D388" s="19"/>
       <x:c r="E388" s="17"/>
+      <x:c r="F388" s="28"/>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="18"/>
@@ -3103,6 +3520,7 @@
       <x:c r="C389" s="19"/>
       <x:c r="D389" s="19"/>
       <x:c r="E389" s="17"/>
+      <x:c r="F389" s="28"/>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="18"/>
@@ -3110,6 +3528,7 @@
       <x:c r="C390" s="19"/>
       <x:c r="D390" s="19"/>
       <x:c r="E390" s="17"/>
+      <x:c r="F390" s="28"/>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="18"/>
@@ -3117,6 +3536,7 @@
       <x:c r="C391" s="19"/>
       <x:c r="D391" s="19"/>
       <x:c r="E391" s="17"/>
+      <x:c r="F391" s="28"/>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="18"/>
@@ -3124,6 +3544,7 @@
       <x:c r="C392" s="19"/>
       <x:c r="D392" s="19"/>
       <x:c r="E392" s="17"/>
+      <x:c r="F392" s="28"/>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="18"/>
@@ -3131,6 +3552,7 @@
       <x:c r="C393" s="19"/>
       <x:c r="D393" s="19"/>
       <x:c r="E393" s="17"/>
+      <x:c r="F393" s="28"/>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="18"/>
@@ -3138,6 +3560,7 @@
       <x:c r="C394" s="19"/>
       <x:c r="D394" s="19"/>
       <x:c r="E394" s="17"/>
+      <x:c r="F394" s="28"/>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="18"/>
@@ -3145,6 +3568,7 @@
       <x:c r="C395" s="19"/>
       <x:c r="D395" s="19"/>
       <x:c r="E395" s="17"/>
+      <x:c r="F395" s="28"/>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="18"/>
@@ -3152,6 +3576,7 @@
       <x:c r="C396" s="19"/>
       <x:c r="D396" s="19"/>
       <x:c r="E396" s="17"/>
+      <x:c r="F396" s="28"/>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="18"/>
@@ -3159,6 +3584,7 @@
       <x:c r="C397" s="19"/>
       <x:c r="D397" s="19"/>
       <x:c r="E397" s="17"/>
+      <x:c r="F397" s="28"/>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="18"/>
@@ -3166,6 +3592,7 @@
       <x:c r="C398" s="19"/>
       <x:c r="D398" s="19"/>
       <x:c r="E398" s="17"/>
+      <x:c r="F398" s="28"/>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="18"/>
@@ -3173,6 +3600,7 @@
       <x:c r="C399" s="19"/>
       <x:c r="D399" s="19"/>
       <x:c r="E399" s="17"/>
+      <x:c r="F399" s="28"/>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="18"/>
@@ -3180,6 +3608,7 @@
       <x:c r="C400" s="19"/>
       <x:c r="D400" s="19"/>
       <x:c r="E400" s="17"/>
+      <x:c r="F400" s="28"/>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="18"/>
@@ -3187,6 +3616,7 @@
       <x:c r="C401" s="19"/>
       <x:c r="D401" s="19"/>
       <x:c r="E401" s="17"/>
+      <x:c r="F401" s="28"/>
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="18"/>
@@ -3194,6 +3624,7 @@
       <x:c r="C402" s="19"/>
       <x:c r="D402" s="19"/>
       <x:c r="E402" s="17"/>
+      <x:c r="F402" s="28"/>
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="18"/>
@@ -3201,6 +3632,7 @@
       <x:c r="C403" s="19"/>
       <x:c r="D403" s="19"/>
       <x:c r="E403" s="17"/>
+      <x:c r="F403" s="28"/>
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="18"/>
@@ -3208,6 +3640,7 @@
       <x:c r="C404" s="19"/>
       <x:c r="D404" s="19"/>
       <x:c r="E404" s="17"/>
+      <x:c r="F404" s="28"/>
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="18"/>
@@ -3215,6 +3648,7 @@
       <x:c r="C405" s="19"/>
       <x:c r="D405" s="19"/>
       <x:c r="E405" s="17"/>
+      <x:c r="F405" s="28"/>
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="18"/>
@@ -3222,6 +3656,7 @@
       <x:c r="C406" s="19"/>
       <x:c r="D406" s="19"/>
       <x:c r="E406" s="17"/>
+      <x:c r="F406" s="28"/>
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="18"/>
@@ -3229,6 +3664,7 @@
       <x:c r="C407" s="19"/>
       <x:c r="D407" s="19"/>
       <x:c r="E407" s="17"/>
+      <x:c r="F407" s="28"/>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="18"/>
@@ -3236,6 +3672,7 @@
       <x:c r="C408" s="19"/>
       <x:c r="D408" s="19"/>
       <x:c r="E408" s="17"/>
+      <x:c r="F408" s="28"/>
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="18"/>
@@ -3243,6 +3680,7 @@
       <x:c r="C409" s="19"/>
       <x:c r="D409" s="19"/>
       <x:c r="E409" s="17"/>
+      <x:c r="F409" s="28"/>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="18"/>
@@ -3250,6 +3688,7 @@
       <x:c r="C410" s="19"/>
       <x:c r="D410" s="19"/>
       <x:c r="E410" s="17"/>
+      <x:c r="F410" s="28"/>
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="18"/>
@@ -3257,6 +3696,7 @@
       <x:c r="C411" s="19"/>
       <x:c r="D411" s="19"/>
       <x:c r="E411" s="17"/>
+      <x:c r="F411" s="28"/>
     </x:row>
     <x:row r="412">
       <x:c r="A412" s="18"/>
@@ -3264,6 +3704,7 @@
       <x:c r="C412" s="19"/>
       <x:c r="D412" s="19"/>
       <x:c r="E412" s="17"/>
+      <x:c r="F412" s="28"/>
     </x:row>
     <x:row r="413">
       <x:c r="A413" s="18"/>
@@ -3271,6 +3712,7 @@
       <x:c r="C413" s="19"/>
       <x:c r="D413" s="19"/>
       <x:c r="E413" s="17"/>
+      <x:c r="F413" s="28"/>
     </x:row>
     <x:row r="414">
       <x:c r="A414" s="18"/>
@@ -3278,6 +3720,7 @@
       <x:c r="C414" s="19"/>
       <x:c r="D414" s="19"/>
       <x:c r="E414" s="17"/>
+      <x:c r="F414" s="28"/>
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="18"/>
@@ -3285,6 +3728,7 @@
       <x:c r="C415" s="19"/>
       <x:c r="D415" s="19"/>
       <x:c r="E415" s="17"/>
+      <x:c r="F415" s="28"/>
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="18"/>
@@ -3292,6 +3736,7 @@
       <x:c r="C416" s="19"/>
       <x:c r="D416" s="19"/>
       <x:c r="E416" s="17"/>
+      <x:c r="F416" s="28"/>
     </x:row>
     <x:row r="417">
       <x:c r="A417" s="18"/>
@@ -3299,6 +3744,7 @@
       <x:c r="C417" s="19"/>
       <x:c r="D417" s="19"/>
       <x:c r="E417" s="17"/>
+      <x:c r="F417" s="28"/>
     </x:row>
     <x:row r="418">
       <x:c r="A418" s="18"/>
@@ -3306,6 +3752,7 @@
       <x:c r="C418" s="19"/>
       <x:c r="D418" s="19"/>
       <x:c r="E418" s="17"/>
+      <x:c r="F418" s="28"/>
     </x:row>
     <x:row r="419">
       <x:c r="A419" s="18"/>
@@ -3313,6 +3760,7 @@
       <x:c r="C419" s="19"/>
       <x:c r="D419" s="19"/>
       <x:c r="E419" s="17"/>
+      <x:c r="F419" s="28"/>
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="18"/>
@@ -3320,6 +3768,7 @@
       <x:c r="C420" s="19"/>
       <x:c r="D420" s="19"/>
       <x:c r="E420" s="17"/>
+      <x:c r="F420" s="28"/>
     </x:row>
     <x:row r="421">
       <x:c r="A421" s="18"/>
@@ -3327,6 +3776,7 @@
       <x:c r="C421" s="19"/>
       <x:c r="D421" s="19"/>
       <x:c r="E421" s="17"/>
+      <x:c r="F421" s="28"/>
     </x:row>
     <x:row r="422">
       <x:c r="A422" s="18"/>
@@ -3334,6 +3784,7 @@
       <x:c r="C422" s="19"/>
       <x:c r="D422" s="19"/>
       <x:c r="E422" s="17"/>
+      <x:c r="F422" s="28"/>
     </x:row>
     <x:row r="423">
       <x:c r="A423" s="18"/>
@@ -3341,6 +3792,7 @@
       <x:c r="C423" s="19"/>
       <x:c r="D423" s="19"/>
       <x:c r="E423" s="17"/>
+      <x:c r="F423" s="28"/>
     </x:row>
     <x:row r="424">
       <x:c r="A424" s="18"/>
@@ -3348,6 +3800,7 @@
       <x:c r="C424" s="19"/>
       <x:c r="D424" s="19"/>
       <x:c r="E424" s="17"/>
+      <x:c r="F424" s="28"/>
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="18"/>
@@ -3355,6 +3808,7 @@
       <x:c r="C425" s="19"/>
       <x:c r="D425" s="19"/>
       <x:c r="E425" s="17"/>
+      <x:c r="F425" s="28"/>
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="18"/>
@@ -3362,6 +3816,7 @@
       <x:c r="C426" s="19"/>
       <x:c r="D426" s="19"/>
       <x:c r="E426" s="17"/>
+      <x:c r="F426" s="28"/>
     </x:row>
     <x:row r="427">
       <x:c r="A427" s="18"/>
@@ -3369,6 +3824,7 @@
       <x:c r="C427" s="19"/>
       <x:c r="D427" s="19"/>
       <x:c r="E427" s="17"/>
+      <x:c r="F427" s="28"/>
     </x:row>
     <x:row r="428">
       <x:c r="A428" s="18"/>
@@ -3376,6 +3832,7 @@
       <x:c r="C428" s="19"/>
       <x:c r="D428" s="19"/>
       <x:c r="E428" s="17"/>
+      <x:c r="F428" s="28"/>
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="18"/>
@@ -3383,6 +3840,7 @@
       <x:c r="C429" s="19"/>
       <x:c r="D429" s="19"/>
       <x:c r="E429" s="17"/>
+      <x:c r="F429" s="28"/>
     </x:row>
     <x:row r="430">
       <x:c r="A430" s="18"/>
@@ -3390,6 +3848,7 @@
       <x:c r="C430" s="19"/>
       <x:c r="D430" s="19"/>
       <x:c r="E430" s="17"/>
+      <x:c r="F430" s="28"/>
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="18"/>
@@ -3397,6 +3856,7 @@
       <x:c r="C431" s="19"/>
       <x:c r="D431" s="19"/>
       <x:c r="E431" s="17"/>
+      <x:c r="F431" s="28"/>
     </x:row>
     <x:row r="432">
       <x:c r="A432" s="18"/>
@@ -3404,6 +3864,7 @@
       <x:c r="C432" s="19"/>
       <x:c r="D432" s="19"/>
       <x:c r="E432" s="17"/>
+      <x:c r="F432" s="28"/>
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="18"/>
@@ -3411,6 +3872,7 @@
       <x:c r="C433" s="19"/>
       <x:c r="D433" s="19"/>
       <x:c r="E433" s="17"/>
+      <x:c r="F433" s="28"/>
     </x:row>
     <x:row r="434">
       <x:c r="A434" s="18"/>
@@ -3418,6 +3880,7 @@
       <x:c r="C434" s="19"/>
       <x:c r="D434" s="19"/>
       <x:c r="E434" s="17"/>
+      <x:c r="F434" s="28"/>
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="18"/>
@@ -3425,6 +3888,7 @@
       <x:c r="C435" s="19"/>
       <x:c r="D435" s="19"/>
       <x:c r="E435" s="17"/>
+      <x:c r="F435" s="28"/>
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="18"/>
@@ -3432,6 +3896,7 @@
       <x:c r="C436" s="19"/>
       <x:c r="D436" s="19"/>
       <x:c r="E436" s="17"/>
+      <x:c r="F436" s="28"/>
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="18"/>
@@ -3439,6 +3904,7 @@
       <x:c r="C437" s="19"/>
       <x:c r="D437" s="19"/>
       <x:c r="E437" s="17"/>
+      <x:c r="F437" s="28"/>
     </x:row>
     <x:row r="438">
       <x:c r="A438" s="18"/>
@@ -3446,6 +3912,7 @@
       <x:c r="C438" s="19"/>
       <x:c r="D438" s="19"/>
       <x:c r="E438" s="17"/>
+      <x:c r="F438" s="28"/>
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="18"/>
@@ -3453,6 +3920,7 @@
       <x:c r="C439" s="19"/>
       <x:c r="D439" s="19"/>
       <x:c r="E439" s="17"/>
+      <x:c r="F439" s="28"/>
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="18"/>
@@ -3460,6 +3928,7 @@
       <x:c r="C440" s="19"/>
       <x:c r="D440" s="19"/>
       <x:c r="E440" s="17"/>
+      <x:c r="F440" s="28"/>
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="18"/>
@@ -3467,6 +3936,7 @@
       <x:c r="C441" s="19"/>
       <x:c r="D441" s="19"/>
       <x:c r="E441" s="17"/>
+      <x:c r="F441" s="28"/>
     </x:row>
     <x:row r="442">
       <x:c r="A442" s="18"/>
@@ -3474,6 +3944,7 @@
       <x:c r="C442" s="19"/>
       <x:c r="D442" s="19"/>
       <x:c r="E442" s="17"/>
+      <x:c r="F442" s="28"/>
     </x:row>
     <x:row r="443">
       <x:c r="A443" s="18"/>
@@ -3481,6 +3952,7 @@
       <x:c r="C443" s="19"/>
       <x:c r="D443" s="19"/>
       <x:c r="E443" s="17"/>
+      <x:c r="F443" s="28"/>
     </x:row>
     <x:row r="444">
       <x:c r="A444" s="18"/>
@@ -3488,6 +3960,7 @@
       <x:c r="C444" s="19"/>
       <x:c r="D444" s="19"/>
       <x:c r="E444" s="17"/>
+      <x:c r="F444" s="28"/>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="18"/>
@@ -3495,6 +3968,7 @@
       <x:c r="C445" s="19"/>
       <x:c r="D445" s="19"/>
       <x:c r="E445" s="17"/>
+      <x:c r="F445" s="28"/>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="18"/>
@@ -3502,6 +3976,7 @@
       <x:c r="C446" s="19"/>
       <x:c r="D446" s="19"/>
       <x:c r="E446" s="17"/>
+      <x:c r="F446" s="28"/>
     </x:row>
     <x:row r="447">
       <x:c r="A447" s="18"/>
@@ -3509,6 +3984,7 @@
       <x:c r="C447" s="19"/>
       <x:c r="D447" s="19"/>
       <x:c r="E447" s="17"/>
+      <x:c r="F447" s="28"/>
     </x:row>
     <x:row r="448">
       <x:c r="A448" s="18"/>
@@ -3516,6 +3992,7 @@
       <x:c r="C448" s="19"/>
       <x:c r="D448" s="19"/>
       <x:c r="E448" s="17"/>
+      <x:c r="F448" s="28"/>
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="18"/>
@@ -3523,6 +4000,7 @@
       <x:c r="C449" s="19"/>
       <x:c r="D449" s="19"/>
       <x:c r="E449" s="17"/>
+      <x:c r="F449" s="28"/>
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="18"/>
@@ -3530,6 +4008,7 @@
       <x:c r="C450" s="19"/>
       <x:c r="D450" s="19"/>
       <x:c r="E450" s="17"/>
+      <x:c r="F450" s="28"/>
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="18"/>
@@ -3537,6 +4016,7 @@
       <x:c r="C451" s="19"/>
       <x:c r="D451" s="19"/>
       <x:c r="E451" s="17"/>
+      <x:c r="F451" s="28"/>
     </x:row>
     <x:row r="452">
       <x:c r="A452" s="18"/>
@@ -3544,6 +4024,7 @@
       <x:c r="C452" s="19"/>
       <x:c r="D452" s="19"/>
       <x:c r="E452" s="17"/>
+      <x:c r="F452" s="28"/>
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="18"/>
@@ -3551,6 +4032,7 @@
       <x:c r="C453" s="19"/>
       <x:c r="D453" s="19"/>
       <x:c r="E453" s="17"/>
+      <x:c r="F453" s="28"/>
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="18"/>
@@ -3558,6 +4040,7 @@
       <x:c r="C454" s="19"/>
       <x:c r="D454" s="19"/>
       <x:c r="E454" s="17"/>
+      <x:c r="F454" s="28"/>
     </x:row>
     <x:row r="455">
       <x:c r="A455" s="18"/>
@@ -3565,6 +4048,7 @@
       <x:c r="C455" s="19"/>
       <x:c r="D455" s="19"/>
       <x:c r="E455" s="17"/>
+      <x:c r="F455" s="28"/>
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="18"/>
@@ -3572,6 +4056,7 @@
       <x:c r="C456" s="19"/>
       <x:c r="D456" s="19"/>
       <x:c r="E456" s="17"/>
+      <x:c r="F456" s="28"/>
     </x:row>
     <x:row r="457">
       <x:c r="A457" s="18"/>
@@ -3579,6 +4064,7 @@
       <x:c r="C457" s="19"/>
       <x:c r="D457" s="19"/>
       <x:c r="E457" s="17"/>
+      <x:c r="F457" s="28"/>
     </x:row>
     <x:row r="458">
       <x:c r="A458" s="18"/>
@@ -3586,6 +4072,7 @@
       <x:c r="C458" s="19"/>
       <x:c r="D458" s="19"/>
       <x:c r="E458" s="17"/>
+      <x:c r="F458" s="28"/>
     </x:row>
     <x:row r="459">
       <x:c r="A459" s="18"/>
@@ -3593,6 +4080,7 @@
       <x:c r="C459" s="19"/>
       <x:c r="D459" s="19"/>
       <x:c r="E459" s="17"/>
+      <x:c r="F459" s="28"/>
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="18"/>
@@ -3600,6 +4088,7 @@
       <x:c r="C460" s="19"/>
       <x:c r="D460" s="19"/>
       <x:c r="E460" s="17"/>
+      <x:c r="F460" s="28"/>
     </x:row>
     <x:row r="461">
       <x:c r="A461" s="18"/>
@@ -3607,6 +4096,7 @@
       <x:c r="C461" s="19"/>
       <x:c r="D461" s="19"/>
       <x:c r="E461" s="17"/>
+      <x:c r="F461" s="28"/>
     </x:row>
     <x:row r="462">
       <x:c r="A462" s="18"/>
@@ -3614,6 +4104,7 @@
       <x:c r="C462" s="19"/>
       <x:c r="D462" s="19"/>
       <x:c r="E462" s="17"/>
+      <x:c r="F462" s="28"/>
     </x:row>
     <x:row r="463">
       <x:c r="A463" s="18"/>
@@ -3621,6 +4112,7 @@
       <x:c r="C463" s="19"/>
       <x:c r="D463" s="19"/>
       <x:c r="E463" s="17"/>
+      <x:c r="F463" s="28"/>
     </x:row>
     <x:row r="464">
       <x:c r="A464" s="18"/>
@@ -3628,6 +4120,7 @@
       <x:c r="C464" s="19"/>
       <x:c r="D464" s="19"/>
       <x:c r="E464" s="17"/>
+      <x:c r="F464" s="28"/>
     </x:row>
     <x:row r="465">
       <x:c r="A465" s="18"/>
@@ -3635,6 +4128,7 @@
       <x:c r="C465" s="19"/>
       <x:c r="D465" s="19"/>
       <x:c r="E465" s="17"/>
+      <x:c r="F465" s="28"/>
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="18"/>
@@ -3642,6 +4136,7 @@
       <x:c r="C466" s="19"/>
       <x:c r="D466" s="19"/>
       <x:c r="E466" s="17"/>
+      <x:c r="F466" s="28"/>
     </x:row>
     <x:row r="467">
       <x:c r="A467" s="18"/>
@@ -3649,6 +4144,7 @@
       <x:c r="C467" s="19"/>
       <x:c r="D467" s="19"/>
       <x:c r="E467" s="17"/>
+      <x:c r="F467" s="28"/>
     </x:row>
     <x:row r="468">
       <x:c r="A468" s="18"/>
@@ -3656,6 +4152,7 @@
       <x:c r="C468" s="19"/>
       <x:c r="D468" s="19"/>
       <x:c r="E468" s="17"/>
+      <x:c r="F468" s="28"/>
     </x:row>
     <x:row r="469">
       <x:c r="A469" s="18"/>
@@ -3663,6 +4160,7 @@
       <x:c r="C469" s="19"/>
       <x:c r="D469" s="19"/>
       <x:c r="E469" s="17"/>
+      <x:c r="F469" s="28"/>
     </x:row>
     <x:row r="470">
       <x:c r="A470" s="18"/>
@@ -3670,6 +4168,7 @@
       <x:c r="C470" s="19"/>
       <x:c r="D470" s="19"/>
       <x:c r="E470" s="17"/>
+      <x:c r="F470" s="28"/>
     </x:row>
     <x:row r="471">
       <x:c r="A471" s="18"/>
@@ -3677,6 +4176,7 @@
       <x:c r="C471" s="19"/>
       <x:c r="D471" s="19"/>
       <x:c r="E471" s="17"/>
+      <x:c r="F471" s="28"/>
     </x:row>
     <x:row r="472">
       <x:c r="A472" s="18"/>
@@ -3684,6 +4184,7 @@
       <x:c r="C472" s="19"/>
       <x:c r="D472" s="19"/>
       <x:c r="E472" s="17"/>
+      <x:c r="F472" s="28"/>
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="18"/>
@@ -3691,6 +4192,7 @@
       <x:c r="C473" s="19"/>
       <x:c r="D473" s="19"/>
       <x:c r="E473" s="17"/>
+      <x:c r="F473" s="28"/>
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="18"/>
@@ -3698,6 +4200,7 @@
       <x:c r="C474" s="19"/>
       <x:c r="D474" s="19"/>
       <x:c r="E474" s="17"/>
+      <x:c r="F474" s="28"/>
     </x:row>
     <x:row r="475">
       <x:c r="A475" s="18"/>
@@ -3705,6 +4208,7 @@
       <x:c r="C475" s="19"/>
       <x:c r="D475" s="19"/>
       <x:c r="E475" s="17"/>
+      <x:c r="F475" s="28"/>
     </x:row>
     <x:row r="476">
       <x:c r="A476" s="18"/>
@@ -3712,6 +4216,7 @@
       <x:c r="C476" s="19"/>
       <x:c r="D476" s="19"/>
       <x:c r="E476" s="17"/>
+      <x:c r="F476" s="28"/>
     </x:row>
     <x:row r="477">
       <x:c r="A477" s="18"/>
@@ -3719,6 +4224,7 @@
       <x:c r="C477" s="19"/>
       <x:c r="D477" s="19"/>
       <x:c r="E477" s="17"/>
+      <x:c r="F477" s="28"/>
     </x:row>
     <x:row r="478">
       <x:c r="A478" s="18"/>
@@ -3726,6 +4232,7 @@
       <x:c r="C478" s="19"/>
       <x:c r="D478" s="19"/>
       <x:c r="E478" s="17"/>
+      <x:c r="F478" s="28"/>
     </x:row>
     <x:row r="479">
       <x:c r="A479" s="18"/>
@@ -3733,6 +4240,7 @@
       <x:c r="C479" s="19"/>
       <x:c r="D479" s="19"/>
       <x:c r="E479" s="17"/>
+      <x:c r="F479" s="28"/>
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="18"/>
@@ -3740,6 +4248,7 @@
       <x:c r="C480" s="19"/>
       <x:c r="D480" s="19"/>
       <x:c r="E480" s="17"/>
+      <x:c r="F480" s="28"/>
     </x:row>
     <x:row r="481">
       <x:c r="A481" s="18"/>
@@ -3747,6 +4256,7 @@
       <x:c r="C481" s="19"/>
       <x:c r="D481" s="19"/>
       <x:c r="E481" s="17"/>
+      <x:c r="F481" s="28"/>
     </x:row>
     <x:row r="482">
       <x:c r="A482" s="18"/>
@@ -3754,6 +4264,7 @@
       <x:c r="C482" s="19"/>
       <x:c r="D482" s="19"/>
       <x:c r="E482" s="17"/>
+      <x:c r="F482" s="28"/>
     </x:row>
     <x:row r="483">
       <x:c r="A483" s="18"/>
@@ -3761,6 +4272,7 @@
       <x:c r="C483" s="19"/>
       <x:c r="D483" s="19"/>
       <x:c r="E483" s="17"/>
+      <x:c r="F483" s="28"/>
     </x:row>
     <x:row r="484">
       <x:c r="A484" s="18"/>
@@ -3768,6 +4280,7 @@
       <x:c r="C484" s="19"/>
       <x:c r="D484" s="19"/>
       <x:c r="E484" s="17"/>
+      <x:c r="F484" s="28"/>
     </x:row>
     <x:row r="485">
       <x:c r="A485" s="18"/>
@@ -3775,6 +4288,7 @@
       <x:c r="C485" s="19"/>
       <x:c r="D485" s="19"/>
       <x:c r="E485" s="17"/>
+      <x:c r="F485" s="28"/>
     </x:row>
     <x:row r="486">
       <x:c r="A486" s="18"/>
@@ -3782,6 +4296,7 @@
       <x:c r="C486" s="19"/>
       <x:c r="D486" s="19"/>
       <x:c r="E486" s="17"/>
+      <x:c r="F486" s="28"/>
     </x:row>
     <x:row r="487">
       <x:c r="A487" s="18"/>
@@ -3789,6 +4304,7 @@
       <x:c r="C487" s="19"/>
       <x:c r="D487" s="19"/>
       <x:c r="E487" s="17"/>
+      <x:c r="F487" s="28"/>
     </x:row>
     <x:row r="488">
       <x:c r="A488" s="18"/>
@@ -3796,6 +4312,7 @@
       <x:c r="C488" s="19"/>
       <x:c r="D488" s="19"/>
       <x:c r="E488" s="17"/>
+      <x:c r="F488" s="28"/>
     </x:row>
     <x:row r="489">
       <x:c r="A489" s="18"/>
@@ -3803,6 +4320,7 @@
       <x:c r="C489" s="19"/>
       <x:c r="D489" s="19"/>
       <x:c r="E489" s="17"/>
+      <x:c r="F489" s="28"/>
     </x:row>
     <x:row r="490">
       <x:c r="A490" s="18"/>
@@ -3810,6 +4328,7 @@
       <x:c r="C490" s="19"/>
       <x:c r="D490" s="19"/>
       <x:c r="E490" s="17"/>
+      <x:c r="F490" s="28"/>
     </x:row>
     <x:row r="491">
       <x:c r="A491" s="18"/>
@@ -3817,6 +4336,7 @@
       <x:c r="C491" s="19"/>
       <x:c r="D491" s="19"/>
       <x:c r="E491" s="17"/>
+      <x:c r="F491" s="28"/>
     </x:row>
     <x:row r="492">
       <x:c r="A492" s="18"/>
@@ -3824,6 +4344,7 @@
       <x:c r="C492" s="19"/>
       <x:c r="D492" s="19"/>
       <x:c r="E492" s="17"/>
+      <x:c r="F492" s="28"/>
     </x:row>
     <x:row r="493">
       <x:c r="A493" s="18"/>
@@ -3831,6 +4352,7 @@
       <x:c r="C493" s="19"/>
       <x:c r="D493" s="19"/>
       <x:c r="E493" s="17"/>
+      <x:c r="F493" s="28"/>
     </x:row>
     <x:row r="494">
       <x:c r="A494" s="18"/>
@@ -3838,6 +4360,7 @@
       <x:c r="C494" s="19"/>
       <x:c r="D494" s="19"/>
       <x:c r="E494" s="17"/>
+      <x:c r="F494" s="28"/>
     </x:row>
     <x:row r="495">
       <x:c r="A495" s="18"/>
@@ -3845,6 +4368,7 @@
       <x:c r="C495" s="19"/>
       <x:c r="D495" s="19"/>
       <x:c r="E495" s="17"/>
+      <x:c r="F495" s="28"/>
     </x:row>
     <x:row r="496">
       <x:c r="A496" s="18"/>
@@ -3852,6 +4376,7 @@
       <x:c r="C496" s="19"/>
       <x:c r="D496" s="19"/>
       <x:c r="E496" s="17"/>
+      <x:c r="F496" s="28"/>
     </x:row>
     <x:row r="497">
       <x:c r="A497" s="18"/>
@@ -3859,6 +4384,7 @@
       <x:c r="C497" s="19"/>
       <x:c r="D497" s="19"/>
       <x:c r="E497" s="17"/>
+      <x:c r="F497" s="28"/>
     </x:row>
     <x:row r="498">
       <x:c r="A498" s="18"/>
@@ -3866,6 +4392,7 @@
       <x:c r="C498" s="19"/>
       <x:c r="D498" s="19"/>
       <x:c r="E498" s="17"/>
+      <x:c r="F498" s="28"/>
     </x:row>
     <x:row r="499">
       <x:c r="A499" s="18"/>
@@ -3873,6 +4400,7 @@
       <x:c r="C499" s="19"/>
       <x:c r="D499" s="19"/>
       <x:c r="E499" s="17"/>
+      <x:c r="F499" s="28"/>
     </x:row>
     <x:row r="500">
       <x:c r="A500" s="18"/>
@@ -3880,6 +4408,7 @@
       <x:c r="C500" s="19"/>
       <x:c r="D500" s="19"/>
       <x:c r="E500" s="17"/>
+      <x:c r="F500" s="28"/>
     </x:row>
     <x:row r="501">
       <x:c r="A501" s="18"/>
@@ -3887,6 +4416,7 @@
       <x:c r="C501" s="19"/>
       <x:c r="D501" s="19"/>
       <x:c r="E501" s="17"/>
+      <x:c r="F501" s="28"/>
     </x:row>
     <x:row r="502">
       <x:c r="A502" s="18"/>
@@ -3894,6 +4424,7 @@
       <x:c r="C502" s="19"/>
       <x:c r="D502" s="19"/>
       <x:c r="E502" s="17"/>
+      <x:c r="F502" s="28"/>
     </x:row>
     <x:row r="503">
       <x:c r="A503" s="18"/>
@@ -3901,6 +4432,7 @@
       <x:c r="C503" s="19"/>
       <x:c r="D503" s="19"/>
       <x:c r="E503" s="17"/>
+      <x:c r="F503" s="28"/>
     </x:row>
     <x:row r="504">
       <x:c r="A504" s="18"/>
@@ -3908,6 +4440,7 @@
       <x:c r="C504" s="19"/>
       <x:c r="D504" s="19"/>
       <x:c r="E504" s="17"/>
+      <x:c r="F504" s="28"/>
     </x:row>
     <x:row r="505">
       <x:c r="A505" s="18"/>
@@ -3915,6 +4448,7 @@
       <x:c r="C505" s="19"/>
       <x:c r="D505" s="19"/>
       <x:c r="E505" s="17"/>
+      <x:c r="F505" s="28"/>
     </x:row>
     <x:row r="506">
       <x:c r="A506" s="18"/>
@@ -3922,6 +4456,7 @@
       <x:c r="C506" s="19"/>
       <x:c r="D506" s="19"/>
       <x:c r="E506" s="17"/>
+      <x:c r="F506" s="28"/>
     </x:row>
     <x:row r="507">
       <x:c r="A507" s="18"/>
@@ -3929,6 +4464,7 @@
       <x:c r="C507" s="19"/>
       <x:c r="D507" s="19"/>
       <x:c r="E507" s="17"/>
+      <x:c r="F507" s="28"/>
     </x:row>
     <x:row r="508">
       <x:c r="A508" s="18"/>
@@ -3936,6 +4472,7 @@
       <x:c r="C508" s="19"/>
       <x:c r="D508" s="19"/>
       <x:c r="E508" s="17"/>
+      <x:c r="F508" s="28"/>
     </x:row>
     <x:row r="509">
       <x:c r="A509" s="18"/>
@@ -3943,6 +4480,7 @@
       <x:c r="C509" s="19"/>
       <x:c r="D509" s="19"/>
       <x:c r="E509" s="17"/>
+      <x:c r="F509" s="28"/>
     </x:row>
     <x:row r="510">
       <x:c r="A510" s="18"/>
@@ -3950,6 +4488,7 @@
       <x:c r="C510" s="19"/>
       <x:c r="D510" s="19"/>
       <x:c r="E510" s="17"/>
+      <x:c r="F510" s="28"/>
     </x:row>
     <x:row r="511">
       <x:c r="A511" s="18"/>
@@ -3957,6 +4496,7 @@
       <x:c r="C511" s="19"/>
       <x:c r="D511" s="19"/>
       <x:c r="E511" s="17"/>
+      <x:c r="F511" s="28"/>
     </x:row>
     <x:row r="512">
       <x:c r="A512" s="18"/>
@@ -3964,6 +4504,7 @@
       <x:c r="C512" s="19"/>
       <x:c r="D512" s="19"/>
       <x:c r="E512" s="17"/>
+      <x:c r="F512" s="28"/>
     </x:row>
     <x:row r="513">
       <x:c r="A513" s="18"/>
@@ -3971,6 +4512,7 @@
       <x:c r="C513" s="19"/>
       <x:c r="D513" s="19"/>
       <x:c r="E513" s="17"/>
+      <x:c r="F513" s="28"/>
     </x:row>
     <x:row r="514">
       <x:c r="A514" s="18"/>
@@ -3978,6 +4520,7 @@
       <x:c r="C514" s="19"/>
       <x:c r="D514" s="19"/>
       <x:c r="E514" s="17"/>
+      <x:c r="F514" s="28"/>
     </x:row>
     <x:row r="515">
       <x:c r="A515" s="18"/>
@@ -3985,6 +4528,7 @@
       <x:c r="C515" s="19"/>
       <x:c r="D515" s="19"/>
       <x:c r="E515" s="17"/>
+      <x:c r="F515" s="28"/>
     </x:row>
     <x:row r="516">
       <x:c r="A516" s="18"/>
@@ -3992,6 +4536,7 @@
       <x:c r="C516" s="19"/>
       <x:c r="D516" s="19"/>
       <x:c r="E516" s="17"/>
+      <x:c r="F516" s="28"/>
     </x:row>
     <x:row r="517">
       <x:c r="A517" s="18"/>
@@ -3999,6 +4544,7 @@
       <x:c r="C517" s="19"/>
       <x:c r="D517" s="19"/>
       <x:c r="E517" s="17"/>
+      <x:c r="F517" s="28"/>
     </x:row>
     <x:row r="518">
       <x:c r="A518" s="18"/>
@@ -4006,6 +4552,7 @@
       <x:c r="C518" s="19"/>
       <x:c r="D518" s="19"/>
       <x:c r="E518" s="17"/>
+      <x:c r="F518" s="28"/>
     </x:row>
     <x:row r="519">
       <x:c r="A519" s="18"/>
@@ -4013,6 +4560,7 @@
       <x:c r="C519" s="19"/>
       <x:c r="D519" s="19"/>
       <x:c r="E519" s="17"/>
+      <x:c r="F519" s="28"/>
     </x:row>
     <x:row r="520">
       <x:c r="A520" s="18"/>
@@ -4020,6 +4568,7 @@
       <x:c r="C520" s="19"/>
       <x:c r="D520" s="19"/>
       <x:c r="E520" s="17"/>
+      <x:c r="F520" s="28"/>
     </x:row>
     <x:row r="521">
       <x:c r="A521" s="18"/>
@@ -4027,6 +4576,7 @@
       <x:c r="C521" s="19"/>
       <x:c r="D521" s="19"/>
       <x:c r="E521" s="17"/>
+      <x:c r="F521" s="28"/>
     </x:row>
     <x:row r="522">
       <x:c r="A522" s="18"/>
@@ -4034,6 +4584,7 @@
       <x:c r="C522" s="19"/>
       <x:c r="D522" s="19"/>
       <x:c r="E522" s="17"/>
+      <x:c r="F522" s="28"/>
     </x:row>
     <x:row r="523">
       <x:c r="A523" s="18"/>
@@ -4041,6 +4592,7 @@
       <x:c r="C523" s="19"/>
       <x:c r="D523" s="19"/>
       <x:c r="E523" s="17"/>
+      <x:c r="F523" s="28"/>
     </x:row>
     <x:row r="524">
       <x:c r="A524" s="18"/>
@@ -4048,6 +4600,7 @@
       <x:c r="C524" s="19"/>
       <x:c r="D524" s="19"/>
       <x:c r="E524" s="17"/>
+      <x:c r="F524" s="28"/>
     </x:row>
     <x:row r="525">
       <x:c r="A525" s="18"/>
@@ -4055,6 +4608,7 @@
       <x:c r="C525" s="19"/>
       <x:c r="D525" s="19"/>
       <x:c r="E525" s="17"/>
+      <x:c r="F525" s="28"/>
     </x:row>
     <x:row r="526">
       <x:c r="A526" s="18"/>
@@ -4062,6 +4616,7 @@
       <x:c r="C526" s="19"/>
       <x:c r="D526" s="19"/>
       <x:c r="E526" s="17"/>
+      <x:c r="F526" s="28"/>
     </x:row>
     <x:row r="527">
       <x:c r="A527" s="18"/>
@@ -4069,6 +4624,7 @@
       <x:c r="C527" s="19"/>
       <x:c r="D527" s="19"/>
       <x:c r="E527" s="17"/>
+      <x:c r="F527" s="28"/>
     </x:row>
     <x:row r="528">
       <x:c r="A528" s="18"/>
@@ -4076,6 +4632,7 @@
       <x:c r="C528" s="19"/>
       <x:c r="D528" s="19"/>
       <x:c r="E528" s="17"/>
+      <x:c r="F528" s="28"/>
     </x:row>
     <x:row r="529">
       <x:c r="A529" s="18"/>
@@ -4083,6 +4640,7 @@
       <x:c r="C529" s="19"/>
       <x:c r="D529" s="19"/>
       <x:c r="E529" s="17"/>
+      <x:c r="F529" s="28"/>
     </x:row>
     <x:row r="530">
       <x:c r="A530" s="18"/>
@@ -4090,6 +4648,7 @@
       <x:c r="C530" s="19"/>
       <x:c r="D530" s="19"/>
       <x:c r="E530" s="17"/>
+      <x:c r="F530" s="28"/>
     </x:row>
     <x:row r="531">
       <x:c r="A531" s="18"/>
@@ -4097,6 +4656,7 @@
       <x:c r="C531" s="19"/>
       <x:c r="D531" s="19"/>
       <x:c r="E531" s="17"/>
+      <x:c r="F531" s="28"/>
     </x:row>
     <x:row r="532">
       <x:c r="A532" s="18"/>
@@ -4104,6 +4664,7 @@
       <x:c r="C532" s="19"/>
       <x:c r="D532" s="19"/>
       <x:c r="E532" s="17"/>
+      <x:c r="F532" s="28"/>
     </x:row>
     <x:row r="533">
       <x:c r="A533" s="18"/>
@@ -4111,6 +4672,7 @@
       <x:c r="C533" s="19"/>
       <x:c r="D533" s="19"/>
       <x:c r="E533" s="17"/>
+      <x:c r="F533" s="28"/>
     </x:row>
     <x:row r="534">
       <x:c r="A534" s="18"/>
@@ -4118,6 +4680,7 @@
       <x:c r="C534" s="19"/>
       <x:c r="D534" s="19"/>
       <x:c r="E534" s="17"/>
+      <x:c r="F534" s="28"/>
     </x:row>
     <x:row r="535">
       <x:c r="A535" s="18"/>
@@ -4125,6 +4688,7 @@
       <x:c r="C535" s="19"/>
       <x:c r="D535" s="19"/>
       <x:c r="E535" s="17"/>
+      <x:c r="F535" s="28"/>
     </x:row>
     <x:row r="536">
       <x:c r="A536" s="18"/>
@@ -4132,6 +4696,7 @@
       <x:c r="C536" s="19"/>
       <x:c r="D536" s="19"/>
       <x:c r="E536" s="17"/>
+      <x:c r="F536" s="28"/>
     </x:row>
     <x:row r="537">
       <x:c r="A537" s="18"/>
@@ -4139,6 +4704,7 @@
       <x:c r="C537" s="19"/>
       <x:c r="D537" s="19"/>
       <x:c r="E537" s="17"/>
+      <x:c r="F537" s="28"/>
     </x:row>
     <x:row r="538">
       <x:c r="A538" s="18"/>
@@ -4146,6 +4712,7 @@
       <x:c r="C538" s="19"/>
       <x:c r="D538" s="19"/>
       <x:c r="E538" s="17"/>
+      <x:c r="F538" s="28"/>
     </x:row>
     <x:row r="539">
       <x:c r="A539" s="18"/>
@@ -4153,6 +4720,7 @@
       <x:c r="C539" s="19"/>
       <x:c r="D539" s="19"/>
       <x:c r="E539" s="17"/>
+      <x:c r="F539" s="28"/>
     </x:row>
     <x:row r="540">
       <x:c r="A540" s="18"/>
@@ -4160,6 +4728,7 @@
       <x:c r="C540" s="19"/>
       <x:c r="D540" s="19"/>
       <x:c r="E540" s="17"/>
+      <x:c r="F540" s="28"/>
     </x:row>
     <x:row r="541">
       <x:c r="A541" s="18"/>
@@ -4167,6 +4736,7 @@
       <x:c r="C541" s="19"/>
       <x:c r="D541" s="19"/>
       <x:c r="E541" s="17"/>
+      <x:c r="F541" s="28"/>
     </x:row>
     <x:row r="542">
       <x:c r="A542" s="18"/>
@@ -4174,6 +4744,7 @@
       <x:c r="C542" s="19"/>
       <x:c r="D542" s="19"/>
       <x:c r="E542" s="17"/>
+      <x:c r="F542" s="28"/>
     </x:row>
     <x:row r="543">
       <x:c r="A543" s="18"/>
@@ -4181,6 +4752,7 @@
       <x:c r="C543" s="19"/>
       <x:c r="D543" s="19"/>
       <x:c r="E543" s="17"/>
+      <x:c r="F543" s="28"/>
     </x:row>
     <x:row r="544">
       <x:c r="A544" s="18"/>
@@ -4188,6 +4760,7 @@
       <x:c r="C544" s="19"/>
       <x:c r="D544" s="19"/>
       <x:c r="E544" s="17"/>
+      <x:c r="F544" s="28"/>
     </x:row>
     <x:row r="545">
       <x:c r="A545" s="18"/>
@@ -4195,6 +4768,7 @@
       <x:c r="C545" s="19"/>
       <x:c r="D545" s="19"/>
       <x:c r="E545" s="17"/>
+      <x:c r="F545" s="28"/>
     </x:row>
     <x:row r="546">
       <x:c r="A546" s="18"/>
@@ -4202,6 +4776,7 @@
       <x:c r="C546" s="19"/>
       <x:c r="D546" s="19"/>
       <x:c r="E546" s="17"/>
+      <x:c r="F546" s="28"/>
     </x:row>
     <x:row r="547">
       <x:c r="A547" s="18"/>
@@ -4209,6 +4784,7 @@
       <x:c r="C547" s="19"/>
       <x:c r="D547" s="19"/>
       <x:c r="E547" s="17"/>
+      <x:c r="F547" s="28"/>
     </x:row>
     <x:row r="548">
       <x:c r="A548" s="18"/>
@@ -4216,6 +4792,7 @@
       <x:c r="C548" s="19"/>
       <x:c r="D548" s="19"/>
       <x:c r="E548" s="17"/>
+      <x:c r="F548" s="28"/>
     </x:row>
     <x:row r="549">
       <x:c r="A549" s="18"/>
@@ -4223,6 +4800,7 @@
       <x:c r="C549" s="19"/>
       <x:c r="D549" s="19"/>
       <x:c r="E549" s="17"/>
+      <x:c r="F549" s="28"/>
     </x:row>
     <x:row r="550">
       <x:c r="A550" s="18"/>
@@ -4230,6 +4808,7 @@
       <x:c r="C550" s="19"/>
       <x:c r="D550" s="19"/>
       <x:c r="E550" s="17"/>
+      <x:c r="F550" s="28"/>
     </x:row>
     <x:row r="551">
       <x:c r="A551" s="18"/>
@@ -4237,6 +4816,7 @@
       <x:c r="C551" s="19"/>
       <x:c r="D551" s="19"/>
       <x:c r="E551" s="17"/>
+      <x:c r="F551" s="28"/>
     </x:row>
     <x:row r="552">
       <x:c r="A552" s="18"/>
@@ -4244,6 +4824,7 @@
       <x:c r="C552" s="19"/>
       <x:c r="D552" s="19"/>
       <x:c r="E552" s="17"/>
+      <x:c r="F552" s="28"/>
     </x:row>
     <x:row r="553">
       <x:c r="A553" s="18"/>
@@ -4251,6 +4832,7 @@
       <x:c r="C553" s="19"/>
       <x:c r="D553" s="19"/>
       <x:c r="E553" s="17"/>
+      <x:c r="F553" s="28"/>
     </x:row>
     <x:row r="554">
       <x:c r="A554" s="18"/>
@@ -4258,6 +4840,7 @@
       <x:c r="C554" s="19"/>
       <x:c r="D554" s="19"/>
       <x:c r="E554" s="17"/>
+      <x:c r="F554" s="28"/>
     </x:row>
     <x:row r="555">
       <x:c r="A555" s="18"/>
@@ -4265,6 +4848,7 @@
       <x:c r="C555" s="19"/>
       <x:c r="D555" s="19"/>
       <x:c r="E555" s="17"/>
+      <x:c r="F555" s="28"/>
     </x:row>
     <x:row r="556">
       <x:c r="A556" s="18"/>
@@ -4272,6 +4856,7 @@
       <x:c r="C556" s="19"/>
       <x:c r="D556" s="19"/>
       <x:c r="E556" s="17"/>
+      <x:c r="F556" s="28"/>
     </x:row>
     <x:row r="557">
       <x:c r="A557" s="18"/>
@@ -4279,6 +4864,7 @@
       <x:c r="C557" s="19"/>
       <x:c r="D557" s="19"/>
       <x:c r="E557" s="17"/>
+      <x:c r="F557" s="28"/>
     </x:row>
     <x:row r="558">
       <x:c r="A558" s="18"/>
@@ -4286,6 +4872,7 @@
       <x:c r="C558" s="19"/>
       <x:c r="D558" s="19"/>
       <x:c r="E558" s="17"/>
+      <x:c r="F558" s="28"/>
     </x:row>
     <x:row r="559">
       <x:c r="A559" s="18"/>
@@ -4293,6 +4880,7 @@
       <x:c r="C559" s="19"/>
       <x:c r="D559" s="19"/>
       <x:c r="E559" s="17"/>
+      <x:c r="F559" s="28"/>
     </x:row>
     <x:row r="560">
       <x:c r="A560" s="18"/>
@@ -4300,6 +4888,7 @@
       <x:c r="C560" s="19"/>
       <x:c r="D560" s="19"/>
       <x:c r="E560" s="17"/>
+      <x:c r="F560" s="28"/>
     </x:row>
     <x:row r="561">
       <x:c r="A561" s="18"/>
@@ -4307,6 +4896,7 @@
       <x:c r="C561" s="19"/>
       <x:c r="D561" s="19"/>
       <x:c r="E561" s="17"/>
+      <x:c r="F561" s="28"/>
     </x:row>
     <x:row r="562">
       <x:c r="A562" s="18"/>
@@ -4314,6 +4904,7 @@
       <x:c r="C562" s="19"/>
       <x:c r="D562" s="19"/>
       <x:c r="E562" s="17"/>
+      <x:c r="F562" s="28"/>
     </x:row>
     <x:row r="563">
       <x:c r="A563" s="18"/>
@@ -4321,6 +4912,7 @@
       <x:c r="C563" s="19"/>
       <x:c r="D563" s="19"/>
       <x:c r="E563" s="17"/>
+      <x:c r="F563" s="28"/>
     </x:row>
     <x:row r="564">
       <x:c r="A564" s="18"/>
@@ -4328,6 +4920,7 @@
       <x:c r="C564" s="19"/>
       <x:c r="D564" s="19"/>
       <x:c r="E564" s="17"/>
+      <x:c r="F564" s="28"/>
     </x:row>
     <x:row r="565">
       <x:c r="A565" s="18"/>
@@ -4335,6 +4928,7 @@
       <x:c r="C565" s="19"/>
       <x:c r="D565" s="19"/>
       <x:c r="E565" s="17"/>
+      <x:c r="F565" s="28"/>
     </x:row>
     <x:row r="566">
       <x:c r="A566" s="18"/>
@@ -4342,6 +4936,7 @@
       <x:c r="C566" s="19"/>
       <x:c r="D566" s="19"/>
       <x:c r="E566" s="17"/>
+      <x:c r="F566" s="28"/>
     </x:row>
     <x:row r="567">
       <x:c r="A567" s="18"/>
@@ -4349,6 +4944,7 @@
       <x:c r="C567" s="19"/>
       <x:c r="D567" s="19"/>
       <x:c r="E567" s="17"/>
+      <x:c r="F567" s="28"/>
     </x:row>
     <x:row r="568">
       <x:c r="A568" s="18"/>
@@ -4356,6 +4952,7 @@
       <x:c r="C568" s="19"/>
       <x:c r="D568" s="19"/>
       <x:c r="E568" s="17"/>
+      <x:c r="F568" s="28"/>
     </x:row>
     <x:row r="569">
       <x:c r="A569" s="18"/>
@@ -4363,6 +4960,7 @@
       <x:c r="C569" s="19"/>
       <x:c r="D569" s="19"/>
       <x:c r="E569" s="17"/>
+      <x:c r="F569" s="28"/>
     </x:row>
     <x:row r="570">
       <x:c r="A570" s="18"/>
@@ -4370,6 +4968,7 @@
       <x:c r="C570" s="19"/>
       <x:c r="D570" s="19"/>
       <x:c r="E570" s="17"/>
+      <x:c r="F570" s="28"/>
     </x:row>
     <x:row r="571">
       <x:c r="A571" s="18"/>
@@ -4377,6 +4976,7 @@
       <x:c r="C571" s="19"/>
       <x:c r="D571" s="19"/>
       <x:c r="E571" s="17"/>
+      <x:c r="F571" s="28"/>
     </x:row>
     <x:row r="572">
       <x:c r="A572" s="18"/>
@@ -4384,6 +4984,7 @@
       <x:c r="C572" s="19"/>
       <x:c r="D572" s="19"/>
       <x:c r="E572" s="17"/>
+      <x:c r="F572" s="28"/>
     </x:row>
     <x:row r="573">
       <x:c r="A573" s="18"/>
@@ -4391,6 +4992,7 @@
       <x:c r="C573" s="19"/>
       <x:c r="D573" s="19"/>
       <x:c r="E573" s="17"/>
+      <x:c r="F573" s="28"/>
     </x:row>
     <x:row r="574">
       <x:c r="A574" s="18"/>
@@ -4398,6 +5000,7 @@
       <x:c r="C574" s="19"/>
       <x:c r="D574" s="19"/>
       <x:c r="E574" s="17"/>
+      <x:c r="F574" s="28"/>
     </x:row>
     <x:row r="575">
       <x:c r="A575" s="18"/>
@@ -4405,6 +5008,7 @@
       <x:c r="C575" s="19"/>
       <x:c r="D575" s="19"/>
       <x:c r="E575" s="17"/>
+      <x:c r="F575" s="28"/>
     </x:row>
     <x:row r="576">
       <x:c r="A576" s="18"/>
@@ -4412,6 +5016,7 @@
       <x:c r="C576" s="19"/>
       <x:c r="D576" s="19"/>
       <x:c r="E576" s="17"/>
+      <x:c r="F576" s="28"/>
     </x:row>
     <x:row r="577">
       <x:c r="A577" s="18"/>
@@ -4419,6 +5024,7 @@
       <x:c r="C577" s="19"/>
       <x:c r="D577" s="19"/>
       <x:c r="E577" s="17"/>
+      <x:c r="F577" s="28"/>
     </x:row>
     <x:row r="578">
       <x:c r="A578" s="18"/>
@@ -4426,6 +5032,7 @@
       <x:c r="C578" s="19"/>
       <x:c r="D578" s="19"/>
       <x:c r="E578" s="17"/>
+      <x:c r="F578" s="28"/>
     </x:row>
     <x:row r="579">
       <x:c r="A579" s="18"/>
@@ -4433,6 +5040,7 @@
       <x:c r="C579" s="19"/>
       <x:c r="D579" s="19"/>
       <x:c r="E579" s="17"/>
+      <x:c r="F579" s="28"/>
     </x:row>
     <x:row r="580">
       <x:c r="A580" s="18"/>
@@ -4440,6 +5048,7 @@
       <x:c r="C580" s="19"/>
       <x:c r="D580" s="19"/>
       <x:c r="E580" s="17"/>
+      <x:c r="F580" s="28"/>
     </x:row>
     <x:row r="581">
       <x:c r="A581" s="18"/>
@@ -4447,6 +5056,7 @@
       <x:c r="C581" s="19"/>
       <x:c r="D581" s="19"/>
       <x:c r="E581" s="17"/>
+      <x:c r="F581" s="28"/>
     </x:row>
     <x:row r="582">
       <x:c r="A582" s="18"/>
@@ -4454,6 +5064,7 @@
       <x:c r="C582" s="19"/>
       <x:c r="D582" s="19"/>
       <x:c r="E582" s="17"/>
+      <x:c r="F582" s="28"/>
     </x:row>
     <x:row r="583">
       <x:c r="A583" s="18"/>
@@ -4461,6 +5072,7 @@
       <x:c r="C583" s="19"/>
       <x:c r="D583" s="19"/>
       <x:c r="E583" s="17"/>
+      <x:c r="F583" s="28"/>
     </x:row>
     <x:row r="584">
       <x:c r="A584" s="18"/>
@@ -4468,6 +5080,7 @@
       <x:c r="C584" s="19"/>
       <x:c r="D584" s="19"/>
       <x:c r="E584" s="17"/>
+      <x:c r="F584" s="28"/>
     </x:row>
     <x:row r="585">
       <x:c r="A585" s="18"/>
@@ -4475,6 +5088,7 @@
       <x:c r="C585" s="19"/>
       <x:c r="D585" s="19"/>
       <x:c r="E585" s="17"/>
+      <x:c r="F585" s="28"/>
     </x:row>
     <x:row r="586">
       <x:c r="A586" s="18"/>
@@ -4482,6 +5096,7 @@
       <x:c r="C586" s="19"/>
       <x:c r="D586" s="19"/>
       <x:c r="E586" s="17"/>
+      <x:c r="F586" s="28"/>
     </x:row>
     <x:row r="587">
       <x:c r="A587" s="18"/>
@@ -4489,6 +5104,7 @@
       <x:c r="C587" s="19"/>
       <x:c r="D587" s="19"/>
       <x:c r="E587" s="17"/>
+      <x:c r="F587" s="28"/>
     </x:row>
     <x:row r="588">
       <x:c r="A588" s="18"/>
@@ -4496,6 +5112,7 @@
       <x:c r="C588" s="19"/>
       <x:c r="D588" s="19"/>
       <x:c r="E588" s="17"/>
+      <x:c r="F588" s="28"/>
     </x:row>
     <x:row r="589">
       <x:c r="A589" s="18"/>
@@ -4503,6 +5120,7 @@
       <x:c r="C589" s="19"/>
       <x:c r="D589" s="19"/>
       <x:c r="E589" s="17"/>
+      <x:c r="F589" s="28"/>
     </x:row>
     <x:row r="590">
       <x:c r="A590" s="18"/>
@@ -4510,6 +5128,7 @@
       <x:c r="C590" s="19"/>
       <x:c r="D590" s="19"/>
       <x:c r="E590" s="17"/>
+      <x:c r="F590" s="28"/>
     </x:row>
     <x:row r="591">
       <x:c r="A591" s="18"/>
@@ -4517,6 +5136,7 @@
       <x:c r="C591" s="19"/>
       <x:c r="D591" s="19"/>
       <x:c r="E591" s="17"/>
+      <x:c r="F591" s="28"/>
     </x:row>
     <x:row r="592">
       <x:c r="A592" s="18"/>
@@ -4524,6 +5144,7 @@
       <x:c r="C592" s="19"/>
       <x:c r="D592" s="19"/>
       <x:c r="E592" s="17"/>
+      <x:c r="F592" s="28"/>
     </x:row>
     <x:row r="593">
       <x:c r="A593" s="18"/>
@@ -4531,6 +5152,7 @@
       <x:c r="C593" s="19"/>
       <x:c r="D593" s="19"/>
       <x:c r="E593" s="17"/>
+      <x:c r="F593" s="28"/>
     </x:row>
     <x:row r="594">
       <x:c r="A594" s="18"/>
@@ -4538,6 +5160,7 @@
       <x:c r="C594" s="19"/>
       <x:c r="D594" s="19"/>
       <x:c r="E594" s="17"/>
+      <x:c r="F594" s="28"/>
     </x:row>
     <x:row r="595">
       <x:c r="A595" s="18"/>
@@ -4545,6 +5168,7 @@
       <x:c r="C595" s="19"/>
       <x:c r="D595" s="19"/>
       <x:c r="E595" s="17"/>
+      <x:c r="F595" s="28"/>
     </x:row>
     <x:row r="596">
       <x:c r="A596" s="18"/>
@@ -4552,6 +5176,7 @@
       <x:c r="C596" s="19"/>
       <x:c r="D596" s="19"/>
       <x:c r="E596" s="17"/>
+      <x:c r="F596" s="28"/>
     </x:row>
     <x:row r="597">
       <x:c r="A597" s="18"/>
@@ -4559,6 +5184,7 @@
       <x:c r="C597" s="19"/>
       <x:c r="D597" s="19"/>
       <x:c r="E597" s="17"/>
+      <x:c r="F597" s="28"/>
     </x:row>
     <x:row r="598">
       <x:c r="A598" s="18"/>
@@ -4566,6 +5192,7 @@
       <x:c r="C598" s="19"/>
       <x:c r="D598" s="19"/>
       <x:c r="E598" s="17"/>
+      <x:c r="F598" s="28"/>
     </x:row>
     <x:row r="599">
       <x:c r="A599" s="18"/>
@@ -4573,6 +5200,7 @@
       <x:c r="C599" s="19"/>
       <x:c r="D599" s="19"/>
       <x:c r="E599" s="17"/>
+      <x:c r="F599" s="28"/>
     </x:row>
     <x:row r="600">
       <x:c r="A600" s="18"/>
@@ -4580,6 +5208,7 @@
       <x:c r="C600" s="19"/>
       <x:c r="D600" s="19"/>
       <x:c r="E600" s="17"/>
+      <x:c r="F600" s="28"/>
     </x:row>
     <x:row r="601">
       <x:c r="A601" s="18"/>
@@ -4587,6 +5216,7 @@
       <x:c r="C601" s="19"/>
       <x:c r="D601" s="19"/>
       <x:c r="E601" s="17"/>
+      <x:c r="F601" s="28"/>
     </x:row>
     <x:row r="602">
       <x:c r="A602" s="18"/>
@@ -4594,6 +5224,7 @@
       <x:c r="C602" s="19"/>
       <x:c r="D602" s="19"/>
       <x:c r="E602" s="17"/>
+      <x:c r="F602" s="28"/>
     </x:row>
     <x:row r="603">
       <x:c r="A603" s="18"/>
@@ -4601,6 +5232,7 @@
       <x:c r="C603" s="19"/>
       <x:c r="D603" s="19"/>
       <x:c r="E603" s="17"/>
+      <x:c r="F603" s="28"/>
     </x:row>
     <x:row r="604">
       <x:c r="A604" s="18"/>
@@ -4608,6 +5240,7 @@
       <x:c r="C604" s="19"/>
       <x:c r="D604" s="19"/>
       <x:c r="E604" s="17"/>
+      <x:c r="F604" s="28"/>
     </x:row>
     <x:row r="605">
       <x:c r="A605" s="18"/>
@@ -4615,6 +5248,7 @@
       <x:c r="C605" s="19"/>
       <x:c r="D605" s="19"/>
       <x:c r="E605" s="17"/>
+      <x:c r="F605" s="28"/>
     </x:row>
     <x:row r="606">
       <x:c r="A606" s="18"/>
@@ -4622,6 +5256,7 @@
       <x:c r="C606" s="19"/>
       <x:c r="D606" s="19"/>
       <x:c r="E606" s="17"/>
+      <x:c r="F606" s="28"/>
     </x:row>
     <x:row r="607">
       <x:c r="A607" s="18"/>
@@ -4629,6 +5264,7 @@
       <x:c r="C607" s="19"/>
       <x:c r="D607" s="19"/>
       <x:c r="E607" s="17"/>
+      <x:c r="F607" s="28"/>
     </x:row>
     <x:row r="608">
       <x:c r="A608" s="18"/>
@@ -4636,6 +5272,7 @@
       <x:c r="C608" s="19"/>
       <x:c r="D608" s="19"/>
       <x:c r="E608" s="17"/>
+      <x:c r="F608" s="28"/>
     </x:row>
     <x:row r="609">
       <x:c r="A609" s="18"/>
@@ -4643,6 +5280,7 @@
       <x:c r="C609" s="19"/>
       <x:c r="D609" s="19"/>
       <x:c r="E609" s="17"/>
+      <x:c r="F609" s="28"/>
     </x:row>
     <x:row r="610">
       <x:c r="A610" s="18"/>
@@ -4650,6 +5288,7 @@
       <x:c r="C610" s="19"/>
       <x:c r="D610" s="19"/>
       <x:c r="E610" s="17"/>
+      <x:c r="F610" s="28"/>
     </x:row>
     <x:row r="611">
       <x:c r="A611" s="18"/>
@@ -4657,6 +5296,7 @@
       <x:c r="C611" s="19"/>
       <x:c r="D611" s="19"/>
       <x:c r="E611" s="17"/>
+      <x:c r="F611" s="28"/>
     </x:row>
     <x:row r="612">
       <x:c r="A612" s="18"/>
@@ -4664,6 +5304,7 @@
       <x:c r="C612" s="19"/>
       <x:c r="D612" s="19"/>
       <x:c r="E612" s="17"/>
+      <x:c r="F612" s="28"/>
     </x:row>
     <x:row r="613">
       <x:c r="A613" s="18"/>
@@ -4671,6 +5312,7 @@
       <x:c r="C613" s="19"/>
       <x:c r="D613" s="19"/>
       <x:c r="E613" s="17"/>
+      <x:c r="F613" s="28"/>
     </x:row>
     <x:row r="614">
       <x:c r="A614" s="18"/>
@@ -4678,6 +5320,7 @@
       <x:c r="C614" s="19"/>
       <x:c r="D614" s="19"/>
       <x:c r="E614" s="17"/>
+      <x:c r="F614" s="28"/>
     </x:row>
     <x:row r="615">
       <x:c r="A615" s="18"/>
@@ -4685,6 +5328,7 @@
       <x:c r="C615" s="19"/>
       <x:c r="D615" s="19"/>
       <x:c r="E615" s="17"/>
+      <x:c r="F615" s="28"/>
     </x:row>
     <x:row r="616">
       <x:c r="A616" s="18"/>
@@ -4692,6 +5336,7 @@
       <x:c r="C616" s="19"/>
       <x:c r="D616" s="19"/>
       <x:c r="E616" s="17"/>
+      <x:c r="F616" s="28"/>
     </x:row>
     <x:row r="617">
       <x:c r="A617" s="18"/>
@@ -4699,6 +5344,7 @@
       <x:c r="C617" s="19"/>
       <x:c r="D617" s="19"/>
       <x:c r="E617" s="17"/>
+      <x:c r="F617" s="28"/>
     </x:row>
     <x:row r="618">
       <x:c r="A618" s="18"/>
@@ -4706,6 +5352,7 @@
       <x:c r="C618" s="19"/>
       <x:c r="D618" s="19"/>
       <x:c r="E618" s="17"/>
+      <x:c r="F618" s="28"/>
     </x:row>
     <x:row r="619">
       <x:c r="A619" s="18"/>
@@ -4713,6 +5360,7 @@
       <x:c r="C619" s="19"/>
       <x:c r="D619" s="19"/>
       <x:c r="E619" s="17"/>
+      <x:c r="F619" s="28"/>
     </x:row>
     <x:row r="620">
       <x:c r="A620" s="18"/>
@@ -4720,6 +5368,7 @@
       <x:c r="C620" s="19"/>
       <x:c r="D620" s="19"/>
       <x:c r="E620" s="17"/>
+      <x:c r="F620" s="28"/>
     </x:row>
     <x:row r="621">
       <x:c r="A621" s="18"/>
@@ -4727,6 +5376,7 @@
       <x:c r="C621" s="19"/>
       <x:c r="D621" s="19"/>
       <x:c r="E621" s="17"/>
+      <x:c r="F621" s="28"/>
     </x:row>
     <x:row r="622">
       <x:c r="A622" s="18"/>
@@ -4734,6 +5384,7 @@
       <x:c r="C622" s="19"/>
       <x:c r="D622" s="19"/>
       <x:c r="E622" s="17"/>
+      <x:c r="F622" s="28"/>
     </x:row>
     <x:row r="623">
       <x:c r="A623" s="18"/>
@@ -4741,6 +5392,7 @@
       <x:c r="C623" s="19"/>
       <x:c r="D623" s="19"/>
       <x:c r="E623" s="17"/>
+      <x:c r="F623" s="28"/>
     </x:row>
     <x:row r="624">
       <x:c r="A624" s="18"/>
@@ -4748,6 +5400,7 @@
       <x:c r="C624" s="19"/>
       <x:c r="D624" s="19"/>
       <x:c r="E624" s="17"/>
+      <x:c r="F624" s="28"/>
     </x:row>
     <x:row r="625">
       <x:c r="A625" s="18"/>
@@ -4755,6 +5408,7 @@
       <x:c r="C625" s="19"/>
       <x:c r="D625" s="19"/>
       <x:c r="E625" s="17"/>
+      <x:c r="F625" s="28"/>
     </x:row>
     <x:row r="626">
       <x:c r="A626" s="18"/>
@@ -4762,6 +5416,7 @@
       <x:c r="C626" s="19"/>
       <x:c r="D626" s="19"/>
       <x:c r="E626" s="17"/>
+      <x:c r="F626" s="28"/>
     </x:row>
     <x:row r="627">
       <x:c r="A627" s="18"/>
@@ -4769,6 +5424,7 @@
       <x:c r="C627" s="19"/>
       <x:c r="D627" s="19"/>
       <x:c r="E627" s="17"/>
+      <x:c r="F627" s="28"/>
     </x:row>
     <x:row r="628">
       <x:c r="A628" s="18"/>
@@ -4776,6 +5432,7 @@
       <x:c r="C628" s="19"/>
       <x:c r="D628" s="19"/>
       <x:c r="E628" s="17"/>
+      <x:c r="F628" s="28"/>
     </x:row>
     <x:row r="629">
       <x:c r="A629" s="18"/>
@@ -4783,6 +5440,7 @@
       <x:c r="C629" s="19"/>
       <x:c r="D629" s="19"/>
       <x:c r="E629" s="17"/>
+      <x:c r="F629" s="28"/>
     </x:row>
     <x:row r="630">
       <x:c r="A630" s="18"/>
@@ -4790,6 +5448,7 @@
       <x:c r="C630" s="19"/>
       <x:c r="D630" s="19"/>
       <x:c r="E630" s="17"/>
+      <x:c r="F630" s="28"/>
     </x:row>
     <x:row r="631">
       <x:c r="A631" s="18"/>
@@ -4797,6 +5456,7 @@
       <x:c r="C631" s="19"/>
       <x:c r="D631" s="19"/>
       <x:c r="E631" s="17"/>
+      <x:c r="F631" s="28"/>
     </x:row>
     <x:row r="632">
       <x:c r="A632" s="18"/>
@@ -4804,6 +5464,7 @@
       <x:c r="C632" s="19"/>
       <x:c r="D632" s="19"/>
       <x:c r="E632" s="17"/>
+      <x:c r="F632" s="28"/>
     </x:row>
     <x:row r="633">
       <x:c r="A633" s="18"/>
@@ -4811,6 +5472,7 @@
       <x:c r="C633" s="19"/>
       <x:c r="D633" s="19"/>
       <x:c r="E633" s="17"/>
+      <x:c r="F633" s="28"/>
     </x:row>
     <x:row r="634">
       <x:c r="A634" s="18"/>
@@ -4818,6 +5480,7 @@
       <x:c r="C634" s="19"/>
       <x:c r="D634" s="19"/>
       <x:c r="E634" s="17"/>
+      <x:c r="F634" s="28"/>
     </x:row>
     <x:row r="635">
       <x:c r="A635" s="18"/>
@@ -4825,6 +5488,7 @@
       <x:c r="C635" s="19"/>
       <x:c r="D635" s="19"/>
       <x:c r="E635" s="17"/>
+      <x:c r="F635" s="28"/>
     </x:row>
     <x:row r="636">
       <x:c r="A636" s="18"/>
@@ -4832,6 +5496,7 @@
       <x:c r="C636" s="19"/>
       <x:c r="D636" s="19"/>
       <x:c r="E636" s="17"/>
+      <x:c r="F636" s="28"/>
     </x:row>
     <x:row r="637">
       <x:c r="A637" s="18"/>
@@ -4839,6 +5504,7 @@
       <x:c r="C637" s="19"/>
       <x:c r="D637" s="19"/>
       <x:c r="E637" s="17"/>
+      <x:c r="F637" s="28"/>
     </x:row>
     <x:row r="638">
       <x:c r="A638" s="18"/>
@@ -4846,6 +5512,7 @@
       <x:c r="C638" s="19"/>
       <x:c r="D638" s="19"/>
       <x:c r="E638" s="17"/>
+      <x:c r="F638" s="28"/>
     </x:row>
     <x:row r="639">
       <x:c r="A639" s="18"/>
@@ -4853,6 +5520,7 @@
       <x:c r="C639" s="19"/>
       <x:c r="D639" s="19"/>
       <x:c r="E639" s="17"/>
+      <x:c r="F639" s="28"/>
     </x:row>
     <x:row r="640">
       <x:c r="A640" s="18"/>
@@ -4860,6 +5528,7 @@
       <x:c r="C640" s="19"/>
       <x:c r="D640" s="19"/>
       <x:c r="E640" s="17"/>
+      <x:c r="F640" s="28"/>
     </x:row>
     <x:row r="641">
       <x:c r="A641" s="18"/>
@@ -4867,6 +5536,7 @@
       <x:c r="C641" s="19"/>
       <x:c r="D641" s="19"/>
       <x:c r="E641" s="17"/>
+      <x:c r="F641" s="28"/>
     </x:row>
     <x:row r="642">
       <x:c r="A642" s="18"/>
@@ -4874,6 +5544,7 @@
       <x:c r="C642" s="19"/>
       <x:c r="D642" s="19"/>
       <x:c r="E642" s="17"/>
+      <x:c r="F642" s="28"/>
     </x:row>
     <x:row r="643">
       <x:c r="A643" s="18"/>
@@ -4881,6 +5552,7 @@
       <x:c r="C643" s="19"/>
       <x:c r="D643" s="19"/>
       <x:c r="E643" s="17"/>
+      <x:c r="F643" s="28"/>
     </x:row>
     <x:row r="644">
       <x:c r="A644" s="18"/>
@@ -4888,6 +5560,7 @@
       <x:c r="C644" s="19"/>
       <x:c r="D644" s="19"/>
       <x:c r="E644" s="17"/>
+      <x:c r="F644" s="28"/>
     </x:row>
     <x:row r="645">
       <x:c r="A645" s="18"/>
@@ -4895,6 +5568,7 @@
       <x:c r="C645" s="19"/>
       <x:c r="D645" s="19"/>
       <x:c r="E645" s="17"/>
+      <x:c r="F645" s="28"/>
     </x:row>
     <x:row r="646">
       <x:c r="A646" s="18"/>
@@ -4902,6 +5576,7 @@
       <x:c r="C646" s="19"/>
       <x:c r="D646" s="19"/>
       <x:c r="E646" s="17"/>
+      <x:c r="F646" s="28"/>
     </x:row>
     <x:row r="647">
       <x:c r="A647" s="18"/>
@@ -4909,6 +5584,7 @@
       <x:c r="C647" s="19"/>
       <x:c r="D647" s="19"/>
       <x:c r="E647" s="17"/>
+      <x:c r="F647" s="28"/>
     </x:row>
     <x:row r="648">
       <x:c r="A648" s="18"/>
@@ -4916,6 +5592,7 @@
       <x:c r="C648" s="19"/>
       <x:c r="D648" s="19"/>
       <x:c r="E648" s="17"/>
+      <x:c r="F648" s="28"/>
     </x:row>
     <x:row r="649">
       <x:c r="A649" s="18"/>
@@ -4923,6 +5600,7 @@
       <x:c r="C649" s="19"/>
       <x:c r="D649" s="19"/>
       <x:c r="E649" s="17"/>
+      <x:c r="F649" s="28"/>
     </x:row>
     <x:row r="650">
       <x:c r="A650" s="18"/>
@@ -4930,6 +5608,7 @@
       <x:c r="C650" s="19"/>
       <x:c r="D650" s="19"/>
       <x:c r="E650" s="17"/>
+      <x:c r="F650" s="28"/>
     </x:row>
     <x:row r="651">
       <x:c r="A651" s="18"/>
@@ -4937,6 +5616,7 @@
       <x:c r="C651" s="19"/>
       <x:c r="D651" s="19"/>
       <x:c r="E651" s="17"/>
+      <x:c r="F651" s="28"/>
     </x:row>
     <x:row r="652">
       <x:c r="A652" s="18"/>
@@ -4944,6 +5624,7 @@
       <x:c r="C652" s="19"/>
       <x:c r="D652" s="19"/>
       <x:c r="E652" s="17"/>
+      <x:c r="F652" s="28"/>
     </x:row>
     <x:row r="653">
       <x:c r="A653" s="18"/>
@@ -4951,6 +5632,7 @@
       <x:c r="C653" s="19"/>
       <x:c r="D653" s="19"/>
       <x:c r="E653" s="17"/>
+      <x:c r="F653" s="28"/>
     </x:row>
     <x:row r="654">
       <x:c r="A654" s="18"/>
@@ -4958,6 +5640,7 @@
       <x:c r="C654" s="19"/>
       <x:c r="D654" s="19"/>
       <x:c r="E654" s="17"/>
+      <x:c r="F654" s="28"/>
     </x:row>
     <x:row r="655">
       <x:c r="A655" s="18"/>
@@ -4965,6 +5648,7 @@
       <x:c r="C655" s="19"/>
       <x:c r="D655" s="19"/>
       <x:c r="E655" s="17"/>
+      <x:c r="F655" s="28"/>
     </x:row>
     <x:row r="656">
       <x:c r="A656" s="18"/>
@@ -4972,6 +5656,7 @@
       <x:c r="C656" s="19"/>
       <x:c r="D656" s="19"/>
       <x:c r="E656" s="17"/>
+      <x:c r="F656" s="28"/>
     </x:row>
     <x:row r="657">
       <x:c r="A657" s="18"/>
@@ -4979,6 +5664,7 @@
       <x:c r="C657" s="19"/>
       <x:c r="D657" s="19"/>
       <x:c r="E657" s="17"/>
+      <x:c r="F657" s="28"/>
     </x:row>
     <x:row r="658">
       <x:c r="A658" s="18"/>
@@ -4986,6 +5672,7 @@
       <x:c r="C658" s="19"/>
       <x:c r="D658" s="19"/>
       <x:c r="E658" s="17"/>
+      <x:c r="F658" s="28"/>
     </x:row>
     <x:row r="659">
       <x:c r="A659" s="18"/>
@@ -4993,6 +5680,7 @@
       <x:c r="C659" s="19"/>
       <x:c r="D659" s="19"/>
       <x:c r="E659" s="17"/>
+      <x:c r="F659" s="28"/>
     </x:row>
     <x:row r="660">
       <x:c r="A660" s="18"/>
@@ -5000,6 +5688,7 @@
       <x:c r="C660" s="19"/>
       <x:c r="D660" s="19"/>
       <x:c r="E660" s="17"/>
+      <x:c r="F660" s="28"/>
     </x:row>
     <x:row r="661">
       <x:c r="A661" s="18"/>
@@ -5007,6 +5696,7 @@
       <x:c r="C661" s="19"/>
       <x:c r="D661" s="19"/>
       <x:c r="E661" s="17"/>
+      <x:c r="F661" s="28"/>
     </x:row>
     <x:row r="662">
       <x:c r="A662" s="18"/>
@@ -5014,6 +5704,7 @@
       <x:c r="C662" s="19"/>
       <x:c r="D662" s="19"/>
       <x:c r="E662" s="17"/>
+      <x:c r="F662" s="28"/>
     </x:row>
     <x:row r="663">
       <x:c r="A663" s="18"/>
@@ -5021,6 +5712,7 @@
       <x:c r="C663" s="19"/>
       <x:c r="D663" s="19"/>
       <x:c r="E663" s="17"/>
+      <x:c r="F663" s="28"/>
     </x:row>
     <x:row r="664">
       <x:c r="A664" s="18"/>
@@ -5028,6 +5720,7 @@
       <x:c r="C664" s="19"/>
       <x:c r="D664" s="19"/>
       <x:c r="E664" s="17"/>
+      <x:c r="F664" s="28"/>
     </x:row>
     <x:row r="665">
       <x:c r="A665" s="18"/>
@@ -5035,6 +5728,7 @@
       <x:c r="C665" s="19"/>
       <x:c r="D665" s="19"/>
       <x:c r="E665" s="17"/>
+      <x:c r="F665" s="28"/>
     </x:row>
     <x:row r="666">
       <x:c r="A666" s="18"/>
@@ -5042,6 +5736,7 @@
       <x:c r="C666" s="19"/>
       <x:c r="D666" s="19"/>
       <x:c r="E666" s="17"/>
+      <x:c r="F666" s="28"/>
     </x:row>
     <x:row r="667">
       <x:c r="A667" s="18"/>
@@ -5049,6 +5744,7 @@
       <x:c r="C667" s="19"/>
       <x:c r="D667" s="19"/>
       <x:c r="E667" s="17"/>
+      <x:c r="F667" s="28"/>
     </x:row>
     <x:row r="668">
       <x:c r="A668" s="18"/>
@@ -5056,6 +5752,7 @@
       <x:c r="C668" s="19"/>
       <x:c r="D668" s="19"/>
       <x:c r="E668" s="17"/>
+      <x:c r="F668" s="28"/>
     </x:row>
     <x:row r="669">
       <x:c r="A669" s="18"/>
@@ -5063,6 +5760,7 @@
       <x:c r="C669" s="19"/>
       <x:c r="D669" s="19"/>
       <x:c r="E669" s="17"/>
+      <x:c r="F669" s="28"/>
     </x:row>
     <x:row r="670">
       <x:c r="A670" s="18"/>
@@ -5070,6 +5768,7 @@
       <x:c r="C670" s="19"/>
       <x:c r="D670" s="19"/>
       <x:c r="E670" s="17"/>
+      <x:c r="F670" s="28"/>
     </x:row>
     <x:row r="671">
       <x:c r="A671" s="18"/>
@@ -5077,6 +5776,7 @@
       <x:c r="C671" s="19"/>
       <x:c r="D671" s="19"/>
       <x:c r="E671" s="17"/>
+      <x:c r="F671" s="28"/>
     </x:row>
     <x:row r="672">
       <x:c r="A672" s="18"/>
@@ -5084,6 +5784,7 @@
       <x:c r="C672" s="19"/>
       <x:c r="D672" s="19"/>
       <x:c r="E672" s="17"/>
+      <x:c r="F672" s="28"/>
     </x:row>
     <x:row r="673">
       <x:c r="A673" s="18"/>
@@ -5091,6 +5792,7 @@
       <x:c r="C673" s="19"/>
       <x:c r="D673" s="19"/>
       <x:c r="E673" s="17"/>
+      <x:c r="F673" s="28"/>
     </x:row>
     <x:row r="674">
       <x:c r="A674" s="18"/>
@@ -5098,6 +5800,7 @@
       <x:c r="C674" s="19"/>
       <x:c r="D674" s="19"/>
       <x:c r="E674" s="17"/>
+      <x:c r="F674" s="28"/>
     </x:row>
     <x:row r="675">
       <x:c r="A675" s="18"/>
@@ -5105,6 +5808,7 @@
       <x:c r="C675" s="19"/>
       <x:c r="D675" s="19"/>
       <x:c r="E675" s="17"/>
+      <x:c r="F675" s="28"/>
     </x:row>
     <x:row r="676">
       <x:c r="A676" s="18"/>
@@ -5112,6 +5816,7 @@
       <x:c r="C676" s="19"/>
       <x:c r="D676" s="19"/>
       <x:c r="E676" s="17"/>
+      <x:c r="F676" s="28"/>
     </x:row>
     <x:row r="677">
       <x:c r="A677" s="18"/>
@@ -5119,6 +5824,7 @@
       <x:c r="C677" s="19"/>
       <x:c r="D677" s="19"/>
       <x:c r="E677" s="17"/>
+      <x:c r="F677" s="28"/>
     </x:row>
     <x:row r="678">
       <x:c r="A678" s="18"/>
@@ -5126,6 +5832,7 @@
       <x:c r="C678" s="19"/>
       <x:c r="D678" s="19"/>
       <x:c r="E678" s="17"/>
+      <x:c r="F678" s="28"/>
     </x:row>
     <x:row r="679">
       <x:c r="A679" s="18"/>
@@ -5133,6 +5840,7 @@
       <x:c r="C679" s="19"/>
       <x:c r="D679" s="19"/>
       <x:c r="E679" s="17"/>
+      <x:c r="F679" s="28"/>
     </x:row>
     <x:row r="680">
       <x:c r="A680" s="18"/>
@@ -5140,6 +5848,7 @@
       <x:c r="C680" s="19"/>
       <x:c r="D680" s="19"/>
       <x:c r="E680" s="17"/>
+      <x:c r="F680" s="28"/>
     </x:row>
     <x:row r="681">
       <x:c r="A681" s="18"/>
@@ -5147,6 +5856,7 @@
       <x:c r="C681" s="19"/>
       <x:c r="D681" s="19"/>
       <x:c r="E681" s="17"/>
+      <x:c r="F681" s="28"/>
     </x:row>
     <x:row r="682">
       <x:c r="A682" s="18"/>
@@ -5154,6 +5864,7 @@
       <x:c r="C682" s="19"/>
       <x:c r="D682" s="19"/>
       <x:c r="E682" s="17"/>
+      <x:c r="F682" s="28"/>
     </x:row>
     <x:row r="683">
       <x:c r="A683" s="18"/>
@@ -5161,6 +5872,7 @@
       <x:c r="C683" s="19"/>
       <x:c r="D683" s="19"/>
       <x:c r="E683" s="17"/>
+      <x:c r="F683" s="28"/>
     </x:row>
     <x:row r="684">
       <x:c r="A684" s="18"/>
@@ -5168,6 +5880,7 @@
       <x:c r="C684" s="19"/>
       <x:c r="D684" s="19"/>
       <x:c r="E684" s="17"/>
+      <x:c r="F684" s="28"/>
     </x:row>
     <x:row r="685">
       <x:c r="A685" s="18"/>
@@ -5175,6 +5888,7 @@
       <x:c r="C685" s="19"/>
       <x:c r="D685" s="19"/>
       <x:c r="E685" s="17"/>
+      <x:c r="F685" s="28"/>
     </x:row>
     <x:row r="686">
       <x:c r="A686" s="18"/>
@@ -5182,6 +5896,7 @@
       <x:c r="C686" s="19"/>
       <x:c r="D686" s="19"/>
       <x:c r="E686" s="17"/>
+      <x:c r="F686" s="28"/>
     </x:row>
     <x:row r="687">
       <x:c r="A687" s="18"/>
@@ -5189,6 +5904,7 @@
       <x:c r="C687" s="19"/>
       <x:c r="D687" s="19"/>
       <x:c r="E687" s="17"/>
+      <x:c r="F687" s="28"/>
     </x:row>
     <x:row r="688">
       <x:c r="A688" s="18"/>
@@ -5196,6 +5912,7 @@
       <x:c r="C688" s="19"/>
       <x:c r="D688" s="19"/>
       <x:c r="E688" s="17"/>
+      <x:c r="F688" s="28"/>
     </x:row>
     <x:row r="689">
       <x:c r="A689" s="18"/>
@@ -5203,6 +5920,7 @@
       <x:c r="C689" s="19"/>
       <x:c r="D689" s="19"/>
       <x:c r="E689" s="17"/>
+      <x:c r="F689" s="28"/>
     </x:row>
     <x:row r="690">
       <x:c r="A690" s="18"/>
@@ -5210,6 +5928,7 @@
       <x:c r="C690" s="19"/>
       <x:c r="D690" s="19"/>
       <x:c r="E690" s="17"/>
+      <x:c r="F690" s="28"/>
     </x:row>
     <x:row r="691">
       <x:c r="A691" s="18"/>
@@ -5217,6 +5936,7 @@
       <x:c r="C691" s="19"/>
       <x:c r="D691" s="19"/>
       <x:c r="E691" s="17"/>
+      <x:c r="F691" s="28"/>
     </x:row>
     <x:row r="692">
       <x:c r="A692" s="18"/>
@@ -5224,6 +5944,7 @@
       <x:c r="C692" s="19"/>
       <x:c r="D692" s="19"/>
       <x:c r="E692" s="17"/>
+      <x:c r="F692" s="28"/>
     </x:row>
     <x:row r="693">
       <x:c r="A693" s="18"/>
@@ -5231,6 +5952,7 @@
       <x:c r="C693" s="19"/>
       <x:c r="D693" s="19"/>
       <x:c r="E693" s="17"/>
+      <x:c r="F693" s="28"/>
     </x:row>
     <x:row r="694">
       <x:c r="A694" s="18"/>
@@ -5238,6 +5960,7 @@
       <x:c r="C694" s="19"/>
       <x:c r="D694" s="19"/>
       <x:c r="E694" s="17"/>
+      <x:c r="F694" s="28"/>
     </x:row>
     <x:row r="695">
       <x:c r="A695" s="18"/>
@@ -5245,6 +5968,7 @@
       <x:c r="C695" s="19"/>
       <x:c r="D695" s="19"/>
       <x:c r="E695" s="17"/>
+      <x:c r="F695" s="28"/>
     </x:row>
     <x:row r="696">
       <x:c r="A696" s="18"/>
@@ -5252,6 +5976,7 @@
       <x:c r="C696" s="19"/>
       <x:c r="D696" s="19"/>
       <x:c r="E696" s="17"/>
+      <x:c r="F696" s="28"/>
     </x:row>
     <x:row r="697">
       <x:c r="A697" s="18"/>
@@ -5259,6 +5984,7 @@
       <x:c r="C697" s="19"/>
       <x:c r="D697" s="19"/>
       <x:c r="E697" s="17"/>
+      <x:c r="F697" s="28"/>
     </x:row>
     <x:row r="698">
       <x:c r="A698" s="18"/>
@@ -5266,6 +5992,7 @@
       <x:c r="C698" s="19"/>
       <x:c r="D698" s="19"/>
       <x:c r="E698" s="17"/>
+      <x:c r="F698" s="28"/>
     </x:row>
     <x:row r="699">
       <x:c r="A699" s="18"/>
@@ -5273,6 +6000,7 @@
       <x:c r="C699" s="19"/>
       <x:c r="D699" s="19"/>
       <x:c r="E699" s="17"/>
+      <x:c r="F699" s="28"/>
     </x:row>
     <x:row r="700">
       <x:c r="A700" s="18"/>
@@ -5280,6 +6008,7 @@
       <x:c r="C700" s="19"/>
       <x:c r="D700" s="19"/>
       <x:c r="E700" s="17"/>
+      <x:c r="F700" s="28"/>
     </x:row>
     <x:row r="701">
       <x:c r="A701" s="18"/>
@@ -5287,6 +6016,7 @@
       <x:c r="C701" s="19"/>
       <x:c r="D701" s="19"/>
       <x:c r="E701" s="17"/>
+      <x:c r="F701" s="28"/>
     </x:row>
     <x:row r="702">
       <x:c r="A702" s="18"/>
@@ -5294,6 +6024,7 @@
       <x:c r="C702" s="19"/>
       <x:c r="D702" s="19"/>
       <x:c r="E702" s="17"/>
+      <x:c r="F702" s="28"/>
     </x:row>
     <x:row r="703">
       <x:c r="A703" s="18"/>
@@ -5301,6 +6032,7 @@
       <x:c r="C703" s="19"/>
       <x:c r="D703" s="19"/>
       <x:c r="E703" s="17"/>
+      <x:c r="F703" s="28"/>
     </x:row>
     <x:row r="704">
       <x:c r="A704" s="18"/>
@@ -5308,6 +6040,7 @@
       <x:c r="C704" s="19"/>
       <x:c r="D704" s="19"/>
       <x:c r="E704" s="17"/>
+      <x:c r="F704" s="28"/>
     </x:row>
     <x:row r="705">
       <x:c r="A705" s="18"/>
@@ -5315,6 +6048,7 @@
       <x:c r="C705" s="19"/>
       <x:c r="D705" s="19"/>
       <x:c r="E705" s="17"/>
+      <x:c r="F705" s="28"/>
     </x:row>
     <x:row r="706">
       <x:c r="A706" s="18"/>
@@ -5322,6 +6056,7 @@
       <x:c r="C706" s="19"/>
       <x:c r="D706" s="19"/>
       <x:c r="E706" s="17"/>
+      <x:c r="F706" s="28"/>
     </x:row>
     <x:row r="707">
       <x:c r="A707" s="18"/>
@@ -5329,6 +6064,7 @@
       <x:c r="C707" s="19"/>
       <x:c r="D707" s="19"/>
       <x:c r="E707" s="17"/>
+      <x:c r="F707" s="28"/>
     </x:row>
     <x:row r="708">
       <x:c r="A708" s="18"/>
@@ -5336,6 +6072,7 @@
       <x:c r="C708" s="19"/>
       <x:c r="D708" s="19"/>
       <x:c r="E708" s="17"/>
+      <x:c r="F708" s="28"/>
     </x:row>
     <x:row r="709">
       <x:c r="A709" s="18"/>
@@ -5343,6 +6080,7 @@
       <x:c r="C709" s="19"/>
       <x:c r="D709" s="19"/>
       <x:c r="E709" s="17"/>
+      <x:c r="F709" s="28"/>
     </x:row>
     <x:row r="710">
       <x:c r="A710" s="18"/>
@@ -5350,6 +6088,7 @@
       <x:c r="C710" s="19"/>
       <x:c r="D710" s="19"/>
       <x:c r="E710" s="17"/>
+      <x:c r="F710" s="28"/>
     </x:row>
     <x:row r="711">
       <x:c r="A711" s="18"/>
@@ -5357,6 +6096,7 @@
       <x:c r="C711" s="19"/>
       <x:c r="D711" s="19"/>
       <x:c r="E711" s="17"/>
+      <x:c r="F711" s="28"/>
     </x:row>
     <x:row r="712">
       <x:c r="A712" s="18"/>
@@ -5364,6 +6104,7 @@
       <x:c r="C712" s="19"/>
       <x:c r="D712" s="19"/>
       <x:c r="E712" s="17"/>
+      <x:c r="F712" s="28"/>
     </x:row>
     <x:row r="713">
       <x:c r="A713" s="18"/>
@@ -5371,6 +6112,7 @@
       <x:c r="C713" s="19"/>
       <x:c r="D713" s="19"/>
       <x:c r="E713" s="17"/>
+      <x:c r="F713" s="28"/>
     </x:row>
     <x:row r="714">
       <x:c r="A714" s="18"/>
@@ -5378,6 +6120,7 @@
       <x:c r="C714" s="19"/>
       <x:c r="D714" s="19"/>
       <x:c r="E714" s="17"/>
+      <x:c r="F714" s="28"/>
     </x:row>
     <x:row r="715">
       <x:c r="A715" s="18"/>
@@ -5385,6 +6128,7 @@
       <x:c r="C715" s="19"/>
       <x:c r="D715" s="19"/>
       <x:c r="E715" s="17"/>
+      <x:c r="F715" s="28"/>
     </x:row>
     <x:row r="716">
       <x:c r="A716" s="18"/>
@@ -5392,6 +6136,7 @@
       <x:c r="C716" s="19"/>
       <x:c r="D716" s="19"/>
       <x:c r="E716" s="17"/>
+      <x:c r="F716" s="28"/>
     </x:row>
     <x:row r="717">
       <x:c r="A717" s="18"/>
@@ -5399,6 +6144,7 @@
       <x:c r="C717" s="19"/>
       <x:c r="D717" s="19"/>
       <x:c r="E717" s="17"/>
+      <x:c r="F717" s="28"/>
     </x:row>
     <x:row r="718">
       <x:c r="A718" s="18"/>
@@ -5406,6 +6152,7 @@
       <x:c r="C718" s="19"/>
       <x:c r="D718" s="19"/>
       <x:c r="E718" s="17"/>
+      <x:c r="F718" s="28"/>
     </x:row>
     <x:row r="719">
       <x:c r="A719" s="18"/>
@@ -5413,6 +6160,7 @@
       <x:c r="C719" s="19"/>
       <x:c r="D719" s="19"/>
       <x:c r="E719" s="17"/>
+      <x:c r="F719" s="28"/>
     </x:row>
     <x:row r="720">
       <x:c r="A720" s="18"/>
@@ -5420,6 +6168,7 @@
       <x:c r="C720" s="19"/>
       <x:c r="D720" s="19"/>
       <x:c r="E720" s="17"/>
+      <x:c r="F720" s="28"/>
     </x:row>
     <x:row r="721">
       <x:c r="A721" s="18"/>
@@ -5427,6 +6176,7 @@
       <x:c r="C721" s="19"/>
       <x:c r="D721" s="19"/>
       <x:c r="E721" s="17"/>
+      <x:c r="F721" s="28"/>
     </x:row>
     <x:row r="722">
       <x:c r="A722" s="18"/>
@@ -5434,6 +6184,7 @@
       <x:c r="C722" s="19"/>
       <x:c r="D722" s="19"/>
       <x:c r="E722" s="17"/>
+      <x:c r="F722" s="28"/>
     </x:row>
     <x:row r="723">
       <x:c r="A723" s="18"/>
@@ -5441,6 +6192,7 @@
       <x:c r="C723" s="19"/>
       <x:c r="D723" s="19"/>
       <x:c r="E723" s="17"/>
+      <x:c r="F723" s="28"/>
     </x:row>
     <x:row r="724">
       <x:c r="A724" s="18"/>
@@ -5448,6 +6200,7 @@
       <x:c r="C724" s="19"/>
       <x:c r="D724" s="19"/>
       <x:c r="E724" s="17"/>
+      <x:c r="F724" s="28"/>
     </x:row>
     <x:row r="725">
       <x:c r="A725" s="18"/>
@@ -5455,6 +6208,7 @@
       <x:c r="C725" s="19"/>
       <x:c r="D725" s="19"/>
       <x:c r="E725" s="17"/>
+      <x:c r="F725" s="28"/>
     </x:row>
     <x:row r="726">
       <x:c r="A726" s="18"/>
@@ -5462,6 +6216,7 @@
       <x:c r="C726" s="19"/>
       <x:c r="D726" s="19"/>
       <x:c r="E726" s="17"/>
+      <x:c r="F726" s="28"/>
     </x:row>
     <x:row r="727">
       <x:c r="A727" s="18"/>
@@ -5469,6 +6224,7 @@
       <x:c r="C727" s="19"/>
       <x:c r="D727" s="19"/>
       <x:c r="E727" s="17"/>
+      <x:c r="F727" s="28"/>
     </x:row>
     <x:row r="728">
       <x:c r="A728" s="18"/>
@@ -5476,6 +6232,7 @@
       <x:c r="C728" s="19"/>
       <x:c r="D728" s="19"/>
       <x:c r="E728" s="17"/>
+      <x:c r="F728" s="28"/>
     </x:row>
     <x:row r="729">
       <x:c r="A729" s="18"/>
@@ -5483,6 +6240,7 @@
       <x:c r="C729" s="19"/>
       <x:c r="D729" s="19"/>
       <x:c r="E729" s="17"/>
+      <x:c r="F729" s="28"/>
     </x:row>
     <x:row r="730">
       <x:c r="A730" s="18"/>
@@ -5490,6 +6248,7 @@
       <x:c r="C730" s="19"/>
       <x:c r="D730" s="19"/>
       <x:c r="E730" s="17"/>
+      <x:c r="F730" s="28"/>
     </x:row>
     <x:row r="731">
       <x:c r="A731" s="18"/>
@@ -5497,6 +6256,7 @@
       <x:c r="C731" s="19"/>
       <x:c r="D731" s="19"/>
       <x:c r="E731" s="17"/>
+      <x:c r="F731" s="28"/>
     </x:row>
     <x:row r="732">
       <x:c r="A732" s="18"/>
@@ -5504,6 +6264,7 @@
       <x:c r="C732" s="19"/>
       <x:c r="D732" s="19"/>
       <x:c r="E732" s="17"/>
+      <x:c r="F732" s="28"/>
     </x:row>
     <x:row r="733">
       <x:c r="A733" s="18"/>
@@ -5511,6 +6272,7 @@
       <x:c r="C733" s="19"/>
       <x:c r="D733" s="19"/>
       <x:c r="E733" s="17"/>
+      <x:c r="F733" s="28"/>
     </x:row>
     <x:row r="734">
       <x:c r="A734" s="18"/>
@@ -5518,6 +6280,7 @@
       <x:c r="C734" s="19"/>
       <x:c r="D734" s="19"/>
       <x:c r="E734" s="17"/>
+      <x:c r="F734" s="28"/>
     </x:row>
     <x:row r="735">
       <x:c r="A735" s="18"/>
@@ -5525,6 +6288,7 @@
       <x:c r="C735" s="19"/>
       <x:c r="D735" s="19"/>
       <x:c r="E735" s="17"/>
+      <x:c r="F735" s="28"/>
     </x:row>
     <x:row r="736">
       <x:c r="A736" s="18"/>
@@ -5532,6 +6296,7 @@
       <x:c r="C736" s="19"/>
       <x:c r="D736" s="19"/>
       <x:c r="E736" s="17"/>
+      <x:c r="F736" s="28"/>
     </x:row>
     <x:row r="737">
       <x:c r="A737" s="18"/>
@@ -5539,6 +6304,7 @@
       <x:c r="C737" s="19"/>
       <x:c r="D737" s="19"/>
       <x:c r="E737" s="17"/>
+      <x:c r="F737" s="28"/>
     </x:row>
     <x:row r="738">
       <x:c r="A738" s="18"/>
@@ -5546,6 +6312,7 @@
       <x:c r="C738" s="19"/>
       <x:c r="D738" s="19"/>
       <x:c r="E738" s="17"/>
+      <x:c r="F738" s="28"/>
     </x:row>
     <x:row r="739">
       <x:c r="A739" s="18"/>
@@ -5553,6 +6320,7 @@
       <x:c r="C739" s="19"/>
       <x:c r="D739" s="19"/>
       <x:c r="E739" s="17"/>
+      <x:c r="F739" s="28"/>
     </x:row>
     <x:row r="740">
       <x:c r="A740" s="18"/>
@@ -5560,6 +6328,7 @@
       <x:c r="C740" s="19"/>
       <x:c r="D740" s="19"/>
       <x:c r="E740" s="17"/>
+      <x:c r="F740" s="28"/>
     </x:row>
     <x:row r="741">
       <x:c r="A741" s="18"/>
@@ -5567,6 +6336,7 @@
       <x:c r="C741" s="19"/>
       <x:c r="D741" s="19"/>
       <x:c r="E741" s="17"/>
+      <x:c r="F741" s="28"/>
     </x:row>
     <x:row r="742">
       <x:c r="A742" s="18"/>
@@ -5574,6 +6344,7 @@
       <x:c r="C742" s="19"/>
       <x:c r="D742" s="19"/>
       <x:c r="E742" s="17"/>
+      <x:c r="F742" s="28"/>
     </x:row>
     <x:row r="743">
       <x:c r="A743" s="18"/>
@@ -5581,6 +6352,7 @@
       <x:c r="C743" s="19"/>
       <x:c r="D743" s="19"/>
       <x:c r="E743" s="17"/>
+      <x:c r="F743" s="28"/>
     </x:row>
     <x:row r="744">
       <x:c r="A744" s="18"/>
@@ -5588,6 +6360,7 @@
       <x:c r="C744" s="19"/>
       <x:c r="D744" s="19"/>
       <x:c r="E744" s="17"/>
+      <x:c r="F744" s="28"/>
     </x:row>
     <x:row r="745">
       <x:c r="A745" s="18"/>
@@ -5595,6 +6368,7 @@
       <x:c r="C745" s="19"/>
       <x:c r="D745" s="19"/>
       <x:c r="E745" s="17"/>
+      <x:c r="F745" s="28"/>
     </x:row>
     <x:row r="746">
       <x:c r="A746" s="18"/>
@@ -5602,6 +6376,7 @@
       <x:c r="C746" s="19"/>
       <x:c r="D746" s="19"/>
       <x:c r="E746" s="17"/>
+      <x:c r="F746" s="28"/>
     </x:row>
     <x:row r="747">
       <x:c r="A747" s="18"/>
@@ -5609,6 +6384,7 @@
       <x:c r="C747" s="19"/>
       <x:c r="D747" s="19"/>
       <x:c r="E747" s="17"/>
+      <x:c r="F747" s="28"/>
     </x:row>
     <x:row r="748">
       <x:c r="A748" s="18"/>
@@ -5616,6 +6392,7 @@
       <x:c r="C748" s="19"/>
       <x:c r="D748" s="19"/>
       <x:c r="E748" s="17"/>
+      <x:c r="F748" s="28"/>
     </x:row>
     <x:row r="749">
       <x:c r="A749" s="18"/>
@@ -5623,6 +6400,7 @@
       <x:c r="C749" s="19"/>
       <x:c r="D749" s="19"/>
       <x:c r="E749" s="17"/>
+      <x:c r="F749" s="28"/>
     </x:row>
     <x:row r="750">
       <x:c r="A750" s="18"/>
@@ -5630,6 +6408,7 @@
       <x:c r="C750" s="19"/>
       <x:c r="D750" s="19"/>
       <x:c r="E750" s="17"/>
+      <x:c r="F750" s="28"/>
     </x:row>
     <x:row r="751">
       <x:c r="A751" s="18"/>
@@ -5637,6 +6416,7 @@
       <x:c r="C751" s="19"/>
       <x:c r="D751" s="19"/>
       <x:c r="E751" s="17"/>
+      <x:c r="F751" s="28"/>
     </x:row>
     <x:row r="752">
       <x:c r="A752" s="18"/>
@@ -5644,6 +6424,7 @@
       <x:c r="C752" s="19"/>
       <x:c r="D752" s="19"/>
       <x:c r="E752" s="17"/>
+      <x:c r="F752" s="28"/>
     </x:row>
     <x:row r="753">
       <x:c r="A753" s="18"/>
@@ -5651,6 +6432,7 @@
       <x:c r="C753" s="19"/>
       <x:c r="D753" s="19"/>
       <x:c r="E753" s="17"/>
+      <x:c r="F753" s="28"/>
     </x:row>
     <x:row r="754">
       <x:c r="A754" s="18"/>
@@ -5658,6 +6440,7 @@
       <x:c r="C754" s="19"/>
       <x:c r="D754" s="19"/>
       <x:c r="E754" s="17"/>
+      <x:c r="F754" s="28"/>
     </x:row>
     <x:row r="755">
       <x:c r="A755" s="18"/>
@@ -5665,6 +6448,7 @@
       <x:c r="C755" s="19"/>
       <x:c r="D755" s="19"/>
       <x:c r="E755" s="17"/>
+      <x:c r="F755" s="28"/>
     </x:row>
     <x:row r="756">
       <x:c r="A756" s="18"/>
@@ -5672,6 +6456,7 @@
       <x:c r="C756" s="19"/>
       <x:c r="D756" s="19"/>
       <x:c r="E756" s="17"/>
+      <x:c r="F756" s="28"/>
     </x:row>
     <x:row r="757">
       <x:c r="A757" s="18"/>
@@ -5679,6 +6464,7 @@
       <x:c r="C757" s="19"/>
       <x:c r="D757" s="19"/>
       <x:c r="E757" s="17"/>
+      <x:c r="F757" s="28"/>
     </x:row>
     <x:row r="758">
       <x:c r="A758" s="18"/>
@@ -5686,6 +6472,7 @@
       <x:c r="C758" s="19"/>
       <x:c r="D758" s="19"/>
       <x:c r="E758" s="17"/>
+      <x:c r="F758" s="28"/>
     </x:row>
     <x:row r="759">
       <x:c r="A759" s="18"/>
@@ -5693,6 +6480,7 @@
       <x:c r="C759" s="19"/>
       <x:c r="D759" s="19"/>
       <x:c r="E759" s="17"/>
+      <x:c r="F759" s="28"/>
     </x:row>
     <x:row r="760">
       <x:c r="A760" s="18"/>
@@ -5700,6 +6488,7 @@
       <x:c r="C760" s="19"/>
       <x:c r="D760" s="19"/>
       <x:c r="E760" s="17"/>
+      <x:c r="F760" s="28"/>
     </x:row>
     <x:row r="761">
       <x:c r="A761" s="18"/>
@@ -5707,6 +6496,7 @@
       <x:c r="C761" s="19"/>
       <x:c r="D761" s="19"/>
       <x:c r="E761" s="17"/>
+      <x:c r="F761" s="28"/>
     </x:row>
     <x:row r="762">
       <x:c r="A762" s="18"/>
@@ -5714,6 +6504,7 @@
       <x:c r="C762" s="19"/>
       <x:c r="D762" s="19"/>
       <x:c r="E762" s="17"/>
+      <x:c r="F762" s="28"/>
     </x:row>
     <x:row r="763">
       <x:c r="A763" s="18"/>
@@ -5721,6 +6512,7 @@
       <x:c r="C763" s="19"/>
       <x:c r="D763" s="19"/>
       <x:c r="E763" s="17"/>
+      <x:c r="F763" s="28"/>
     </x:row>
     <x:row r="764">
       <x:c r="A764" s="18"/>
@@ -5728,6 +6520,7 @@
       <x:c r="C764" s="19"/>
       <x:c r="D764" s="19"/>
       <x:c r="E764" s="17"/>
+      <x:c r="F764" s="28"/>
     </x:row>
     <x:row r="765">
       <x:c r="A765" s="18"/>
@@ -5735,6 +6528,7 @@
       <x:c r="C765" s="19"/>
       <x:c r="D765" s="19"/>
       <x:c r="E765" s="17"/>
+      <x:c r="F765" s="28"/>
     </x:row>
     <x:row r="766">
       <x:c r="A766" s="18"/>
@@ -5742,6 +6536,7 @@
       <x:c r="C766" s="19"/>
       <x:c r="D766" s="19"/>
       <x:c r="E766" s="17"/>
+      <x:c r="F766" s="28"/>
     </x:row>
     <x:row r="767">
       <x:c r="A767" s="18"/>
@@ -5749,6 +6544,7 @@
       <x:c r="C767" s="19"/>
       <x:c r="D767" s="19"/>
       <x:c r="E767" s="17"/>
+      <x:c r="F767" s="28"/>
     </x:row>
     <x:row r="768">
       <x:c r="A768" s="18"/>
@@ -5756,6 +6552,7 @@
       <x:c r="C768" s="19"/>
       <x:c r="D768" s="19"/>
       <x:c r="E768" s="17"/>
+      <x:c r="F768" s="28"/>
     </x:row>
     <x:row r="769">
       <x:c r="A769" s="18"/>
@@ -5763,6 +6560,7 @@
       <x:c r="C769" s="19"/>
       <x:c r="D769" s="19"/>
       <x:c r="E769" s="17"/>
+      <x:c r="F769" s="28"/>
     </x:row>
     <x:row r="770">
       <x:c r="A770" s="18"/>
@@ -5770,6 +6568,7 @@
       <x:c r="C770" s="19"/>
       <x:c r="D770" s="19"/>
       <x:c r="E770" s="17"/>
+      <x:c r="F770" s="28"/>
     </x:row>
     <x:row r="771">
       <x:c r="A771" s="18"/>
@@ -5777,6 +6576,7 @@
       <x:c r="C771" s="19"/>
       <x:c r="D771" s="19"/>
       <x:c r="E771" s="17"/>
+      <x:c r="F771" s="28"/>
     </x:row>
     <x:row r="772">
       <x:c r="A772" s="18"/>
@@ -5784,6 +6584,7 @@
       <x:c r="C772" s="19"/>
       <x:c r="D772" s="19"/>
       <x:c r="E772" s="17"/>
+      <x:c r="F772" s="28"/>
     </x:row>
     <x:row r="773">
       <x:c r="A773" s="18"/>
@@ -5791,6 +6592,7 @@
       <x:c r="C773" s="19"/>
       <x:c r="D773" s="19"/>
       <x:c r="E773" s="17"/>
+      <x:c r="F773" s="28"/>
     </x:row>
     <x:row r="774">
       <x:c r="A774" s="18"/>
@@ -5798,6 +6600,7 @@
       <x:c r="C774" s="19"/>
       <x:c r="D774" s="19"/>
       <x:c r="E774" s="17"/>
+      <x:c r="F774" s="28"/>
     </x:row>
     <x:row r="775">
       <x:c r="A775" s="18"/>
@@ -5805,6 +6608,7 @@
       <x:c r="C775" s="19"/>
       <x:c r="D775" s="19"/>
       <x:c r="E775" s="17"/>
+      <x:c r="F775" s="28"/>
     </x:row>
     <x:row r="776">
       <x:c r="A776" s="18"/>
@@ -5812,6 +6616,7 @@
       <x:c r="C776" s="19"/>
       <x:c r="D776" s="19"/>
       <x:c r="E776" s="17"/>
+      <x:c r="F776" s="28"/>
     </x:row>
     <x:row r="777">
       <x:c r="A777" s="18"/>
@@ -5819,6 +6624,7 @@
       <x:c r="C777" s="19"/>
       <x:c r="D777" s="19"/>
       <x:c r="E777" s="17"/>
+      <x:c r="F777" s="28"/>
     </x:row>
     <x:row r="778">
       <x:c r="A778" s="18"/>
@@ -5826,6 +6632,7 @@
       <x:c r="C778" s="19"/>
       <x:c r="D778" s="19"/>
       <x:c r="E778" s="17"/>
+      <x:c r="F778" s="28"/>
     </x:row>
     <x:row r="779">
       <x:c r="A779" s="18"/>
@@ -5833,6 +6640,7 @@
       <x:c r="C779" s="19"/>
       <x:c r="D779" s="19"/>
       <x:c r="E779" s="17"/>
+      <x:c r="F779" s="28"/>
     </x:row>
     <x:row r="780">
       <x:c r="A780" s="18"/>
@@ -5840,6 +6648,7 @@
       <x:c r="C780" s="19"/>
       <x:c r="D780" s="19"/>
       <x:c r="E780" s="17"/>
+      <x:c r="F780" s="28"/>
     </x:row>
     <x:row r="781">
       <x:c r="A781" s="18"/>
@@ -5847,6 +6656,7 @@
       <x:c r="C781" s="19"/>
       <x:c r="D781" s="19"/>
       <x:c r="E781" s="17"/>
+      <x:c r="F781" s="28"/>
     </x:row>
     <x:row r="782">
       <x:c r="A782" s="18"/>
@@ -5854,6 +6664,7 @@
       <x:c r="C782" s="19"/>
       <x:c r="D782" s="19"/>
       <x:c r="E782" s="17"/>
+      <x:c r="F782" s="28"/>
     </x:row>
     <x:row r="783">
       <x:c r="A783" s="18"/>
@@ -5861,6 +6672,7 @@
       <x:c r="C783" s="19"/>
       <x:c r="D783" s="19"/>
       <x:c r="E783" s="17"/>
+      <x:c r="F783" s="28"/>
     </x:row>
     <x:row r="784">
       <x:c r="A784" s="18"/>
@@ -5868,6 +6680,7 @@
       <x:c r="C784" s="19"/>
       <x:c r="D784" s="19"/>
       <x:c r="E784" s="17"/>
+      <x:c r="F784" s="28"/>
     </x:row>
     <x:row r="785">
       <x:c r="A785" s="18"/>
@@ -5875,6 +6688,7 @@
       <x:c r="C785" s="19"/>
       <x:c r="D785" s="19"/>
       <x:c r="E785" s="17"/>
+      <x:c r="F785" s="28"/>
     </x:row>
     <x:row r="786">
       <x:c r="A786" s="18"/>
@@ -5882,6 +6696,7 @@
       <x:c r="C786" s="19"/>
       <x:c r="D786" s="19"/>
       <x:c r="E786" s="17"/>
+      <x:c r="F786" s="28"/>
     </x:row>
     <x:row r="787">
       <x:c r="A787" s="18"/>
@@ -5889,6 +6704,7 @@
       <x:c r="C787" s="19"/>
       <x:c r="D787" s="19"/>
       <x:c r="E787" s="17"/>
+      <x:c r="F787" s="28"/>
     </x:row>
     <x:row r="788">
       <x:c r="A788" s="18"/>
@@ -5896,6 +6712,7 @@
       <x:c r="C788" s="19"/>
       <x:c r="D788" s="19"/>
       <x:c r="E788" s="17"/>
+      <x:c r="F788" s="28"/>
     </x:row>
     <x:row r="789">
       <x:c r="A789" s="18"/>
@@ -5903,6 +6720,7 @@
       <x:c r="C789" s="19"/>
       <x:c r="D789" s="19"/>
       <x:c r="E789" s="17"/>
+      <x:c r="F789" s="28"/>
     </x:row>
     <x:row r="790">
       <x:c r="A790" s="18"/>
@@ -5910,6 +6728,7 @@
       <x:c r="C790" s="19"/>
       <x:c r="D790" s="19"/>
       <x:c r="E790" s="17"/>
+      <x:c r="F790" s="28"/>
     </x:row>
     <x:row r="791">
       <x:c r="A791" s="18"/>
@@ -5917,6 +6736,7 @@
       <x:c r="C791" s="19"/>
       <x:c r="D791" s="19"/>
       <x:c r="E791" s="17"/>
+      <x:c r="F791" s="28"/>
     </x:row>
     <x:row r="792">
       <x:c r="A792" s="18"/>
@@ -5924,6 +6744,7 @@
       <x:c r="C792" s="19"/>
       <x:c r="D792" s="19"/>
       <x:c r="E792" s="17"/>
+      <x:c r="F792" s="28"/>
     </x:row>
     <x:row r="793">
       <x:c r="A793" s="18"/>
@@ -5931,6 +6752,7 @@
       <x:c r="C793" s="19"/>
       <x:c r="D793" s="19"/>
       <x:c r="E793" s="17"/>
+      <x:c r="F793" s="28"/>
     </x:row>
     <x:row r="794">
       <x:c r="A794" s="18"/>
@@ -5938,6 +6760,7 @@
       <x:c r="C794" s="19"/>
       <x:c r="D794" s="19"/>
       <x:c r="E794" s="17"/>
+      <x:c r="F794" s="28"/>
     </x:row>
     <x:row r="795">
       <x:c r="A795" s="18"/>
@@ -5945,6 +6768,7 @@
       <x:c r="C795" s="19"/>
       <x:c r="D795" s="19"/>
       <x:c r="E795" s="17"/>
+      <x:c r="F795" s="28"/>
     </x:row>
     <x:row r="796">
       <x:c r="A796" s="18"/>
@@ -5952,6 +6776,7 @@
       <x:c r="C796" s="19"/>
       <x:c r="D796" s="19"/>
       <x:c r="E796" s="17"/>
+      <x:c r="F796" s="28"/>
     </x:row>
     <x:row r="797">
       <x:c r="A797" s="18"/>
@@ -5959,6 +6784,7 @@
       <x:c r="C797" s="19"/>
       <x:c r="D797" s="19"/>
       <x:c r="E797" s="17"/>
+      <x:c r="F797" s="28"/>
     </x:row>
     <x:row r="798">
       <x:c r="A798" s="18"/>
@@ -5966,6 +6792,7 @@
       <x:c r="C798" s="19"/>
       <x:c r="D798" s="19"/>
       <x:c r="E798" s="17"/>
+      <x:c r="F798" s="28"/>
     </x:row>
     <x:row r="799">
       <x:c r="A799" s="18"/>
@@ -5973,6 +6800,7 @@
       <x:c r="C799" s="19"/>
       <x:c r="D799" s="19"/>
       <x:c r="E799" s="17"/>
+      <x:c r="F799" s="28"/>
     </x:row>
     <x:row r="800">
       <x:c r="A800" s="18"/>
@@ -5980,6 +6808,7 @@
       <x:c r="C800" s="19"/>
       <x:c r="D800" s="19"/>
       <x:c r="E800" s="17"/>
+      <x:c r="F800" s="28"/>
     </x:row>
     <x:row r="801">
       <x:c r="A801" s="18"/>
@@ -5987,6 +6816,7 @@
       <x:c r="C801" s="19"/>
       <x:c r="D801" s="19"/>
       <x:c r="E801" s="17"/>
+      <x:c r="F801" s="28"/>
     </x:row>
     <x:row r="802">
       <x:c r="A802" s="18"/>
@@ -5994,6 +6824,7 @@
       <x:c r="C802" s="19"/>
       <x:c r="D802" s="19"/>
       <x:c r="E802" s="17"/>
+      <x:c r="F802" s="28"/>
     </x:row>
     <x:row r="803">
       <x:c r="A803" s="18"/>
@@ -6001,6 +6832,7 @@
       <x:c r="C803" s="19"/>
       <x:c r="D803" s="19"/>
       <x:c r="E803" s="17"/>
+      <x:c r="F803" s="28"/>
     </x:row>
     <x:row r="804">
       <x:c r="A804" s="18"/>
@@ -6008,6 +6840,7 @@
       <x:c r="C804" s="19"/>
       <x:c r="D804" s="19"/>
       <x:c r="E804" s="17"/>
+      <x:c r="F804" s="28"/>
     </x:row>
     <x:row r="805">
       <x:c r="A805" s="18"/>
@@ -6015,6 +6848,7 @@
       <x:c r="C805" s="19"/>
       <x:c r="D805" s="19"/>
       <x:c r="E805" s="17"/>
+      <x:c r="F805" s="28"/>
     </x:row>
     <x:row r="806">
       <x:c r="A806" s="18"/>
@@ -6022,6 +6856,7 @@
       <x:c r="C806" s="19"/>
       <x:c r="D806" s="19"/>
       <x:c r="E806" s="17"/>
+      <x:c r="F806" s="28"/>
     </x:row>
     <x:row r="807">
       <x:c r="A807" s="18"/>
@@ -6029,6 +6864,7 @@
       <x:c r="C807" s="19"/>
       <x:c r="D807" s="19"/>
       <x:c r="E807" s="17"/>
+      <x:c r="F807" s="28"/>
     </x:row>
     <x:row r="808">
       <x:c r="A808" s="18"/>
@@ -6036,6 +6872,7 @@
       <x:c r="C808" s="19"/>
       <x:c r="D808" s="19"/>
       <x:c r="E808" s="17"/>
+      <x:c r="F808" s="28"/>
     </x:row>
     <x:row r="809">
       <x:c r="A809" s="18"/>
@@ -6043,6 +6880,7 @@
       <x:c r="C809" s="19"/>
       <x:c r="D809" s="19"/>
       <x:c r="E809" s="17"/>
+      <x:c r="F809" s="28"/>
     </x:row>
     <x:row r="810">
       <x:c r="A810" s="18"/>
@@ -6050,6 +6888,7 @@
       <x:c r="C810" s="19"/>
       <x:c r="D810" s="19"/>
       <x:c r="E810" s="17"/>
+      <x:c r="F810" s="28"/>
     </x:row>
     <x:row r="811">
       <x:c r="A811" s="18"/>
@@ -6057,6 +6896,7 @@
       <x:c r="C811" s="19"/>
       <x:c r="D811" s="19"/>
       <x:c r="E811" s="17"/>
+      <x:c r="F811" s="28"/>
     </x:row>
     <x:row r="812">
       <x:c r="A812" s="18"/>
@@ -6064,6 +6904,7 @@
       <x:c r="C812" s="19"/>
       <x:c r="D812" s="19"/>
       <x:c r="E812" s="17"/>
+      <x:c r="F812" s="28"/>
     </x:row>
     <x:row r="813">
       <x:c r="A813" s="18"/>
@@ -6071,6 +6912,7 @@
       <x:c r="C813" s="19"/>
       <x:c r="D813" s="19"/>
       <x:c r="E813" s="17"/>
+      <x:c r="F813" s="28"/>
     </x:row>
     <x:row r="814">
       <x:c r="A814" s="18"/>
@@ -6078,6 +6920,7 @@
       <x:c r="C814" s="19"/>
       <x:c r="D814" s="19"/>
       <x:c r="E814" s="17"/>
+      <x:c r="F814" s="28"/>
     </x:row>
     <x:row r="815">
       <x:c r="A815" s="18"/>
@@ -6085,6 +6928,7 @@
       <x:c r="C815" s="19"/>
       <x:c r="D815" s="19"/>
       <x:c r="E815" s="17"/>
+      <x:c r="F815" s="28"/>
     </x:row>
     <x:row r="816">
       <x:c r="A816" s="18"/>
@@ -6092,6 +6936,7 @@
       <x:c r="C816" s="19"/>
       <x:c r="D816" s="19"/>
       <x:c r="E816" s="17"/>
+      <x:c r="F816" s="28"/>
     </x:row>
     <x:row r="817">
       <x:c r="A817" s="18"/>
@@ -6099,6 +6944,7 @@
       <x:c r="C817" s="19"/>
       <x:c r="D817" s="19"/>
       <x:c r="E817" s="17"/>
+      <x:c r="F817" s="28"/>
     </x:row>
     <x:row r="818">
       <x:c r="A818" s="18"/>
@@ -6106,6 +6952,7 @@
       <x:c r="C818" s="19"/>
       <x:c r="D818" s="19"/>
       <x:c r="E818" s="17"/>
+      <x:c r="F818" s="28"/>
     </x:row>
     <x:row r="819">
       <x:c r="A819" s="18"/>
@@ -6113,6 +6960,7 @@
       <x:c r="C819" s="19"/>
       <x:c r="D819" s="19"/>
       <x:c r="E819" s="17"/>
+      <x:c r="F819" s="28"/>
     </x:row>
     <x:row r="820">
       <x:c r="A820" s="18"/>
@@ -6120,6 +6968,7 @@
       <x:c r="C820" s="19"/>
       <x:c r="D820" s="19"/>
       <x:c r="E820" s="17"/>
+      <x:c r="F820" s="28"/>
     </x:row>
     <x:row r="821">
       <x:c r="A821" s="18"/>
@@ -6127,6 +6976,7 @@
       <x:c r="C821" s="19"/>
       <x:c r="D821" s="19"/>
       <x:c r="E821" s="17"/>
+      <x:c r="F821" s="28"/>
     </x:row>
     <x:row r="822">
       <x:c r="A822" s="18"/>
@@ -6134,6 +6984,7 @@
       <x:c r="C822" s="19"/>
       <x:c r="D822" s="19"/>
       <x:c r="E822" s="17"/>
+      <x:c r="F822" s="28"/>
     </x:row>
     <x:row r="823">
       <x:c r="A823" s="18"/>
@@ -6141,6 +6992,7 @@
       <x:c r="C823" s="19"/>
       <x:c r="D823" s="19"/>
       <x:c r="E823" s="17"/>
+      <x:c r="F823" s="28"/>
     </x:row>
     <x:row r="824">
       <x:c r="A824" s="18"/>
@@ -6148,6 +7000,7 @@
       <x:c r="C824" s="19"/>
       <x:c r="D824" s="19"/>
       <x:c r="E824" s="17"/>
+      <x:c r="F824" s="28"/>
     </x:row>
     <x:row r="825">
       <x:c r="A825" s="18"/>
@@ -6155,6 +7008,7 @@
       <x:c r="C825" s="19"/>
       <x:c r="D825" s="19"/>
       <x:c r="E825" s="17"/>
+      <x:c r="F825" s="28"/>
     </x:row>
     <x:row r="826">
       <x:c r="A826" s="18"/>
@@ -6162,6 +7016,7 @@
       <x:c r="C826" s="19"/>
       <x:c r="D826" s="19"/>
       <x:c r="E826" s="17"/>
+      <x:c r="F826" s="28"/>
     </x:row>
     <x:row r="827">
       <x:c r="A827" s="18"/>
@@ -6169,6 +7024,7 @@
       <x:c r="C827" s="19"/>
       <x:c r="D827" s="19"/>
       <x:c r="E827" s="17"/>
+      <x:c r="F827" s="28"/>
     </x:row>
     <x:row r="828">
       <x:c r="A828" s="18"/>
@@ -6176,6 +7032,7 @@
       <x:c r="C828" s="19"/>
       <x:c r="D828" s="19"/>
       <x:c r="E828" s="17"/>
+      <x:c r="F828" s="28"/>
     </x:row>
     <x:row r="829">
       <x:c r="A829" s="18"/>
@@ -6183,6 +7040,7 @@
       <x:c r="C829" s="19"/>
       <x:c r="D829" s="19"/>
       <x:c r="E829" s="17"/>
+      <x:c r="F829" s="28"/>
     </x:row>
     <x:row r="830">
       <x:c r="A830" s="18"/>
@@ -6190,6 +7048,7 @@
       <x:c r="C830" s="19"/>
       <x:c r="D830" s="19"/>
       <x:c r="E830" s="17"/>
+      <x:c r="F830" s="28"/>
     </x:row>
     <x:row r="831">
       <x:c r="A831" s="18"/>
@@ -6197,6 +7056,7 @@
       <x:c r="C831" s="19"/>
       <x:c r="D831" s="19"/>
       <x:c r="E831" s="17"/>
+      <x:c r="F831" s="28"/>
     </x:row>
     <x:row r="832">
       <x:c r="A832" s="18"/>
@@ -6204,6 +7064,7 @@
       <x:c r="C832" s="19"/>
       <x:c r="D832" s="19"/>
       <x:c r="E832" s="17"/>
+      <x:c r="F832" s="28"/>
     </x:row>
     <x:row r="833">
       <x:c r="A833" s="18"/>
@@ -6211,6 +7072,7 @@
       <x:c r="C833" s="19"/>
       <x:c r="D833" s="19"/>
       <x:c r="E833" s="17"/>
+      <x:c r="F833" s="28"/>
     </x:row>
     <x:row r="834">
       <x:c r="A834" s="18"/>
@@ -6218,6 +7080,7 @@
       <x:c r="C834" s="19"/>
       <x:c r="D834" s="19"/>
       <x:c r="E834" s="17"/>
+      <x:c r="F834" s="28"/>
     </x:row>
     <x:row r="835">
       <x:c r="A835" s="18"/>
@@ -6225,6 +7088,7 @@
       <x:c r="C835" s="19"/>
       <x:c r="D835" s="19"/>
       <x:c r="E835" s="17"/>
+      <x:c r="F835" s="28"/>
     </x:row>
     <x:row r="836">
       <x:c r="A836" s="18"/>
@@ -6232,6 +7096,7 @@
       <x:c r="C836" s="19"/>
       <x:c r="D836" s="19"/>
       <x:c r="E836" s="17"/>
+      <x:c r="F836" s="28"/>
     </x:row>
     <x:row r="837">
       <x:c r="A837" s="18"/>
@@ -6239,6 +7104,7 @@
       <x:c r="C837" s="19"/>
       <x:c r="D837" s="19"/>
       <x:c r="E837" s="17"/>
+      <x:c r="F837" s="28"/>
     </x:row>
     <x:row r="838">
       <x:c r="A838" s="18"/>
@@ -6246,6 +7112,7 @@
       <x:c r="C838" s="19"/>
       <x:c r="D838" s="19"/>
       <x:c r="E838" s="17"/>
+      <x:c r="F838" s="28"/>
     </x:row>
     <x:row r="839">
       <x:c r="A839" s="18"/>
@@ -6253,6 +7120,7 @@
       <x:c r="C839" s="19"/>
       <x:c r="D839" s="19"/>
       <x:c r="E839" s="17"/>
+      <x:c r="F839" s="28"/>
     </x:row>
     <x:row r="840">
       <x:c r="A840" s="18"/>
@@ -6260,6 +7128,7 @@
       <x:c r="C840" s="19"/>
       <x:c r="D840" s="19"/>
       <x:c r="E840" s="17"/>
+      <x:c r="F840" s="28"/>
     </x:row>
     <x:row r="841">
       <x:c r="A841" s="18"/>
@@ -6267,6 +7136,7 @@
       <x:c r="C841" s="19"/>
       <x:c r="D841" s="19"/>
       <x:c r="E841" s="17"/>
+      <x:c r="F841" s="28"/>
     </x:row>
     <x:row r="842">
       <x:c r="A842" s="18"/>
@@ -6274,6 +7144,7 @@
       <x:c r="C842" s="19"/>
       <x:c r="D842" s="19"/>
       <x:c r="E842" s="17"/>
+      <x:c r="F842" s="28"/>
     </x:row>
     <x:row r="843">
       <x:c r="A843" s="18"/>
@@ -6281,6 +7152,7 @@
       <x:c r="C843" s="19"/>
       <x:c r="D843" s="19"/>
       <x:c r="E843" s="17"/>
+      <x:c r="F843" s="28"/>
     </x:row>
     <x:row r="844">
       <x:c r="A844" s="18"/>
@@ -6288,6 +7160,7 @@
       <x:c r="C844" s="19"/>
       <x:c r="D844" s="19"/>
       <x:c r="E844" s="17"/>
+      <x:c r="F844" s="28"/>
     </x:row>
     <x:row r="845">
       <x:c r="A845" s="18"/>
@@ -6295,6 +7168,7 @@
       <x:c r="C845" s="19"/>
       <x:c r="D845" s="19"/>
       <x:c r="E845" s="17"/>
+      <x:c r="F845" s="28"/>
     </x:row>
     <x:row r="846">
       <x:c r="A846" s="18"/>
@@ -6302,6 +7176,7 @@
       <x:c r="C846" s="19"/>
       <x:c r="D846" s="19"/>
       <x:c r="E846" s="17"/>
+      <x:c r="F846" s="28"/>
     </x:row>
     <x:row r="847">
       <x:c r="A847" s="18"/>
@@ -6309,6 +7184,7 @@
       <x:c r="C847" s="19"/>
       <x:c r="D847" s="19"/>
       <x:c r="E847" s="17"/>
+      <x:c r="F847" s="28"/>
     </x:row>
     <x:row r="848">
       <x:c r="A848" s="18"/>
@@ -6316,6 +7192,7 @@
       <x:c r="C848" s="19"/>
       <x:c r="D848" s="19"/>
       <x:c r="E848" s="17"/>
+      <x:c r="F848" s="28"/>
     </x:row>
     <x:row r="849">
       <x:c r="A849" s="18"/>
@@ -6323,6 +7200,7 @@
       <x:c r="C849" s="19"/>
       <x:c r="D849" s="19"/>
       <x:c r="E849" s="17"/>
+      <x:c r="F849" s="28"/>
     </x:row>
     <x:row r="850">
       <x:c r="A850" s="18"/>
@@ -6330,6 +7208,7 @@
       <x:c r="C850" s="19"/>
       <x:c r="D850" s="19"/>
       <x:c r="E850" s="17"/>
+      <x:c r="F850" s="28"/>
     </x:row>
     <x:row r="851">
       <x:c r="A851" s="18"/>
@@ -6337,6 +7216,7 @@
       <x:c r="C851" s="19"/>
       <x:c r="D851" s="19"/>
       <x:c r="E851" s="17"/>
+      <x:c r="F851" s="28"/>
     </x:row>
     <x:row r="852">
       <x:c r="A852" s="18"/>
@@ -6344,6 +7224,7 @@
       <x:c r="C852" s="19"/>
       <x:c r="D852" s="19"/>
       <x:c r="E852" s="17"/>
+      <x:c r="F852" s="28"/>
     </x:row>
     <x:row r="853">
       <x:c r="A853" s="18"/>
@@ -6351,6 +7232,7 @@
       <x:c r="C853" s="19"/>
       <x:c r="D853" s="19"/>
       <x:c r="E853" s="17"/>
+      <x:c r="F853" s="28"/>
     </x:row>
     <x:row r="854">
       <x:c r="A854" s="18"/>
@@ -6358,6 +7240,7 @@
       <x:c r="C854" s="19"/>
       <x:c r="D854" s="19"/>
       <x:c r="E854" s="17"/>
+      <x:c r="F854" s="28"/>
     </x:row>
     <x:row r="855">
       <x:c r="A855" s="18"/>
@@ -6365,6 +7248,7 @@
       <x:c r="C855" s="19"/>
       <x:c r="D855" s="19"/>
       <x:c r="E855" s="17"/>
+      <x:c r="F855" s="28"/>
     </x:row>
     <x:row r="856">
       <x:c r="A856" s="18"/>
@@ -6372,6 +7256,7 @@
       <x:c r="C856" s="19"/>
       <x:c r="D856" s="19"/>
       <x:c r="E856" s="17"/>
+      <x:c r="F856" s="28"/>
     </x:row>
     <x:row r="857">
       <x:c r="A857" s="18"/>
@@ -6379,6 +7264,7 @@
       <x:c r="C857" s="19"/>
       <x:c r="D857" s="19"/>
       <x:c r="E857" s="17"/>
+      <x:c r="F857" s="28"/>
     </x:row>
     <x:row r="858">
       <x:c r="A858" s="18"/>
@@ -6386,6 +7272,7 @@
       <x:c r="C858" s="19"/>
       <x:c r="D858" s="19"/>
       <x:c r="E858" s="17"/>
+      <x:c r="F858" s="28"/>
     </x:row>
     <x:row r="859">
       <x:c r="A859" s="18"/>
@@ -6393,6 +7280,7 @@
       <x:c r="C859" s="19"/>
       <x:c r="D859" s="19"/>
       <x:c r="E859" s="17"/>
+      <x:c r="F859" s="28"/>
     </x:row>
     <x:row r="860">
       <x:c r="A860" s="18"/>
@@ -6400,6 +7288,7 @@
       <x:c r="C860" s="19"/>
       <x:c r="D860" s="19"/>
       <x:c r="E860" s="17"/>
+      <x:c r="F860" s="28"/>
     </x:row>
     <x:row r="861">
       <x:c r="A861" s="18"/>
@@ -6407,6 +7296,7 @@
       <x:c r="C861" s="19"/>
       <x:c r="D861" s="19"/>
       <x:c r="E861" s="17"/>
+      <x:c r="F861" s="28"/>
     </x:row>
     <x:row r="862">
       <x:c r="A862" s="18"/>
@@ -6414,6 +7304,7 @@
       <x:c r="C862" s="19"/>
       <x:c r="D862" s="19"/>
       <x:c r="E862" s="17"/>
+      <x:c r="F862" s="28"/>
     </x:row>
     <x:row r="863">
       <x:c r="A863" s="18"/>
@@ -6421,6 +7312,7 @@
       <x:c r="C863" s="19"/>
       <x:c r="D863" s="19"/>
       <x:c r="E863" s="17"/>
+      <x:c r="F863" s="28"/>
     </x:row>
     <x:row r="864">
       <x:c r="A864" s="18"/>
@@ -6428,6 +7320,7 @@
       <x:c r="C864" s="19"/>
       <x:c r="D864" s="19"/>
       <x:c r="E864" s="17"/>
+      <x:c r="F864" s="28"/>
     </x:row>
     <x:row r="865">
       <x:c r="A865" s="18"/>
@@ -6435,6 +7328,7 @@
       <x:c r="C865" s="19"/>
       <x:c r="D865" s="19"/>
       <x:c r="E865" s="17"/>
+      <x:c r="F865" s="28"/>
     </x:row>
     <x:row r="866">
       <x:c r="A866" s="18"/>
@@ -6442,6 +7336,7 @@
       <x:c r="C866" s="19"/>
       <x:c r="D866" s="19"/>
       <x:c r="E866" s="17"/>
+      <x:c r="F866" s="28"/>
     </x:row>
     <x:row r="867">
       <x:c r="A867" s="18"/>
@@ -6449,6 +7344,7 @@
       <x:c r="C867" s="19"/>
       <x:c r="D867" s="19"/>
       <x:c r="E867" s="17"/>
+      <x:c r="F867" s="28"/>
     </x:row>
     <x:row r="868">
       <x:c r="A868" s="18"/>
@@ -6456,6 +7352,7 @@
       <x:c r="C868" s="19"/>
       <x:c r="D868" s="19"/>
       <x:c r="E868" s="17"/>
+      <x:c r="F868" s="28"/>
     </x:row>
     <x:row r="869">
       <x:c r="A869" s="18"/>
@@ -6463,6 +7360,7 @@
       <x:c r="C869" s="19"/>
       <x:c r="D869" s="19"/>
       <x:c r="E869" s="17"/>
+      <x:c r="F869" s="28"/>
     </x:row>
     <x:row r="870">
       <x:c r="A870" s="18"/>
@@ -6470,6 +7368,7 @@
       <x:c r="C870" s="19"/>
       <x:c r="D870" s="19"/>
       <x:c r="E870" s="17"/>
+      <x:c r="F870" s="28"/>
     </x:row>
     <x:row r="871">
       <x:c r="A871" s="18"/>
@@ -6477,6 +7376,7 @@
       <x:c r="C871" s="19"/>
       <x:c r="D871" s="19"/>
       <x:c r="E871" s="17"/>
+      <x:c r="F871" s="28"/>
     </x:row>
     <x:row r="872">
       <x:c r="A872" s="18"/>
@@ -6484,6 +7384,7 @@
       <x:c r="C872" s="19"/>
       <x:c r="D872" s="19"/>
       <x:c r="E872" s="17"/>
+      <x:c r="F872" s="28"/>
     </x:row>
     <x:row r="873">
       <x:c r="A873" s="18"/>
@@ -6491,6 +7392,7 @@
       <x:c r="C873" s="19"/>
       <x:c r="D873" s="19"/>
       <x:c r="E873" s="17"/>
+      <x:c r="F873" s="28"/>
     </x:row>
     <x:row r="874">
       <x:c r="A874" s="18"/>
@@ -6498,6 +7400,7 @@
       <x:c r="C874" s="19"/>
       <x:c r="D874" s="19"/>
       <x:c r="E874" s="17"/>
+      <x:c r="F874" s="28"/>
     </x:row>
     <x:row r="875">
       <x:c r="A875" s="18"/>
@@ -6505,6 +7408,7 @@
       <x:c r="C875" s="19"/>
       <x:c r="D875" s="19"/>
       <x:c r="E875" s="17"/>
+      <x:c r="F875" s="28"/>
     </x:row>
     <x:row r="876">
       <x:c r="A876" s="18"/>
@@ -6512,6 +7416,7 @@
       <x:c r="C876" s="19"/>
       <x:c r="D876" s="19"/>
       <x:c r="E876" s="17"/>
+      <x:c r="F876" s="28"/>
     </x:row>
     <x:row r="877">
       <x:c r="A877" s="18"/>
@@ -6519,6 +7424,7 @@
       <x:c r="C877" s="19"/>
       <x:c r="D877" s="19"/>
       <x:c r="E877" s="17"/>
+      <x:c r="F877" s="28"/>
     </x:row>
     <x:row r="878">
       <x:c r="A878" s="18"/>
@@ -6526,6 +7432,7 @@
       <x:c r="C878" s="19"/>
       <x:c r="D878" s="19"/>
       <x:c r="E878" s="17"/>
+      <x:c r="F878" s="28"/>
     </x:row>
     <x:row r="879">
       <x:c r="A879" s="18"/>
@@ -6533,6 +7440,7 @@
       <x:c r="C879" s="19"/>
       <x:c r="D879" s="19"/>
       <x:c r="E879" s="17"/>
+      <x:c r="F879" s="28"/>
     </x:row>
     <x:row r="880">
       <x:c r="A880" s="18"/>
@@ -6540,6 +7448,7 @@
       <x:c r="C880" s="19"/>
       <x:c r="D880" s="19"/>
       <x:c r="E880" s="17"/>
+      <x:c r="F880" s="28"/>
     </x:row>
     <x:row r="881">
       <x:c r="A881" s="18"/>
@@ -6547,6 +7456,7 @@
       <x:c r="C881" s="19"/>
       <x:c r="D881" s="19"/>
       <x:c r="E881" s="17"/>
+      <x:c r="F881" s="28"/>
     </x:row>
     <x:row r="882">
       <x:c r="A882" s="18"/>
@@ -6554,6 +7464,7 @@
       <x:c r="C882" s="19"/>
       <x:c r="D882" s="19"/>
       <x:c r="E882" s="17"/>
+      <x:c r="F882" s="28"/>
     </x:row>
     <x:row r="883">
       <x:c r="A883" s="18"/>
@@ -6561,6 +7472,7 @@
       <x:c r="C883" s="19"/>
       <x:c r="D883" s="19"/>
       <x:c r="E883" s="17"/>
+      <x:c r="F883" s="28"/>
     </x:row>
     <x:row r="884">
       <x:c r="A884" s="18"/>
@@ -6568,6 +7480,7 @@
       <x:c r="C884" s="19"/>
       <x:c r="D884" s="19"/>
       <x:c r="E884" s="17"/>
+      <x:c r="F884" s="28"/>
     </x:row>
     <x:row r="885">
       <x:c r="A885" s="18"/>
@@ -6575,6 +7488,7 @@
       <x:c r="C885" s="19"/>
       <x:c r="D885" s="19"/>
       <x:c r="E885" s="17"/>
+      <x:c r="F885" s="28"/>
     </x:row>
     <x:row r="886">
       <x:c r="A886" s="18"/>
@@ -6582,6 +7496,7 @@
       <x:c r="C886" s="19"/>
       <x:c r="D886" s="19"/>
       <x:c r="E886" s="17"/>
+      <x:c r="F886" s="28"/>
     </x:row>
     <x:row r="887">
       <x:c r="A887" s="18"/>
@@ -6589,6 +7504,7 @@
       <x:c r="C887" s="19"/>
       <x:c r="D887" s="19"/>
       <x:c r="E887" s="17"/>
+      <x:c r="F887" s="28"/>
     </x:row>
     <x:row r="888">
       <x:c r="A888" s="18"/>
@@ -6596,6 +7512,7 @@
       <x:c r="C888" s="19"/>
       <x:c r="D888" s="19"/>
       <x:c r="E888" s="17"/>
+      <x:c r="F888" s="28"/>
     </x:row>
     <x:row r="889">
       <x:c r="A889" s="18"/>
@@ -6603,6 +7520,7 @@
       <x:c r="C889" s="19"/>
       <x:c r="D889" s="19"/>
       <x:c r="E889" s="17"/>
+      <x:c r="F889" s="28"/>
     </x:row>
     <x:row r="890">
       <x:c r="A890" s="18"/>
@@ -6610,6 +7528,7 @@
       <x:c r="C890" s="19"/>
       <x:c r="D890" s="19"/>
       <x:c r="E890" s="17"/>
+      <x:c r="F890" s="28"/>
     </x:row>
     <x:row r="891">
       <x:c r="A891" s="18"/>
@@ -6617,6 +7536,7 @@
       <x:c r="C891" s="19"/>
       <x:c r="D891" s="19"/>
       <x:c r="E891" s="17"/>
+      <x:c r="F891" s="28"/>
     </x:row>
     <x:row r="892">
       <x:c r="A892" s="18"/>
@@ -6624,6 +7544,7 @@
       <x:c r="C892" s="19"/>
       <x:c r="D892" s="19"/>
       <x:c r="E892" s="17"/>
+      <x:c r="F892" s="28"/>
     </x:row>
     <x:row r="893">
       <x:c r="A893" s="18"/>
@@ -6631,6 +7552,7 @@
       <x:c r="C893" s="19"/>
       <x:c r="D893" s="19"/>
       <x:c r="E893" s="17"/>
+      <x:c r="F893" s="28"/>
     </x:row>
     <x:row r="894">
       <x:c r="A894" s="18"/>
@@ -6638,6 +7560,7 @@
       <x:c r="C894" s="19"/>
       <x:c r="D894" s="19"/>
       <x:c r="E894" s="17"/>
+      <x:c r="F894" s="28"/>
     </x:row>
     <x:row r="895">
       <x:c r="A895" s="18"/>
@@ -6645,6 +7568,7 @@
       <x:c r="C895" s="19"/>
       <x:c r="D895" s="19"/>
       <x:c r="E895" s="17"/>
+      <x:c r="F895" s="28"/>
     </x:row>
     <x:row r="896">
       <x:c r="A896" s="18"/>
@@ -6652,6 +7576,7 @@
       <x:c r="C896" s="19"/>
       <x:c r="D896" s="19"/>
       <x:c r="E896" s="17"/>
+      <x:c r="F896" s="28"/>
     </x:row>
     <x:row r="897">
       <x:c r="A897" s="18"/>
@@ -6659,6 +7584,7 @@
       <x:c r="C897" s="19"/>
       <x:c r="D897" s="19"/>
       <x:c r="E897" s="17"/>
+      <x:c r="F897" s="28"/>
     </x:row>
     <x:row r="898">
       <x:c r="A898" s="18"/>
@@ -6666,6 +7592,7 @@
       <x:c r="C898" s="19"/>
       <x:c r="D898" s="19"/>
       <x:c r="E898" s="17"/>
+      <x:c r="F898" s="28"/>
     </x:row>
     <x:row r="899">
       <x:c r="A899" s="18"/>
@@ -6673,6 +7600,7 @@
       <x:c r="C899" s="19"/>
       <x:c r="D899" s="19"/>
       <x:c r="E899" s="17"/>
+      <x:c r="F899" s="28"/>
     </x:row>
     <x:row r="900">
       <x:c r="A900" s="18"/>
@@ -6680,6 +7608,7 @@
       <x:c r="C900" s="19"/>
       <x:c r="D900" s="19"/>
       <x:c r="E900" s="17"/>
+      <x:c r="F900" s="28"/>
     </x:row>
     <x:row r="901">
       <x:c r="A901" s="18"/>
@@ -6687,6 +7616,7 @@
       <x:c r="C901" s="19"/>
       <x:c r="D901" s="19"/>
       <x:c r="E901" s="17"/>
+      <x:c r="F901" s="28"/>
     </x:row>
     <x:row r="902">
       <x:c r="A902" s="18"/>
@@ -6694,6 +7624,7 @@
       <x:c r="C902" s="19"/>
       <x:c r="D902" s="19"/>
       <x:c r="E902" s="17"/>
+      <x:c r="F902" s="28"/>
     </x:row>
     <x:row r="903">
       <x:c r="A903" s="18"/>
@@ -6701,6 +7632,7 @@
       <x:c r="C903" s="19"/>
       <x:c r="D903" s="19"/>
       <x:c r="E903" s="17"/>
+      <x:c r="F903" s="28"/>
     </x:row>
     <x:row r="904">
       <x:c r="A904" s="18"/>
@@ -6708,6 +7640,7 @@
       <x:c r="C904" s="19"/>
       <x:c r="D904" s="19"/>
       <x:c r="E904" s="17"/>
+      <x:c r="F904" s="28"/>
     </x:row>
     <x:row r="905">
       <x:c r="A905" s="18"/>
@@ -6715,6 +7648,7 @@
       <x:c r="C905" s="19"/>
       <x:c r="D905" s="19"/>
       <x:c r="E905" s="17"/>
+      <x:c r="F905" s="28"/>
     </x:row>
     <x:row r="906">
       <x:c r="A906" s="18"/>
@@ -6722,6 +7656,7 @@
       <x:c r="C906" s="19"/>
       <x:c r="D906" s="19"/>
       <x:c r="E906" s="17"/>
+      <x:c r="F906" s="28"/>
     </x:row>
     <x:row r="907">
       <x:c r="A907" s="18"/>
@@ -6729,6 +7664,7 @@
       <x:c r="C907" s="19"/>
       <x:c r="D907" s="19"/>
       <x:c r="E907" s="17"/>
+      <x:c r="F907" s="28"/>
     </x:row>
     <x:row r="908">
       <x:c r="A908" s="18"/>
@@ -6736,6 +7672,7 @@
       <x:c r="C908" s="19"/>
       <x:c r="D908" s="19"/>
       <x:c r="E908" s="17"/>
+      <x:c r="F908" s="28"/>
     </x:row>
     <x:row r="909">
       <x:c r="A909" s="18"/>
@@ -6743,6 +7680,7 @@
       <x:c r="C909" s="19"/>
       <x:c r="D909" s="19"/>
       <x:c r="E909" s="17"/>
+      <x:c r="F909" s="28"/>
     </x:row>
     <x:row r="910">
       <x:c r="A910" s="18"/>
@@ -6750,6 +7688,7 @@
       <x:c r="C910" s="19"/>
       <x:c r="D910" s="19"/>
       <x:c r="E910" s="17"/>
+      <x:c r="F910" s="28"/>
     </x:row>
     <x:row r="911">
       <x:c r="A911" s="18"/>
@@ -6757,6 +7696,7 @@
       <x:c r="C911" s="19"/>
       <x:c r="D911" s="19"/>
       <x:c r="E911" s="17"/>
+      <x:c r="F911" s="28"/>
     </x:row>
     <x:row r="912">
       <x:c r="A912" s="18"/>
@@ -6764,6 +7704,7 @@
       <x:c r="C912" s="19"/>
       <x:c r="D912" s="19"/>
       <x:c r="E912" s="17"/>
+      <x:c r="F912" s="28"/>
     </x:row>
     <x:row r="913">
       <x:c r="A913" s="18"/>
@@ -6771,6 +7712,7 @@
       <x:c r="C913" s="19"/>
       <x:c r="D913" s="19"/>
       <x:c r="E913" s="17"/>
+      <x:c r="F913" s="28"/>
     </x:row>
     <x:row r="914">
       <x:c r="A914" s="18"/>
@@ -6778,6 +7720,7 @@
       <x:c r="C914" s="19"/>
       <x:c r="D914" s="19"/>
       <x:c r="E914" s="17"/>
+      <x:c r="F914" s="28"/>
     </x:row>
     <x:row r="915">
       <x:c r="A915" s="18"/>
@@ -6785,6 +7728,7 @@
       <x:c r="C915" s="19"/>
       <x:c r="D915" s="19"/>
       <x:c r="E915" s="17"/>
+      <x:c r="F915" s="28"/>
     </x:row>
     <x:row r="916">
       <x:c r="A916" s="18"/>
@@ -6792,6 +7736,7 @@
       <x:c r="C916" s="19"/>
       <x:c r="D916" s="19"/>
       <x:c r="E916" s="17"/>
+      <x:c r="F916" s="28"/>
     </x:row>
     <x:row r="917">
       <x:c r="A917" s="18"/>
@@ -6799,6 +7744,7 @@
       <x:c r="C917" s="19"/>
       <x:c r="D917" s="19"/>
       <x:c r="E917" s="17"/>
+      <x:c r="F917" s="28"/>
     </x:row>
     <x:row r="918">
       <x:c r="A918" s="18"/>
@@ -6806,6 +7752,7 @@
       <x:c r="C918" s="19"/>
       <x:c r="D918" s="19"/>
       <x:c r="E918" s="17"/>
+      <x:c r="F918" s="28"/>
     </x:row>
     <x:row r="919">
       <x:c r="A919" s="18"/>
@@ -6813,6 +7760,7 @@
       <x:c r="C919" s="19"/>
       <x:c r="D919" s="19"/>
       <x:c r="E919" s="17"/>
+      <x:c r="F919" s="28"/>
     </x:row>
     <x:row r="920">
       <x:c r="A920" s="18"/>
@@ -6820,6 +7768,7 @@
       <x:c r="C920" s="19"/>
       <x:c r="D920" s="19"/>
       <x:c r="E920" s="17"/>
+      <x:c r="F920" s="28"/>
     </x:row>
     <x:row r="921">
       <x:c r="A921" s="18"/>
@@ -6827,6 +7776,7 @@
       <x:c r="C921" s="19"/>
       <x:c r="D921" s="19"/>
       <x:c r="E921" s="17"/>
+      <x:c r="F921" s="28"/>
     </x:row>
     <x:row r="922">
       <x:c r="A922" s="18"/>
@@ -6834,6 +7784,7 @@
       <x:c r="C922" s="19"/>
       <x:c r="D922" s="19"/>
       <x:c r="E922" s="17"/>
+      <x:c r="F922" s="28"/>
     </x:row>
     <x:row r="923">
       <x:c r="A923" s="18"/>
@@ -6841,6 +7792,7 @@
       <x:c r="C923" s="19"/>
       <x:c r="D923" s="19"/>
       <x:c r="E923" s="17"/>
+      <x:c r="F923" s="28"/>
     </x:row>
     <x:row r="924">
       <x:c r="A924" s="18"/>
@@ -6848,6 +7800,7 @@
       <x:c r="C924" s="19"/>
       <x:c r="D924" s="19"/>
       <x:c r="E924" s="17"/>
+      <x:c r="F924" s="28"/>
     </x:row>
     <x:row r="925">
       <x:c r="A925" s="18"/>
@@ -6855,6 +7808,7 @@
       <x:c r="C925" s="19"/>
       <x:c r="D925" s="19"/>
       <x:c r="E925" s="17"/>
+      <x:c r="F925" s="28"/>
     </x:row>
     <x:row r="926">
       <x:c r="A926" s="18"/>
@@ -6862,6 +7816,7 @@
       <x:c r="C926" s="19"/>
       <x:c r="D926" s="19"/>
       <x:c r="E926" s="17"/>
+      <x:c r="F926" s="28"/>
     </x:row>
     <x:row r="927">
       <x:c r="A927" s="18"/>
@@ -6869,6 +7824,7 @@
       <x:c r="C927" s="19"/>
       <x:c r="D927" s="19"/>
       <x:c r="E927" s="17"/>
+      <x:c r="F927" s="28"/>
     </x:row>
     <x:row r="928">
       <x:c r="A928" s="18"/>
@@ -6876,6 +7832,7 @@
       <x:c r="C928" s="19"/>
       <x:c r="D928" s="19"/>
       <x:c r="E928" s="17"/>
+      <x:c r="F928" s="28"/>
     </x:row>
     <x:row r="929">
       <x:c r="A929" s="18"/>
@@ -6883,6 +7840,7 @@
       <x:c r="C929" s="19"/>
       <x:c r="D929" s="19"/>
       <x:c r="E929" s="17"/>
+      <x:c r="F929" s="28"/>
     </x:row>
     <x:row r="930">
       <x:c r="A930" s="18"/>
@@ -6890,6 +7848,7 @@
       <x:c r="C930" s="19"/>
       <x:c r="D930" s="19"/>
       <x:c r="E930" s="17"/>
+      <x:c r="F930" s="28"/>
     </x:row>
     <x:row r="931">
       <x:c r="A931" s="18"/>
@@ -6897,6 +7856,7 @@
       <x:c r="C931" s="19"/>
       <x:c r="D931" s="19"/>
       <x:c r="E931" s="17"/>
+      <x:c r="F931" s="28"/>
     </x:row>
     <x:row r="932">
       <x:c r="A932" s="18"/>
@@ -6904,6 +7864,7 @@
       <x:c r="C932" s="19"/>
       <x:c r="D932" s="19"/>
       <x:c r="E932" s="17"/>
+      <x:c r="F932" s="28"/>
     </x:row>
     <x:row r="933">
       <x:c r="A933" s="18"/>
@@ -6911,6 +7872,7 @@
       <x:c r="C933" s="19"/>
       <x:c r="D933" s="19"/>
       <x:c r="E933" s="17"/>
+      <x:c r="F933" s="28"/>
     </x:row>
     <x:row r="934">
       <x:c r="A934" s="18"/>
@@ -6918,6 +7880,7 @@
       <x:c r="C934" s="19"/>
       <x:c r="D934" s="19"/>
       <x:c r="E934" s="17"/>
+      <x:c r="F934" s="28"/>
     </x:row>
     <x:row r="935">
       <x:c r="A935" s="18"/>
@@ -6925,6 +7888,7 @@
       <x:c r="C935" s="19"/>
       <x:c r="D935" s="19"/>
       <x:c r="E935" s="17"/>
+      <x:c r="F935" s="28"/>
     </x:row>
     <x:row r="936">
       <x:c r="A936" s="18"/>
@@ -6932,6 +7896,7 @@
       <x:c r="C936" s="19"/>
       <x:c r="D936" s="19"/>
       <x:c r="E936" s="17"/>
+      <x:c r="F936" s="28"/>
     </x:row>
     <x:row r="937">
       <x:c r="A937" s="18"/>
@@ -6939,6 +7904,7 @@
       <x:c r="C937" s="19"/>
       <x:c r="D937" s="19"/>
       <x:c r="E937" s="17"/>
+      <x:c r="F937" s="28"/>
     </x:row>
     <x:row r="938">
       <x:c r="A938" s="18"/>
@@ -6946,6 +7912,7 @@
       <x:c r="C938" s="19"/>
       <x:c r="D938" s="19"/>
       <x:c r="E938" s="17"/>
+      <x:c r="F938" s="28"/>
     </x:row>
     <x:row r="939">
       <x:c r="A939" s="18"/>
@@ -6953,6 +7920,7 @@
       <x:c r="C939" s="19"/>
       <x:c r="D939" s="19"/>
       <x:c r="E939" s="17"/>
+      <x:c r="F939" s="28"/>
     </x:row>
     <x:row r="940">
       <x:c r="A940" s="18"/>
@@ -6960,6 +7928,7 @@
       <x:c r="C940" s="19"/>
       <x:c r="D940" s="19"/>
       <x:c r="E940" s="17"/>
+      <x:c r="F940" s="28"/>
     </x:row>
     <x:row r="941">
       <x:c r="A941" s="18"/>
@@ -6967,6 +7936,7 @@
       <x:c r="C941" s="19"/>
       <x:c r="D941" s="19"/>
       <x:c r="E941" s="17"/>
+      <x:c r="F941" s="28"/>
     </x:row>
     <x:row r="942">
       <x:c r="A942" s="18"/>
@@ -6974,6 +7944,7 @@
       <x:c r="C942" s="19"/>
       <x:c r="D942" s="19"/>
       <x:c r="E942" s="17"/>
+      <x:c r="F942" s="28"/>
     </x:row>
     <x:row r="943">
       <x:c r="A943" s="18"/>
@@ -6981,6 +7952,7 @@
       <x:c r="C943" s="19"/>
       <x:c r="D943" s="19"/>
       <x:c r="E943" s="17"/>
+      <x:c r="F943" s="28"/>
     </x:row>
     <x:row r="944">
       <x:c r="A944" s="18"/>
@@ -6988,6 +7960,7 @@
       <x:c r="C944" s="19"/>
       <x:c r="D944" s="19"/>
       <x:c r="E944" s="17"/>
+      <x:c r="F944" s="28"/>
     </x:row>
     <x:row r="945">
       <x:c r="A945" s="18"/>
@@ -6995,6 +7968,7 @@
       <x:c r="C945" s="19"/>
       <x:c r="D945" s="19"/>
       <x:c r="E945" s="17"/>
+      <x:c r="F945" s="28"/>
     </x:row>
     <x:row r="946">
       <x:c r="A946" s="18"/>
@@ -7002,6 +7976,7 @@
       <x:c r="C946" s="19"/>
       <x:c r="D946" s="19"/>
       <x:c r="E946" s="17"/>
+      <x:c r="F946" s="28"/>
     </x:row>
     <x:row r="947">
       <x:c r="A947" s="18"/>
@@ -7009,6 +7984,7 @@
       <x:c r="C947" s="19"/>
       <x:c r="D947" s="19"/>
       <x:c r="E947" s="17"/>
+      <x:c r="F947" s="28"/>
     </x:row>
     <x:row r="948">
       <x:c r="A948" s="18"/>
@@ -7016,6 +7992,7 @@
       <x:c r="C948" s="19"/>
       <x:c r="D948" s="19"/>
       <x:c r="E948" s="17"/>
+      <x:c r="F948" s="28"/>
     </x:row>
     <x:row r="949">
       <x:c r="A949" s="18"/>
@@ -7023,6 +8000,7 @@
       <x:c r="C949" s="19"/>
       <x:c r="D949" s="19"/>
       <x:c r="E949" s="17"/>
+      <x:c r="F949" s="28"/>
     </x:row>
     <x:row r="950">
       <x:c r="A950" s="18"/>
@@ -7030,6 +8008,7 @@
       <x:c r="C950" s="19"/>
       <x:c r="D950" s="19"/>
       <x:c r="E950" s="17"/>
+      <x:c r="F950" s="28"/>
     </x:row>
     <x:row r="951">
       <x:c r="A951" s="18"/>
@@ -7037,6 +8016,7 @@
       <x:c r="C951" s="19"/>
       <x:c r="D951" s="19"/>
       <x:c r="E951" s="17"/>
+      <x:c r="F951" s="28"/>
     </x:row>
     <x:row r="952">
       <x:c r="A952" s="18"/>
@@ -7044,6 +8024,7 @@
       <x:c r="C952" s="19"/>
       <x:c r="D952" s="19"/>
       <x:c r="E952" s="17"/>
+      <x:c r="F952" s="28"/>
     </x:row>
     <x:row r="953">
       <x:c r="A953" s="18"/>
@@ -7051,6 +8032,7 @@
       <x:c r="C953" s="19"/>
       <x:c r="D953" s="19"/>
       <x:c r="E953" s="17"/>
+      <x:c r="F953" s="28"/>
     </x:row>
     <x:row r="954">
       <x:c r="A954" s="18"/>
@@ -7058,6 +8040,7 @@
       <x:c r="C954" s="19"/>
       <x:c r="D954" s="19"/>
       <x:c r="E954" s="17"/>
+      <x:c r="F954" s="28"/>
     </x:row>
     <x:row r="955">
       <x:c r="A955" s="18"/>
@@ -7065,6 +8048,7 @@
       <x:c r="C955" s="19"/>
       <x:c r="D955" s="19"/>
       <x:c r="E955" s="17"/>
+      <x:c r="F955" s="28"/>
     </x:row>
     <x:row r="956">
       <x:c r="A956" s="18"/>
@@ -7072,6 +8056,7 @@
       <x:c r="C956" s="19"/>
       <x:c r="D956" s="19"/>
       <x:c r="E956" s="17"/>
+      <x:c r="F956" s="28"/>
     </x:row>
     <x:row r="957">
       <x:c r="A957" s="18"/>
@@ -7079,6 +8064,7 @@
       <x:c r="C957" s="19"/>
       <x:c r="D957" s="19"/>
       <x:c r="E957" s="17"/>
+      <x:c r="F957" s="28"/>
     </x:row>
     <x:row r="958">
       <x:c r="A958" s="18"/>
@@ -7086,6 +8072,7 @@
       <x:c r="C958" s="19"/>
       <x:c r="D958" s="19"/>
       <x:c r="E958" s="17"/>
+      <x:c r="F958" s="28"/>
     </x:row>
     <x:row r="959">
       <x:c r="A959" s="18"/>
@@ -7093,6 +8080,7 @@
       <x:c r="C959" s="19"/>
       <x:c r="D959" s="19"/>
       <x:c r="E959" s="17"/>
+      <x:c r="F959" s="28"/>
     </x:row>
     <x:row r="960">
       <x:c r="A960" s="18"/>
@@ -7100,6 +8088,7 @@
       <x:c r="C960" s="19"/>
       <x:c r="D960" s="19"/>
       <x:c r="E960" s="17"/>
+      <x:c r="F960" s="28"/>
     </x:row>
     <x:row r="961">
       <x:c r="A961" s="18"/>
@@ -7107,6 +8096,7 @@
       <x:c r="C961" s="19"/>
       <x:c r="D961" s="19"/>
       <x:c r="E961" s="17"/>
+      <x:c r="F961" s="28"/>
     </x:row>
     <x:row r="962">
       <x:c r="A962" s="18"/>
@@ -7114,6 +8104,7 @@
       <x:c r="C962" s="19"/>
       <x:c r="D962" s="19"/>
       <x:c r="E962" s="17"/>
+      <x:c r="F962" s="28"/>
     </x:row>
     <x:row r="963">
       <x:c r="A963" s="18"/>
@@ -7121,6 +8112,7 @@
       <x:c r="C963" s="19"/>
       <x:c r="D963" s="19"/>
       <x:c r="E963" s="17"/>
+      <x:c r="F963" s="28"/>
     </x:row>
     <x:row r="964">
       <x:c r="A964" s="18"/>
@@ -7128,6 +8120,7 @@
       <x:c r="C964" s="19"/>
       <x:c r="D964" s="19"/>
       <x:c r="E964" s="17"/>
+      <x:c r="F964" s="28"/>
     </x:row>
     <x:row r="965">
       <x:c r="A965" s="18"/>
@@ -7135,6 +8128,7 @@
       <x:c r="C965" s="19"/>
       <x:c r="D965" s="19"/>
       <x:c r="E965" s="17"/>
+      <x:c r="F965" s="28"/>
     </x:row>
     <x:row r="966">
       <x:c r="A966" s="18"/>
@@ -7142,6 +8136,7 @@
       <x:c r="C966" s="19"/>
       <x:c r="D966" s="19"/>
       <x:c r="E966" s="17"/>
+      <x:c r="F966" s="28"/>
     </x:row>
     <x:row r="967">
       <x:c r="A967" s="18"/>
@@ -7149,6 +8144,7 @@
       <x:c r="C967" s="19"/>
       <x:c r="D967" s="19"/>
       <x:c r="E967" s="17"/>
+      <x:c r="F967" s="28"/>
     </x:row>
     <x:row r="968">
       <x:c r="A968" s="18"/>
@@ -7156,6 +8152,7 @@
       <x:c r="C968" s="19"/>
       <x:c r="D968" s="19"/>
       <x:c r="E968" s="17"/>
+      <x:c r="F968" s="28"/>
     </x:row>
     <x:row r="969">
       <x:c r="A969" s="18"/>
@@ -7163,6 +8160,7 @@
       <x:c r="C969" s="19"/>
       <x:c r="D969" s="19"/>
       <x:c r="E969" s="17"/>
+      <x:c r="F969" s="28"/>
     </x:row>
     <x:row r="970">
       <x:c r="A970" s="18"/>
@@ -7170,6 +8168,7 @@
       <x:c r="C970" s="19"/>
       <x:c r="D970" s="19"/>
       <x:c r="E970" s="17"/>
+      <x:c r="F970" s="28"/>
     </x:row>
     <x:row r="971">
       <x:c r="A971" s="18"/>
@@ -7177,6 +8176,7 @@
       <x:c r="C971" s="19"/>
       <x:c r="D971" s="19"/>
       <x:c r="E971" s="17"/>
+      <x:c r="F971" s="28"/>
     </x:row>
     <x:row r="972">
       <x:c r="A972" s="18"/>
@@ -7184,6 +8184,7 @@
       <x:c r="C972" s="19"/>
       <x:c r="D972" s="19"/>
       <x:c r="E972" s="17"/>
+      <x:c r="F972" s="28"/>
     </x:row>
     <x:row r="973">
       <x:c r="A973" s="18"/>
@@ -7191,6 +8192,7 @@
       <x:c r="C973" s="19"/>
       <x:c r="D973" s="19"/>
       <x:c r="E973" s="17"/>
+      <x:c r="F973" s="28"/>
     </x:row>
     <x:row r="974">
       <x:c r="A974" s="18"/>
@@ -7198,6 +8200,7 @@
       <x:c r="C974" s="19"/>
       <x:c r="D974" s="19"/>
       <x:c r="E974" s="17"/>
+      <x:c r="F974" s="28"/>
     </x:row>
     <x:row r="975">
       <x:c r="A975" s="18"/>
@@ -7205,6 +8208,7 @@
       <x:c r="C975" s="19"/>
       <x:c r="D975" s="19"/>
       <x:c r="E975" s="17"/>
+      <x:c r="F975" s="28"/>
     </x:row>
     <x:row r="976">
       <x:c r="A976" s="18"/>
@@ -7212,6 +8216,7 @@
       <x:c r="C976" s="19"/>
       <x:c r="D976" s="19"/>
       <x:c r="E976" s="17"/>
+      <x:c r="F976" s="28"/>
     </x:row>
     <x:row r="977">
       <x:c r="A977" s="18"/>
@@ -7219,6 +8224,7 @@
       <x:c r="C977" s="19"/>
       <x:c r="D977" s="19"/>
       <x:c r="E977" s="17"/>
+      <x:c r="F977" s="28"/>
     </x:row>
     <x:row r="978">
       <x:c r="A978" s="18"/>
@@ -7226,6 +8232,7 @@
       <x:c r="C978" s="19"/>
       <x:c r="D978" s="19"/>
       <x:c r="E978" s="17"/>
+      <x:c r="F978" s="28"/>
     </x:row>
     <x:row r="979">
       <x:c r="A979" s="18"/>
@@ -7233,6 +8240,7 @@
       <x:c r="C979" s="19"/>
       <x:c r="D979" s="19"/>
       <x:c r="E979" s="17"/>
+      <x:c r="F979" s="28"/>
     </x:row>
     <x:row r="980">
       <x:c r="A980" s="18"/>
@@ -7240,6 +8248,7 @@
       <x:c r="C980" s="19"/>
       <x:c r="D980" s="19"/>
       <x:c r="E980" s="17"/>
+      <x:c r="F980" s="28"/>
     </x:row>
     <x:row r="981">
       <x:c r="A981" s="18"/>
@@ -7247,6 +8256,7 @@
       <x:c r="C981" s="19"/>
       <x:c r="D981" s="19"/>
       <x:c r="E981" s="17"/>
+      <x:c r="F981" s="28"/>
     </x:row>
     <x:row r="982">
       <x:c r="A982" s="18"/>
@@ -7254,6 +8264,7 @@
       <x:c r="C982" s="19"/>
       <x:c r="D982" s="19"/>
       <x:c r="E982" s="17"/>
+      <x:c r="F982" s="28"/>
     </x:row>
     <x:row r="983">
       <x:c r="A983" s="18"/>
@@ -7261,6 +8272,7 @@
       <x:c r="C983" s="19"/>
       <x:c r="D983" s="19"/>
       <x:c r="E983" s="17"/>
+      <x:c r="F983" s="28"/>
     </x:row>
     <x:row r="984">
       <x:c r="A984" s="18"/>
@@ -7268,6 +8280,7 @@
       <x:c r="C984" s="19"/>
       <x:c r="D984" s="19"/>
       <x:c r="E984" s="17"/>
+      <x:c r="F984" s="28"/>
     </x:row>
     <x:row r="985">
       <x:c r="A985" s="18"/>
@@ -7275,6 +8288,7 @@
       <x:c r="C985" s="19"/>
       <x:c r="D985" s="19"/>
       <x:c r="E985" s="17"/>
+      <x:c r="F985" s="28"/>
     </x:row>
     <x:row r="986">
       <x:c r="A986" s="18"/>
@@ -7282,6 +8296,7 @@
       <x:c r="C986" s="19"/>
       <x:c r="D986" s="19"/>
       <x:c r="E986" s="17"/>
+      <x:c r="F986" s="28"/>
     </x:row>
     <x:row r="987">
       <x:c r="A987" s="18"/>
@@ -7289,6 +8304,7 @@
       <x:c r="C987" s="19"/>
       <x:c r="D987" s="19"/>
       <x:c r="E987" s="17"/>
+      <x:c r="F987" s="28"/>
     </x:row>
     <x:row r="988">
       <x:c r="A988" s="18"/>
@@ -7296,6 +8312,7 @@
       <x:c r="C988" s="19"/>
       <x:c r="D988" s="19"/>
       <x:c r="E988" s="17"/>
+      <x:c r="F988" s="28"/>
     </x:row>
     <x:row r="989">
       <x:c r="A989" s="18"/>
@@ -7303,6 +8320,7 @@
       <x:c r="C989" s="19"/>
       <x:c r="D989" s="19"/>
       <x:c r="E989" s="17"/>
+      <x:c r="F989" s="28"/>
     </x:row>
     <x:row r="990">
       <x:c r="A990" s="18"/>
@@ -7310,6 +8328,7 @@
       <x:c r="C990" s="19"/>
       <x:c r="D990" s="19"/>
       <x:c r="E990" s="17"/>
+      <x:c r="F990" s="28"/>
     </x:row>
     <x:row r="991">
       <x:c r="A991" s="18"/>
@@ -7317,6 +8336,7 @@
       <x:c r="C991" s="19"/>
       <x:c r="D991" s="19"/>
       <x:c r="E991" s="17"/>
+      <x:c r="F991" s="28"/>
     </x:row>
     <x:row r="992">
       <x:c r="A992" s="18"/>
@@ -7324,6 +8344,7 @@
       <x:c r="C992" s="19"/>
       <x:c r="D992" s="19"/>
       <x:c r="E992" s="17"/>
+      <x:c r="F992" s="28"/>
     </x:row>
     <x:row r="993">
       <x:c r="A993" s="18"/>
@@ -7331,6 +8352,7 @@
       <x:c r="C993" s="19"/>
       <x:c r="D993" s="19"/>
       <x:c r="E993" s="17"/>
+      <x:c r="F993" s="28"/>
     </x:row>
     <x:row r="994">
       <x:c r="A994" s="18"/>
@@ -7338,6 +8360,7 @@
       <x:c r="C994" s="19"/>
       <x:c r="D994" s="19"/>
       <x:c r="E994" s="17"/>
+      <x:c r="F994" s="28"/>
     </x:row>
     <x:row r="995">
       <x:c r="A995" s="18"/>
@@ -7345,6 +8368,7 @@
       <x:c r="C995" s="19"/>
       <x:c r="D995" s="19"/>
       <x:c r="E995" s="17"/>
+      <x:c r="F995" s="28"/>
     </x:row>
     <x:row r="996">
       <x:c r="A996" s="18"/>
@@ -7352,6 +8376,7 @@
       <x:c r="C996" s="19"/>
       <x:c r="D996" s="19"/>
       <x:c r="E996" s="17"/>
+      <x:c r="F996" s="28"/>
     </x:row>
     <x:row r="997">
       <x:c r="A997" s="18"/>
@@ -7359,6 +8384,7 @@
       <x:c r="C997" s="19"/>
       <x:c r="D997" s="19"/>
       <x:c r="E997" s="17"/>
+      <x:c r="F997" s="28"/>
     </x:row>
     <x:row r="998">
       <x:c r="A998" s="18"/>
@@ -7366,6 +8392,7 @@
       <x:c r="C998" s="19"/>
       <x:c r="D998" s="19"/>
       <x:c r="E998" s="17"/>
+      <x:c r="F998" s="28"/>
     </x:row>
     <x:row r="999">
       <x:c r="A999" s="18"/>
@@ -7373,6 +8400,7 @@
       <x:c r="C999" s="19"/>
       <x:c r="D999" s="19"/>
       <x:c r="E999" s="17"/>
+      <x:c r="F999" s="28"/>
     </x:row>
     <x:row r="1000">
       <x:c r="A1000" s="18"/>
@@ -7380,6 +8408,7 @@
       <x:c r="C1000" s="19"/>
       <x:c r="D1000" s="19"/>
       <x:c r="E1000" s="17"/>
+      <x:c r="F1000" s="28"/>
     </x:row>
     <x:row r="1001">
       <x:c r="A1001" s="18"/>
@@ -7387,6 +8416,7 @@
       <x:c r="C1001" s="19"/>
       <x:c r="D1001" s="19"/>
       <x:c r="E1001" s="17"/>
+      <x:c r="F1001" s="28"/>
     </x:row>
     <x:row r="1002">
       <x:c r="A1002" s="18"/>
@@ -7394,6 +8424,7 @@
       <x:c r="C1002" s="19"/>
       <x:c r="D1002" s="19"/>
       <x:c r="E1002" s="17"/>
+      <x:c r="F1002" s="28"/>
     </x:row>
     <x:row r="1003">
       <x:c r="A1003" s="18"/>
@@ -7401,6 +8432,7 @@
       <x:c r="C1003" s="19"/>
       <x:c r="D1003" s="19"/>
       <x:c r="E1003" s="17"/>
+      <x:c r="F1003" s="28"/>
     </x:row>
     <x:row r="1004">
       <x:c r="A1004" s="18"/>
@@ -7408,15 +8440,16 @@
       <x:c r="C1004" s="19"/>
       <x:c r="D1004" s="19"/>
       <x:c r="E1004" s="17"/>
+      <x:c r="F1004" s="28"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
-  <x:dataValidations count="3">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="B5:B1004">
-      <x:formula1>"Reguler,Barang Sekunder,Pembelian Barang/Paylater"</x:formula1>
+      <x:formula1>"Reguler,Barang Sekunder,Pembelian Barang/Paylater,Voucher"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="whole" operator="greaterThan" sqref="C5:C1004">
       <x:formula1>0</x:formula1>
@@ -7424,6 +8457,9 @@
     <x:dataValidation type="whole" operator="between" sqref="D5:D1004">
       <x:formula1>1</x:formula1>
       <x:formula2>24</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="F5:F1004">
+      <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7443,7 +8479,7 @@
         <x:v>Versi template</x:v>
       </x:c>
       <x:c r="B1" s="20" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -7479,7 +8515,7 @@
         <x:v>Jenis Pinjaman</x:v>
       </x:c>
       <x:c r="B6" s="22" t="str">
-        <x:v>Reguler; Barang Sekunder; Pembelian Barang/Paylater</x:v>
+        <x:v>Reguler; Barang Sekunder; Pembelian Barang/Paylater; Voucher</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
@@ -7514,6 +8550,14 @@
         <x:v>Satu baris lengkap untuk satu pengajuan. Baris kosong diabaikan; baris sebagian ditolak.</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Biaya Admin (Nominal)</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Voucher: tenor 1 bulan. Isi kolom F dengan Rupiah bulat, termasuk 0. Kosongkan untuk jenis lain.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
